--- a/data/partner/Focus Partner Tracking BR.xlsx
+++ b/data/partner/Focus Partner Tracking BR.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mrovere/Library/CloudStorage/GoogleDrive-marcelo@mrovere.com/Other computers/My MacBook Pro/Tenable - geral/Internal - Tenable/Canais/2026 news/EM Cert/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mrovere/Documents/Codex/2026-05-29/acesso-o-google-drive-e-analise/mrovere-treino-push/data/partner/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8134D0E-2241-0747-815D-CB9C2EC72110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -574,14 +574,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -594,19 +591,14 @@
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="11">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -636,6 +628,14 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFC9DAF8"/>
           <bgColor rgb="FFC9DAF8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE5CD"/>
+          <bgColor rgb="FFFCE5CD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -945,38 +945,38 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="29"/>
-      <c r="U1" s="31" t="s">
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="30"/>
+      <c r="U1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="V1" s="29"/>
-      <c r="W1" s="31" t="s">
+      <c r="V1" s="30"/>
+      <c r="W1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="X1" s="30"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="30"/>
-      <c r="AA1" s="30"/>
-      <c r="AB1" s="30"/>
-      <c r="AC1" s="30"/>
-      <c r="AD1" s="30"/>
-      <c r="AE1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="29"/>
+      <c r="AA1" s="29"/>
+      <c r="AB1" s="29"/>
+      <c r="AC1" s="29"/>
+      <c r="AD1" s="29"/>
+      <c r="AE1" s="30"/>
     </row>
     <row r="2" spans="1:31" ht="13" x14ac:dyDescent="0.15">
       <c r="A2" s="2"/>
@@ -984,25 +984,25 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="33" t="s">
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
+      <c r="S2" s="29"/>
+      <c r="T2" s="30"/>
       <c r="U2" s="5" t="s">
         <v>5</v>
       </c>
@@ -1012,18 +1012,18 @@
       <c r="W2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="X2" s="34" t="s">
+      <c r="X2" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="Y2" s="30"/>
-      <c r="Z2" s="30"/>
-      <c r="AA2" s="29"/>
-      <c r="AB2" s="35" t="s">
+      <c r="Y2" s="29"/>
+      <c r="Z2" s="29"/>
+      <c r="AA2" s="30"/>
+      <c r="AB2" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="AC2" s="30"/>
-      <c r="AD2" s="30"/>
-      <c r="AE2" s="29"/>
+      <c r="AC2" s="29"/>
+      <c r="AD2" s="29"/>
+      <c r="AE2" s="30"/>
     </row>
     <row r="3" spans="1:31" ht="13" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
@@ -1125,10 +1125,10 @@
       <c r="F4" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="29"/>
+      <c r="H4" s="30"/>
       <c r="I4" s="20" t="s">
         <v>28</v>
       </c>
@@ -1147,15 +1147,15 @@
       <c r="N4" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="O4" s="28" t="s">
+      <c r="O4" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="P4" s="29"/>
-      <c r="Q4" s="28" t="s">
+      <c r="P4" s="30"/>
+      <c r="Q4" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="R4" s="30"/>
-      <c r="S4" s="29"/>
+      <c r="R4" s="29"/>
+      <c r="S4" s="30"/>
       <c r="T4" s="20" t="s">
         <v>28</v>
       </c>
@@ -11657,16 +11657,16 @@
   </sheetData>
   <autoFilter ref="A3:E19" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="10">
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="F1:T1"/>
+    <mergeCell ref="U1:V1"/>
     <mergeCell ref="W1:AE1"/>
     <mergeCell ref="F2:M2"/>
     <mergeCell ref="N2:T2"/>
     <mergeCell ref="X2:AA2"/>
     <mergeCell ref="AB2:AE2"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="O4:P4"/>
-    <mergeCell ref="Q4:S4"/>
-    <mergeCell ref="F1:T1"/>
-    <mergeCell ref="U1:V1"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:L19">
     <cfRule type="notContainsBlanks" dxfId="10" priority="2">
@@ -11698,25 +11698,25 @@
       <formula>"Accredited"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="V16">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+      <formula>"Accredited"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="W5:W19">
-    <cfRule type="notContainsBlanks" dxfId="4" priority="7">
+    <cfRule type="notContainsBlanks" dxfId="3" priority="7">
       <formula>LEN(TRIM(W5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X5:AE19">
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="high">
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="high">
       <formula>NOT(ISERROR(SEARCH(("high"),(X5))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="medium">
+    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="medium">
       <formula>NOT(ISERROR(SEARCH(("medium"),(X5))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="6" operator="containsText" text="low">
+    <cfRule type="containsText" dxfId="0" priority="6" operator="containsText" text="low">
       <formula>NOT(ISERROR(SEARCH(("low"),(X5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V16">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>"Accredited"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/partner/Focus Partner Tracking BR.xlsx
+++ b/data/partner/Focus Partner Tracking BR.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mrovere/Documents/Codex/2026-05-29/acesso-o-google-drive-e-analise/mrovere-treino-push/data/partner/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mrovere/Library/CloudStorage/GoogleDrive-marcelo@mrovere.com/Other computers/My MacBook Pro/Tenable - geral/Internal - Tenable/Canais/2026 news/EM Cert/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8134D0E-2241-0747-815D-CB9C2EC72110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -574,11 +574,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -591,14 +594,19 @@
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="11">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE5CD"/>
+          <bgColor rgb="FFFCE5CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -628,14 +636,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFC9DAF8"/>
           <bgColor rgb="FFC9DAF8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -945,38 +945,38 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="28" t="s">
+      <c r="F1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-      <c r="R1" s="29"/>
-      <c r="S1" s="29"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="28" t="s">
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="30"/>
+      <c r="R1" s="30"/>
+      <c r="S1" s="30"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="V1" s="30"/>
-      <c r="W1" s="28" t="s">
+      <c r="V1" s="29"/>
+      <c r="W1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="29"/>
-      <c r="AA1" s="29"/>
-      <c r="AB1" s="29"/>
-      <c r="AC1" s="29"/>
-      <c r="AD1" s="29"/>
-      <c r="AE1" s="30"/>
+      <c r="X1" s="30"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="30"/>
+      <c r="AA1" s="30"/>
+      <c r="AB1" s="30"/>
+      <c r="AC1" s="30"/>
+      <c r="AD1" s="30"/>
+      <c r="AE1" s="29"/>
     </row>
     <row r="2" spans="1:31" ht="13" x14ac:dyDescent="0.15">
       <c r="A2" s="2"/>
@@ -984,25 +984,25 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="32" t="s">
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="29"/>
-      <c r="T2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
+      <c r="T2" s="29"/>
       <c r="U2" s="5" t="s">
         <v>5</v>
       </c>
@@ -1012,18 +1012,18 @@
       <c r="W2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="X2" s="33" t="s">
+      <c r="X2" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="Y2" s="29"/>
-      <c r="Z2" s="29"/>
-      <c r="AA2" s="30"/>
-      <c r="AB2" s="34" t="s">
+      <c r="Y2" s="30"/>
+      <c r="Z2" s="30"/>
+      <c r="AA2" s="29"/>
+      <c r="AB2" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="AC2" s="29"/>
-      <c r="AD2" s="29"/>
-      <c r="AE2" s="30"/>
+      <c r="AC2" s="30"/>
+      <c r="AD2" s="30"/>
+      <c r="AE2" s="29"/>
     </row>
     <row r="3" spans="1:31" ht="13" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
@@ -1125,10 +1125,10 @@
       <c r="F4" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="35" t="s">
+      <c r="G4" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="30"/>
+      <c r="H4" s="29"/>
       <c r="I4" s="20" t="s">
         <v>28</v>
       </c>
@@ -1147,15 +1147,15 @@
       <c r="N4" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="O4" s="35" t="s">
+      <c r="O4" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="35" t="s">
+      <c r="P4" s="29"/>
+      <c r="Q4" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R4" s="29"/>
-      <c r="S4" s="30"/>
+      <c r="R4" s="30"/>
+      <c r="S4" s="29"/>
       <c r="T4" s="20" t="s">
         <v>28</v>
       </c>
@@ -11657,16 +11657,16 @@
   </sheetData>
   <autoFilter ref="A3:E19" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="10">
+    <mergeCell ref="W1:AE1"/>
+    <mergeCell ref="F2:M2"/>
+    <mergeCell ref="N2:T2"/>
+    <mergeCell ref="X2:AA2"/>
+    <mergeCell ref="AB2:AE2"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="O4:P4"/>
     <mergeCell ref="Q4:S4"/>
     <mergeCell ref="F1:T1"/>
     <mergeCell ref="U1:V1"/>
-    <mergeCell ref="W1:AE1"/>
-    <mergeCell ref="F2:M2"/>
-    <mergeCell ref="N2:T2"/>
-    <mergeCell ref="X2:AA2"/>
-    <mergeCell ref="AB2:AE2"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:L19">
     <cfRule type="notContainsBlanks" dxfId="10" priority="2">
@@ -11698,25 +11698,25 @@
       <formula>"Accredited"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V16">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
-      <formula>"Accredited"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="W5:W19">
-    <cfRule type="notContainsBlanks" dxfId="3" priority="7">
+    <cfRule type="notContainsBlanks" dxfId="4" priority="7">
       <formula>LEN(TRIM(W5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X5:AE19">
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="high">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="high">
       <formula>NOT(ISERROR(SEARCH(("high"),(X5))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="medium">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="medium">
       <formula>NOT(ISERROR(SEARCH(("medium"),(X5))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="6" operator="containsText" text="low">
+    <cfRule type="containsText" dxfId="1" priority="6" operator="containsText" text="low">
       <formula>NOT(ISERROR(SEARCH(("low"),(X5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V16">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"Accredited"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/partner/Focus Partner Tracking BR.xlsx
+++ b/data/partner/Focus Partner Tracking BR.xlsx
@@ -3,11 +3,12 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16960" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16960" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="BR" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Tech Certs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Guardian" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BR'!$A$3:$E$19</definedName>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -33,11 +34,6 @@
       <color rgb="FFFFFFFF"/>
       <sz val="16"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -68,8 +64,40 @@
       <color theme="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <color rgb="FF434343"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="12"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -148,8 +176,20 @@
         <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8F9"/>
+        <bgColor rgb="FFF6F8F9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -284,110 +324,187 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF284E3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFF6F8F9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFF6F8F9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFF6F8F9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF284E3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFF6F8F9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFF6F8F9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="15">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -417,6 +534,14 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFC9DAF8"/>
           <bgColor rgb="FFC9DAF8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE5CD"/>
+          <bgColor rgb="FFFCE5CD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -468,8 +593,55 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Guardian-style" pivot="0" count="4">
+      <tableStyleElement type="wholeTable" size="0" dxfId="14"/>
+      <tableStyleElement type="headerRow" dxfId="13"/>
+      <tableStyleElement type="firstRowStripe" dxfId="12"/>
+      <tableStyleElement type="secondRowStripe" dxfId="11"/>
+    </tableStyle>
+  </tableStyles>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -765,44 +937,44 @@
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
       <c r="E1" s="1" t="n"/>
-      <c r="F1" s="36" t="inlineStr">
+      <c r="F1" s="32" t="inlineStr">
         <is>
           <t>Cursos e certificacoes</t>
         </is>
       </c>
-      <c r="G1" s="37" t="n"/>
-      <c r="H1" s="37" t="n"/>
-      <c r="I1" s="37" t="n"/>
-      <c r="J1" s="37" t="n"/>
-      <c r="K1" s="37" t="n"/>
-      <c r="L1" s="37" t="n"/>
-      <c r="M1" s="37" t="n"/>
-      <c r="N1" s="37" t="n"/>
-      <c r="O1" s="37" t="n"/>
-      <c r="P1" s="37" t="n"/>
-      <c r="Q1" s="37" t="n"/>
-      <c r="R1" s="37" t="n"/>
-      <c r="S1" s="37" t="n"/>
-      <c r="T1" s="38" t="n"/>
-      <c r="U1" s="36" t="inlineStr">
+      <c r="G1" s="31" t="n"/>
+      <c r="H1" s="31" t="n"/>
+      <c r="I1" s="31" t="n"/>
+      <c r="J1" s="31" t="n"/>
+      <c r="K1" s="31" t="n"/>
+      <c r="L1" s="31" t="n"/>
+      <c r="M1" s="31" t="n"/>
+      <c r="N1" s="31" t="n"/>
+      <c r="O1" s="31" t="n"/>
+      <c r="P1" s="31" t="n"/>
+      <c r="Q1" s="31" t="n"/>
+      <c r="R1" s="31" t="n"/>
+      <c r="S1" s="31" t="n"/>
+      <c r="T1" s="29" t="n"/>
+      <c r="U1" s="32" t="inlineStr">
         <is>
           <t>EM Delivery</t>
         </is>
       </c>
-      <c r="V1" s="38" t="n"/>
-      <c r="W1" s="36" t="inlineStr">
+      <c r="V1" s="29" t="n"/>
+      <c r="W1" s="32" t="inlineStr">
         <is>
           <t>Pre Sales Delivery</t>
         </is>
       </c>
-      <c r="X1" s="37" t="n"/>
-      <c r="Y1" s="37" t="n"/>
-      <c r="Z1" s="37" t="n"/>
-      <c r="AA1" s="37" t="n"/>
-      <c r="AB1" s="37" t="n"/>
-      <c r="AC1" s="37" t="n"/>
-      <c r="AD1" s="37" t="n"/>
-      <c r="AE1" s="38" t="n"/>
+      <c r="X1" s="31" t="n"/>
+      <c r="Y1" s="31" t="n"/>
+      <c r="Z1" s="31" t="n"/>
+      <c r="AA1" s="31" t="n"/>
+      <c r="AB1" s="31" t="n"/>
+      <c r="AC1" s="31" t="n"/>
+      <c r="AD1" s="31" t="n"/>
+      <c r="AE1" s="29" t="n"/>
     </row>
     <row r="2" ht="13" customHeight="1">
       <c r="A2" s="2" t="n"/>
@@ -810,29 +982,29 @@
       <c r="C2" s="3" t="n"/>
       <c r="D2" s="3" t="n"/>
       <c r="E2" s="4" t="n"/>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="F2" s="30" t="inlineStr">
         <is>
           <t>Introduction</t>
         </is>
       </c>
-      <c r="G2" s="37" t="n"/>
-      <c r="H2" s="37" t="n"/>
-      <c r="I2" s="37" t="n"/>
-      <c r="J2" s="37" t="n"/>
-      <c r="K2" s="37" t="n"/>
-      <c r="L2" s="37" t="n"/>
-      <c r="M2" s="38" t="n"/>
-      <c r="N2" s="13" t="inlineStr">
+      <c r="G2" s="31" t="n"/>
+      <c r="H2" s="31" t="n"/>
+      <c r="I2" s="31" t="n"/>
+      <c r="J2" s="31" t="n"/>
+      <c r="K2" s="31" t="n"/>
+      <c r="L2" s="31" t="n"/>
+      <c r="M2" s="29" t="n"/>
+      <c r="N2" s="35" t="inlineStr">
         <is>
           <t>Specialist</t>
         </is>
       </c>
-      <c r="O2" s="37" t="n"/>
-      <c r="P2" s="37" t="n"/>
-      <c r="Q2" s="37" t="n"/>
-      <c r="R2" s="37" t="n"/>
-      <c r="S2" s="37" t="n"/>
-      <c r="T2" s="38" t="n"/>
+      <c r="O2" s="31" t="n"/>
+      <c r="P2" s="31" t="n"/>
+      <c r="Q2" s="31" t="n"/>
+      <c r="R2" s="31" t="n"/>
+      <c r="S2" s="31" t="n"/>
+      <c r="T2" s="29" t="n"/>
       <c r="U2" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">EM </t>
@@ -848,22 +1020,22 @@
           <t>Guardian</t>
         </is>
       </c>
-      <c r="X2" s="15" t="inlineStr">
+      <c r="X2" s="33" t="inlineStr">
         <is>
           <t>Demo</t>
         </is>
       </c>
-      <c r="Y2" s="37" t="n"/>
-      <c r="Z2" s="37" t="n"/>
-      <c r="AA2" s="38" t="n"/>
-      <c r="AB2" s="16" t="inlineStr">
+      <c r="Y2" s="31" t="n"/>
+      <c r="Z2" s="31" t="n"/>
+      <c r="AA2" s="29" t="n"/>
+      <c r="AB2" s="34" t="inlineStr">
         <is>
           <t>POV</t>
         </is>
       </c>
-      <c r="AC2" s="37" t="n"/>
-      <c r="AD2" s="37" t="n"/>
-      <c r="AE2" s="38" t="n"/>
+      <c r="AC2" s="31" t="n"/>
+      <c r="AD2" s="31" t="n"/>
+      <c r="AE2" s="29" t="n"/>
     </row>
     <row r="3" ht="13" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
@@ -892,72 +1064,72 @@
           <t>ONE</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
+      <c r="G3" s="30" t="inlineStr">
         <is>
           <t>VM</t>
         </is>
       </c>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="H3" s="30" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="I3" s="12" t="inlineStr">
+      <c r="I3" s="30" t="inlineStr">
         <is>
           <t>WAS</t>
         </is>
       </c>
-      <c r="J3" s="12" t="inlineStr">
+      <c r="J3" s="30" t="inlineStr">
         <is>
           <t>IE</t>
         </is>
       </c>
-      <c r="K3" s="12" t="inlineStr">
+      <c r="K3" s="30" t="inlineStr">
         <is>
           <t>OT</t>
         </is>
       </c>
-      <c r="L3" s="12" t="inlineStr">
+      <c r="L3" s="30" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
       </c>
-      <c r="M3" s="12" t="inlineStr">
+      <c r="M3" s="30" t="inlineStr">
         <is>
           <t>Intro CERT</t>
         </is>
       </c>
-      <c r="N3" s="13" t="inlineStr">
+      <c r="N3" s="35" t="inlineStr">
         <is>
           <t>ONE</t>
         </is>
       </c>
-      <c r="O3" s="13" t="inlineStr">
+      <c r="O3" s="35" t="inlineStr">
         <is>
           <t>VM</t>
         </is>
       </c>
-      <c r="P3" s="13" t="inlineStr">
+      <c r="P3" s="35" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="Q3" s="13" t="inlineStr">
+      <c r="Q3" s="35" t="inlineStr">
         <is>
           <t>IE</t>
         </is>
       </c>
-      <c r="R3" s="13" t="inlineStr">
+      <c r="R3" s="35" t="inlineStr">
         <is>
           <t>OT</t>
         </is>
       </c>
-      <c r="S3" s="13" t="inlineStr">
+      <c r="S3" s="35" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
       </c>
-      <c r="T3" s="13" t="inlineStr">
+      <c r="T3" s="35" t="inlineStr">
         <is>
           <t>SP CERT</t>
         </is>
@@ -973,42 +1145,42 @@
         </is>
       </c>
       <c r="W3" s="14" t="n"/>
-      <c r="X3" s="15" t="inlineStr">
+      <c r="X3" s="33" t="inlineStr">
         <is>
           <t>EM</t>
         </is>
       </c>
-      <c r="Y3" s="15" t="inlineStr">
+      <c r="Y3" s="33" t="inlineStr">
         <is>
           <t>VM/WAS</t>
         </is>
       </c>
-      <c r="Z3" s="15" t="inlineStr">
+      <c r="Z3" s="33" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
       </c>
-      <c r="AA3" s="15" t="inlineStr">
+      <c r="AA3" s="33" t="inlineStr">
         <is>
           <t>TPM</t>
         </is>
       </c>
-      <c r="AB3" s="16" t="inlineStr">
+      <c r="AB3" s="34" t="inlineStr">
         <is>
           <t>EM</t>
         </is>
       </c>
-      <c r="AC3" s="16" t="inlineStr">
+      <c r="AC3" s="34" t="inlineStr">
         <is>
           <t>VM/WAS</t>
         </is>
       </c>
-      <c r="AD3" s="16" t="inlineStr">
+      <c r="AD3" s="34" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
       </c>
-      <c r="AE3" s="16" t="inlineStr">
+      <c r="AE3" s="34" t="inlineStr">
         <is>
           <t>TPM</t>
         </is>
@@ -1025,12 +1197,12 @@
           <t>Req</t>
         </is>
       </c>
-      <c r="G4" s="39" t="inlineStr">
+      <c r="G4" s="28" t="inlineStr">
         <is>
           <t>1 out of 2</t>
         </is>
       </c>
-      <c r="H4" s="38" t="n"/>
+      <c r="H4" s="29" t="n"/>
       <c r="I4" s="20" t="inlineStr">
         <is>
           <t>Req</t>
@@ -1061,19 +1233,19 @@
           <t>Req</t>
         </is>
       </c>
-      <c r="O4" s="39" t="inlineStr">
+      <c r="O4" s="28" t="inlineStr">
         <is>
           <t>1 out of 2</t>
         </is>
       </c>
-      <c r="P4" s="38" t="n"/>
-      <c r="Q4" s="39" t="inlineStr">
+      <c r="P4" s="29" t="n"/>
+      <c r="Q4" s="28" t="inlineStr">
         <is>
           <t>2 out of 3</t>
         </is>
       </c>
-      <c r="R4" s="37" t="n"/>
-      <c r="S4" s="38" t="n"/>
+      <c r="R4" s="31" t="n"/>
+      <c r="S4" s="29" t="n"/>
       <c r="T4" s="20" t="inlineStr">
         <is>
           <t>Req</t>
@@ -11919,12 +12091,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N5:S19">
-    <cfRule type="notContainsBlanks" priority="3" dxfId="0">
+    <cfRule type="notContainsBlanks" priority="3" dxfId="4">
       <formula>LEN(TRIM(N5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T5:T19">
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="4">
       <formula>"Accredited"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11938,25 +12110,25 @@
       <formula>"Accredited"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="V16">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="4">
+      <formula>"Accredited"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="W5:W19">
-    <cfRule type="notContainsBlanks" priority="7" dxfId="4">
+    <cfRule type="notContainsBlanks" priority="7" dxfId="3">
       <formula>LEN(TRIM(W5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X5:AE19">
-    <cfRule type="containsText" priority="4" operator="containsText" dxfId="3" text="high">
+    <cfRule type="containsText" priority="4" operator="containsText" dxfId="2" text="high">
       <formula>NOT(ISERROR(SEARCH(("high"),(X5))))</formula>
     </cfRule>
-    <cfRule type="containsText" priority="5" operator="containsText" dxfId="2" text="medium">
+    <cfRule type="containsText" priority="5" operator="containsText" dxfId="1" text="medium">
       <formula>NOT(ISERROR(SEARCH(("medium"),(X5))))</formula>
     </cfRule>
-    <cfRule type="containsText" priority="6" operator="containsText" dxfId="1" text="low">
+    <cfRule type="containsText" priority="6" operator="containsText" dxfId="0" text="low">
       <formula>NOT(ISERROR(SEARCH(("low"),(X5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V16">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
-      <formula>"Accredited"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11970,617 +12142,1077 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:P13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID Reseller</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>VM-SE</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>VM-Sales</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>CS-SE</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>CS-Sales</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>OT-SE</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>OT-Sales</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>IE-SE</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>IE-Sales</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ASM-SE</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ASM-Sales</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Nessus</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ONE-SE</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ONE-Sales</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>MSSP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Shield</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>28</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H2" t="n">
+        <v>49</v>
+      </c>
+      <c r="I2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J2" t="n">
+        <v>38</v>
+      </c>
+      <c r="K2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L2" t="n">
+        <v>37</v>
+      </c>
+      <c r="M2" t="n">
+        <v>40</v>
+      </c>
+      <c r="N2" t="n">
+        <v>21</v>
+      </c>
+      <c r="O2" t="n">
+        <v>64</v>
+      </c>
+      <c r="P2" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>390733</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TDEC</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>739732</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Asper</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>7</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>579399</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>XSITE</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>9</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>8</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ISH</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H6" t="n">
+        <v>9</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>9</v>
+      </c>
+      <c r="N6" t="n">
+        <v>5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>15</v>
+      </c>
+      <c r="P6" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>993857</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>GlobaslSec</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>510201</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NetSecurity</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>7</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>458265</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Future</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" t="n">
+        <v>6</v>
+      </c>
+      <c r="P9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>119472</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>106294</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Under Protection</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M11" t="n">
+        <v>5</v>
+      </c>
+      <c r="N11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O11" t="n">
+        <v>8</v>
+      </c>
+      <c r="P11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>543439</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kryptus</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>686107</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>E-Safer</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4</v>
+      </c>
+      <c r="M13" t="n">
+        <v>4</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>9</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>ID Reseller</t>
+          <t>Guardian Name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>VM-SE</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>VM-Sales</t>
+          <t>Specialist Course</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>CS-SE</t>
+          <t>TCSA</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>CS-Sales</t>
+          <t>TCSE</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>OT-SE</t>
+          <t>TCDE</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>OT-Sales</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>IE-SE</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>IE-Sales</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>ASM-SE</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>ASM-Sales</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Nessus</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ONE-SE</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>ONE-Sales</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>MSSP</t>
+          <t>Obs</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>581437</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Daniel Batista</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>daniel.batista@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>Shield</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>28</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30</v>
-      </c>
-      <c r="E2" t="n">
-        <v>12</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30</v>
-      </c>
-      <c r="G2" t="n">
-        <v>17</v>
-      </c>
-      <c r="H2" t="n">
-        <v>49</v>
-      </c>
-      <c r="I2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J2" t="n">
-        <v>38</v>
-      </c>
-      <c r="K2" t="n">
-        <v>12</v>
-      </c>
-      <c r="L2" t="n">
-        <v>37</v>
-      </c>
-      <c r="M2" t="n">
-        <v>40</v>
-      </c>
-      <c r="N2" t="n">
-        <v>21</v>
-      </c>
-      <c r="O2" t="n">
-        <v>64</v>
-      </c>
-      <c r="P2" t="n">
-        <v>11</v>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>faltam provas</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>390733</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Enalta Diniz</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>elnata.diniz@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Shield</t>
+        </is>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>faltam provas</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Raul Carbonari</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>rcarbonari@tdec.com.br</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>TDEC</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E4" t="b">
         <v>1</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F4" t="b">
         <v>1</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>faltam provas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>David Celestino</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>david.celestino@asper.tec.br</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Asper</t>
+        </is>
+      </c>
+      <c r="D5" t="b">
         <v>1</v>
       </c>
-      <c r="G3" t="n">
+      <c r="E5" t="b">
         <v>1</v>
       </c>
-      <c r="H3" t="n">
+      <c r="F5" t="b">
         <v>1</v>
       </c>
-      <c r="I3" t="n">
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>faltam provas</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Avner Nahum</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avner.nahum@asper.tec.br</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Asper</t>
+        </is>
+      </c>
+      <c r="D6" t="b">
         <v>1</v>
       </c>
-      <c r="J3" t="n">
-        <v>3</v>
-      </c>
-      <c r="K3" t="n">
+      <c r="E6" t="b">
         <v>1</v>
       </c>
-      <c r="L3" t="n">
+      <c r="F6" t="b">
         <v>1</v>
       </c>
-      <c r="M3" t="n">
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>faltam provas</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Lucas Vasconcelos</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>lucas.silva@globalsectec.com.br</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GlobalSec</t>
+        </is>
+      </c>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>realizando curso intro para liberar especialista</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ISH</t>
+        </is>
+      </c>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>aguardando o nelson</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Alessandro Vitalino</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>alessandro.vitalino@netsecurity.com.br</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Netsecurity</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" t="b">
         <v>1</v>
       </c>
-      <c r="N3" t="n">
+      <c r="F9" t="b">
         <v>1</v>
       </c>
-      <c r="O3" t="n">
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>cursos liberados</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Gutenberg Brito</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>gutenberg.brito@netsecurity.com.br</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Netsecurity</t>
+        </is>
+      </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>739732</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Asper</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E4" t="n">
-        <v>5</v>
-      </c>
-      <c r="F4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J4" t="n">
-        <v>8</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" t="n">
-        <v>4</v>
-      </c>
-      <c r="N4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O4" t="n">
-        <v>7</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>579399</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>XSITE</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E5" t="n">
-        <v>9</v>
-      </c>
-      <c r="F5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>8</v>
-      </c>
-      <c r="J5" t="n">
-        <v>9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4</v>
-      </c>
-      <c r="L5" t="n">
-        <v>6</v>
-      </c>
-      <c r="M5" t="n">
-        <v>5</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>8</v>
-      </c>
-      <c r="P5" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>397166</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ISH</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>14</v>
-      </c>
-      <c r="D6" t="n">
-        <v>20</v>
-      </c>
-      <c r="E6" t="n">
-        <v>7</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G6" t="n">
-        <v>9</v>
-      </c>
-      <c r="H6" t="n">
-        <v>9</v>
-      </c>
-      <c r="I6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J6" t="n">
-        <v>8</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3</v>
-      </c>
-      <c r="L6" t="n">
-        <v>6</v>
-      </c>
-      <c r="M6" t="n">
-        <v>9</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>15</v>
-      </c>
-      <c r="P6" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>993857</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>GlobaslSec</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
+      <c r="F10" t="b">
         <v>1</v>
       </c>
-      <c r="J7" t="n">
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>cursos liberados</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Marco Leissman</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>marco.leissmann@underprotection.com.br</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Underprotection</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" t="b">
         <v>1</v>
       </c>
-      <c r="N7" t="n">
+      <c r="F11" t="b">
         <v>1</v>
       </c>
-      <c r="O7" t="n">
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>liberar treinamentos. finalizando online</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ney Gelbcke Junior</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ney.gelbcke@underprotection.com.br</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Underprotection</t>
+        </is>
+      </c>
+      <c r="D12" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>510201</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>NetSecurity</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" t="n">
-        <v>6</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="F12" t="b">
         <v>1</v>
       </c>
-      <c r="F8" t="n">
-        <v>4</v>
-      </c>
-      <c r="H8" t="n">
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>liberar treinamentos. finalizando online</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Yueslly Lisboa</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>yueslly.lisboa@xsite.com.br</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>XSite</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
         <v>1</v>
       </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="E13" t="b">
         <v>1</v>
       </c>
-      <c r="L8" t="n">
-        <v>4</v>
-      </c>
-      <c r="M8" t="n">
-        <v>3</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2</v>
-      </c>
-      <c r="O8" t="n">
-        <v>7</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="F13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>458265</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Future</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H9" t="n">
-        <v>5</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" t="n">
-        <v>4</v>
-      </c>
-      <c r="M9" t="n">
-        <v>4</v>
-      </c>
-      <c r="N9" t="n">
-        <v>4</v>
-      </c>
-      <c r="O9" t="n">
-        <v>6</v>
-      </c>
-      <c r="P9" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>119472</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Accenture</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
+      <c r="G13" t="b">
         <v>1</v>
       </c>
-      <c r="G10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2</v>
-      </c>
-      <c r="P10" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>106294</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Under Protection</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>5</v>
-      </c>
-      <c r="E11" t="n">
-        <v>5</v>
-      </c>
-      <c r="F11" t="n">
-        <v>6</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" t="n">
-        <v>5</v>
-      </c>
-      <c r="I11" t="n">
-        <v>4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>5</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>4</v>
-      </c>
-      <c r="M11" t="n">
-        <v>5</v>
-      </c>
-      <c r="N11" t="n">
-        <v>6</v>
-      </c>
-      <c r="O11" t="n">
-        <v>8</v>
-      </c>
-      <c r="P11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>543439</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Kryptus</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>4</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>686107</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>E-Safer</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>5</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>6</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="n">
-        <v>4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>5</v>
-      </c>
-      <c r="L13" t="n">
-        <v>4</v>
-      </c>
-      <c r="M13" t="n">
-        <v>4</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3</v>
-      </c>
-      <c r="O13" t="n">
-        <v>9</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/partner/Focus Partner Tracking BR.xlsx
+++ b/data/partner/Focus Partner Tracking BR.xlsx
@@ -1161,69 +1161,63 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="G5" s="23" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="H5" s="23" t="inlineStr">
+      <c r="I5" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="I5" s="23" t="n"/>
-      <c r="J5" s="23" t="inlineStr">
+      <c r="J5" s="23" t="n"/>
+      <c r="K5" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="K5" s="23" t="inlineStr">
+      <c r="L5" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="L5" s="23" t="inlineStr">
+      <c r="M5" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="M5" s="23" t="inlineStr">
+      <c r="N5" s="23" t="inlineStr">
+        <is>
+          <t>Accredited</t>
+        </is>
+      </c>
+      <c r="O5" s="23" t="n"/>
+      <c r="P5" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="N5" s="23" t="n"/>
-      <c r="O5" s="23" t="inlineStr">
+      <c r="Q5" s="23" t="n"/>
+      <c r="R5" s="23" t="n"/>
+      <c r="S5" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="P5" s="23" t="n"/>
-      <c r="Q5" s="23" t="n"/>
-      <c r="R5" s="23" t="inlineStr">
+      <c r="T5" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="S5" s="23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="T5" s="23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="U5" s="23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
+      <c r="U5" s="23">
+        <f>IF(AND(O5&lt;&gt;"", OR(P5&lt;&gt;"", Q5&lt;&gt;""), OR(AND(R5&lt;&gt;"", S5&lt;&gt;""), AND(S5&lt;&gt;"", T5&lt;&gt;""), AND(R5&lt;&gt;"", T5&lt;&gt;""))), "Accredited", "In Progress")</f>
+        <v/>
       </c>
       <c r="V5" s="24" t="inlineStr">
         <is>
@@ -1301,36 +1295,42 @@
         </is>
       </c>
       <c r="G6" s="23" t="n"/>
-      <c r="H6" s="23" t="inlineStr">
+      <c r="H6" s="23" t="n"/>
+      <c r="I6" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="I6" s="23" t="n"/>
       <c r="J6" s="23" t="n"/>
-      <c r="K6" s="23" t="inlineStr">
+      <c r="K6" s="23" t="n"/>
+      <c r="L6" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="L6" s="23" t="n"/>
       <c r="M6" s="23" t="n"/>
-      <c r="N6" s="23" t="n"/>
-      <c r="O6" s="23" t="inlineStr">
+      <c r="N6" s="23">
+        <f>IF(AND(G6&lt;&gt;"", OR(H6&lt;&gt;"", I6&lt;&gt;""), J6&lt;&gt;"", K6&lt;&gt;"", L6&lt;&gt;"", M6&lt;&gt;""), "Accredited", "In Progress")</f>
+        <v/>
+      </c>
+      <c r="O6" s="23" t="n"/>
+      <c r="P6" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="P6" s="23" t="n"/>
       <c r="Q6" s="23" t="n"/>
       <c r="R6" s="23" t="n"/>
-      <c r="S6" s="23" t="inlineStr">
+      <c r="S6" s="23" t="n"/>
+      <c r="T6" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="T6" s="23" t="n"/>
-      <c r="U6" s="23" t="n"/>
+      <c r="U6" s="23">
+        <f>IF(AND(O6&lt;&gt;"", OR(P6&lt;&gt;"", Q6&lt;&gt;""), OR(AND(R6&lt;&gt;"", S6&lt;&gt;""), AND(S6&lt;&gt;"", T6&lt;&gt;""), AND(R6&lt;&gt;"", T6&lt;&gt;""))), "Accredited", "In Progress")</f>
+        <v/>
+      </c>
       <c r="V6" s="26" t="n"/>
       <c r="W6" s="23">
         <f>IF(AND(N6="Accredited", U6="Accredited",V6&lt;&gt;""), "Accredited", "In Progress")</f>
@@ -1406,42 +1406,47 @@
           <t>Silver</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="G7" s="23" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="H7" s="23" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="I7" s="23" t="n"/>
       <c r="J7" s="23" t="n"/>
-      <c r="K7" s="23" t="inlineStr">
+      <c r="K7" s="23" t="n"/>
+      <c r="L7" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="L7" s="23" t="n"/>
       <c r="M7" s="23" t="n"/>
-      <c r="N7" s="23" t="n"/>
-      <c r="O7" s="23" t="inlineStr">
+      <c r="N7" s="23">
+        <f>IF(AND(G7&lt;&gt;"", OR(H7&lt;&gt;"", I7&lt;&gt;""), J7&lt;&gt;"", K7&lt;&gt;"", L7&lt;&gt;"", M7&lt;&gt;""), "Accredited", "In Progress")</f>
+        <v/>
+      </c>
+      <c r="O7" s="23" t="n"/>
+      <c r="P7" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="P7" s="23" t="n"/>
       <c r="Q7" s="23" t="n"/>
       <c r="R7" s="23" t="n"/>
       <c r="S7" s="23" t="n"/>
       <c r="T7" s="23" t="n"/>
-      <c r="U7" s="23" t="n"/>
+      <c r="U7" s="23">
+        <f>IF(AND(O7&lt;&gt;"", OR(P7&lt;&gt;"", Q7&lt;&gt;""), OR(AND(R7&lt;&gt;"", S7&lt;&gt;""), AND(S7&lt;&gt;"", T7&lt;&gt;""), AND(R7&lt;&gt;"", T7&lt;&gt;""))), "Accredited", "In Progress")</f>
+        <v/>
+      </c>
       <c r="V7" s="26" t="n"/>
       <c r="W7" s="23">
         <f>IF(AND(N7="Accredited", U7="Accredited",V7&lt;&gt;""), "Accredited", "In Progress")</f>
@@ -1513,62 +1518,60 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="G8" s="23" t="inlineStr">
+      <c r="G8" s="23" t="n"/>
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="H8" s="23" t="inlineStr">
+      <c r="I8" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="I8" s="23" t="n"/>
-      <c r="J8" s="23" t="inlineStr">
+      <c r="J8" s="23" t="n"/>
+      <c r="K8" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="K8" s="23" t="inlineStr">
+      <c r="L8" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="L8" s="23" t="inlineStr">
+      <c r="M8" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="M8" s="23" t="inlineStr">
+      <c r="N8" s="23">
+        <f>IF(AND(G8&lt;&gt;"", OR(H8&lt;&gt;"", I8&lt;&gt;""), J8&lt;&gt;"", K8&lt;&gt;"", L8&lt;&gt;"", M8&lt;&gt;""), "Accredited", "In Progress")</f>
+        <v/>
+      </c>
+      <c r="O8" s="23" t="n"/>
+      <c r="P8" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="N8" s="23" t="n"/>
-      <c r="O8" s="23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="P8" s="23" t="n"/>
       <c r="Q8" s="23" t="n"/>
       <c r="R8" s="23" t="n"/>
-      <c r="S8" s="23" t="inlineStr">
+      <c r="S8" s="23" t="n"/>
+      <c r="T8" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="T8" s="23" t="inlineStr">
+      <c r="U8" s="23">
+        <f>IF(AND(O8&lt;&gt;"", OR(P8&lt;&gt;"", Q8&lt;&gt;""), OR(AND(R8&lt;&gt;"", S8&lt;&gt;""), AND(S8&lt;&gt;"", T8&lt;&gt;""), AND(R8&lt;&gt;"", T8&lt;&gt;""))), "Accredited", "In Progress")</f>
+        <v/>
+      </c>
+      <c r="V8" s="26" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="U8" s="23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="V8" s="26" t="n"/>
       <c r="W8" s="23">
         <f>IF(AND(N8="Accredited", U8="Accredited",V8&lt;&gt;""), "Accredited", "In Progress")</f>
         <v/>
@@ -1643,65 +1646,58 @@
           <t>Platinum</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="H9" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="H9" s="23" t="inlineStr">
+      <c r="I9" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="I9" s="23" t="n"/>
-      <c r="J9" s="23" t="inlineStr">
+      <c r="J9" s="23" t="n"/>
+      <c r="K9" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="K9" s="23" t="inlineStr">
+      <c r="L9" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="L9" s="23" t="inlineStr">
+      <c r="M9" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="M9" s="23" t="inlineStr">
+      <c r="N9" s="23">
+        <f>IF(AND(G9&lt;&gt;"", OR(H9&lt;&gt;"", I9&lt;&gt;""), J9&lt;&gt;"", K9&lt;&gt;"", L9&lt;&gt;"", M9&lt;&gt;""), "Accredited", "In Progress")</f>
+        <v/>
+      </c>
+      <c r="O9" s="23" t="n"/>
+      <c r="P9" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="N9" s="23" t="n"/>
-      <c r="O9" s="23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="P9" s="23" t="n"/>
       <c r="Q9" s="23" t="n"/>
       <c r="R9" s="23" t="n"/>
-      <c r="S9" s="23" t="inlineStr">
+      <c r="S9" s="23" t="n"/>
+      <c r="T9" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="T9" s="23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="U9" s="23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
+      <c r="U9" s="23">
+        <f>IF(AND(O9&lt;&gt;"", OR(P9&lt;&gt;"", Q9&lt;&gt;""), OR(AND(R9&lt;&gt;"", S9&lt;&gt;""), AND(S9&lt;&gt;"", T9&lt;&gt;""), AND(R9&lt;&gt;"", T9&lt;&gt;""))), "Accredited", "In Progress")</f>
+        <v/>
       </c>
       <c r="V9" s="24" t="inlineStr">
         <is>
@@ -1786,21 +1782,27 @@
       <c r="H10" s="23" t="n"/>
       <c r="I10" s="23" t="n"/>
       <c r="J10" s="23" t="n"/>
-      <c r="K10" s="23" t="inlineStr">
+      <c r="K10" s="23" t="n"/>
+      <c r="L10" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="L10" s="23" t="n"/>
       <c r="M10" s="23" t="n"/>
-      <c r="N10" s="23" t="n"/>
+      <c r="N10" s="23">
+        <f>IF(AND(G10&lt;&gt;"", OR(H10&lt;&gt;"", I10&lt;&gt;""), J10&lt;&gt;"", K10&lt;&gt;"", L10&lt;&gt;"", M10&lt;&gt;""), "Accredited", "In Progress")</f>
+        <v/>
+      </c>
       <c r="O10" s="23" t="n"/>
       <c r="P10" s="23" t="n"/>
       <c r="Q10" s="23" t="n"/>
       <c r="R10" s="23" t="n"/>
       <c r="S10" s="23" t="n"/>
       <c r="T10" s="23" t="n"/>
-      <c r="U10" s="23" t="n"/>
+      <c r="U10" s="23">
+        <f>IF(AND(O10&lt;&gt;"", OR(P10&lt;&gt;"", Q10&lt;&gt;""), OR(AND(R10&lt;&gt;"", S10&lt;&gt;""), AND(S10&lt;&gt;"", T10&lt;&gt;""), AND(R10&lt;&gt;"", T10&lt;&gt;""))), "Accredited", "In Progress")</f>
+        <v/>
+      </c>
       <c r="V10" s="26" t="n"/>
       <c r="W10" s="23">
         <f>IF(AND(N10="Accredited", U10="Accredited",V10&lt;&gt;""), "Accredited", "In Progress")</f>
@@ -1840,59 +1842,60 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="G11" s="23" t="inlineStr">
+      <c r="H11" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="H11" s="23" t="inlineStr">
+      <c r="I11" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="I11" s="23" t="n"/>
-      <c r="J11" s="23" t="inlineStr">
+      <c r="J11" s="23" t="n"/>
+      <c r="K11" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="K11" s="23" t="inlineStr">
+      <c r="L11" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="L11" s="23" t="inlineStr">
+      <c r="M11" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="M11" s="23" t="inlineStr">
+      <c r="N11" s="23">
+        <f>IF(AND(G11&lt;&gt;"", OR(H11&lt;&gt;"", I11&lt;&gt;""), J11&lt;&gt;"", K11&lt;&gt;"", L11&lt;&gt;"", M11&lt;&gt;""), "Accredited", "In Progress")</f>
+        <v/>
+      </c>
+      <c r="O11" s="23" t="n"/>
+      <c r="P11" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="N11" s="23" t="n"/>
-      <c r="O11" s="23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="P11" s="23" t="n"/>
       <c r="Q11" s="23" t="n"/>
       <c r="R11" s="23" t="n"/>
       <c r="S11" s="23" t="n"/>
       <c r="T11" s="23" t="n"/>
-      <c r="U11" s="23" t="inlineStr">
+      <c r="U11" s="23">
+        <f>IF(AND(O11&lt;&gt;"", OR(P11&lt;&gt;"", Q11&lt;&gt;""), OR(AND(R11&lt;&gt;"", S11&lt;&gt;""), AND(S11&lt;&gt;"", T11&lt;&gt;""), AND(R11&lt;&gt;"", T11&lt;&gt;""))), "Accredited", "In Progress")</f>
+        <v/>
+      </c>
+      <c r="V11" s="26" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="V11" s="26" t="n"/>
       <c r="W11" s="23">
         <f>IF(AND(N11="Accredited", U11="Accredited",V11&lt;&gt;""), "Accredited", "In Progress")</f>
         <v/>
@@ -1963,37 +1966,43 @@
           <t>Silver</t>
         </is>
       </c>
-      <c r="G12" s="23" t="inlineStr">
+      <c r="G12" s="23" t="n"/>
+      <c r="H12" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="H12" s="23" t="inlineStr">
+      <c r="I12" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="I12" s="23" t="n"/>
       <c r="J12" s="23" t="n"/>
-      <c r="K12" s="23" t="inlineStr">
+      <c r="K12" s="23" t="n"/>
+      <c r="L12" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="L12" s="23" t="n"/>
       <c r="M12" s="23" t="n"/>
-      <c r="N12" s="23" t="n"/>
-      <c r="O12" s="23" t="inlineStr">
+      <c r="N12" s="23">
+        <f>IF(AND(G12&lt;&gt;"", OR(H12&lt;&gt;"", I12&lt;&gt;""), J12&lt;&gt;"", K12&lt;&gt;"", L12&lt;&gt;"", M12&lt;&gt;""), "Accredited", "In Progress")</f>
+        <v/>
+      </c>
+      <c r="O12" s="23" t="n"/>
+      <c r="P12" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="P12" s="23" t="n"/>
       <c r="Q12" s="23" t="n"/>
       <c r="R12" s="23" t="n"/>
       <c r="S12" s="23" t="n"/>
       <c r="T12" s="23" t="n"/>
-      <c r="U12" s="23" t="n"/>
+      <c r="U12" s="23">
+        <f>IF(AND(O12&lt;&gt;"", OR(P12&lt;&gt;"", Q12&lt;&gt;""), OR(AND(R12&lt;&gt;"", S12&lt;&gt;""), AND(S12&lt;&gt;"", T12&lt;&gt;""), AND(R12&lt;&gt;"", T12&lt;&gt;""))), "Accredited", "In Progress")</f>
+        <v/>
+      </c>
       <c r="V12" s="26" t="n"/>
       <c r="W12" s="23">
         <f>IF(AND(N12="Accredited", U12="Accredited",V12&lt;&gt;""), "Accredited", "In Progress")</f>
@@ -2033,44 +2042,42 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="G13" s="23" t="inlineStr">
+      <c r="G13" s="23" t="n"/>
+      <c r="H13" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="H13" s="23" t="n"/>
       <c r="I13" s="23" t="n"/>
       <c r="J13" s="23" t="n"/>
-      <c r="K13" s="23" t="inlineStr">
+      <c r="K13" s="23" t="n"/>
+      <c r="L13" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="L13" s="23" t="inlineStr">
+      <c r="M13" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="M13" s="23" t="inlineStr">
+      <c r="N13" s="23">
+        <f>IF(AND(G13&lt;&gt;"", OR(H13&lt;&gt;"", I13&lt;&gt;""), J13&lt;&gt;"", K13&lt;&gt;"", L13&lt;&gt;"", M13&lt;&gt;""), "Accredited", "In Progress")</f>
+        <v/>
+      </c>
+      <c r="O13" s="23" t="n"/>
+      <c r="P13" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="N13" s="23" t="n"/>
-      <c r="O13" s="23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="P13" s="23" t="n"/>
       <c r="Q13" s="23" t="n"/>
       <c r="R13" s="23" t="n"/>
       <c r="S13" s="23" t="n"/>
       <c r="T13" s="23" t="n"/>
-      <c r="U13" s="23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
+      <c r="U13" s="23">
+        <f>IF(AND(O13&lt;&gt;"", OR(P13&lt;&gt;"", Q13&lt;&gt;""), OR(AND(R13&lt;&gt;"", S13&lt;&gt;""), AND(S13&lt;&gt;"", T13&lt;&gt;""), AND(R13&lt;&gt;"", T13&lt;&gt;""))), "Accredited", "In Progress")</f>
+        <v/>
       </c>
       <c r="V13" s="26" t="inlineStr">
         <is>
@@ -2115,53 +2122,51 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="G14" s="23" t="inlineStr">
+      <c r="H14" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="H14" s="23" t="inlineStr">
+      <c r="I14" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="I14" s="23" t="n"/>
-      <c r="J14" s="23" t="inlineStr">
+      <c r="J14" s="23" t="n"/>
+      <c r="K14" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="K14" s="23" t="inlineStr">
+      <c r="L14" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="L14" s="23" t="inlineStr">
+      <c r="M14" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="M14" s="23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="N14" s="23" t="n"/>
+      <c r="N14" s="23" t="inlineStr">
+        <is>
+          <t>Accredited</t>
+        </is>
+      </c>
       <c r="O14" s="23" t="n"/>
       <c r="P14" s="23" t="n"/>
       <c r="Q14" s="23" t="n"/>
       <c r="R14" s="23" t="n"/>
       <c r="S14" s="23" t="n"/>
       <c r="T14" s="23" t="n"/>
-      <c r="U14" s="23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
+      <c r="U14" s="23">
+        <f>IF(AND(O14&lt;&gt;"", OR(P14&lt;&gt;"", Q14&lt;&gt;""), OR(AND(R14&lt;&gt;"", S14&lt;&gt;""), AND(S14&lt;&gt;"", T14&lt;&gt;""), AND(R14&lt;&gt;"", T14&lt;&gt;""))), "Accredited", "In Progress")</f>
+        <v/>
       </c>
       <c r="V14" s="24" t="inlineStr">
         <is>
@@ -2238,37 +2243,39 @@
           <t>Bronze</t>
         </is>
       </c>
-      <c r="G15" s="23" t="inlineStr">
+      <c r="G15" s="23" t="n"/>
+      <c r="H15" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="H15" s="23" t="n"/>
       <c r="I15" s="23" t="n"/>
       <c r="J15" s="23" t="n"/>
       <c r="K15" s="23" t="n"/>
-      <c r="L15" s="23" t="inlineStr">
+      <c r="L15" s="23" t="n"/>
+      <c r="M15" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="M15" s="23" t="inlineStr">
+      <c r="N15" s="23">
+        <f>IF(AND(G15&lt;&gt;"", OR(H15&lt;&gt;"", I15&lt;&gt;""), J15&lt;&gt;"", K15&lt;&gt;"", L15&lt;&gt;"", M15&lt;&gt;""), "Accredited", "In Progress")</f>
+        <v/>
+      </c>
+      <c r="O15" s="23" t="n"/>
+      <c r="P15" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="N15" s="23" t="n"/>
-      <c r="O15" s="23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="P15" s="23" t="n"/>
       <c r="Q15" s="23" t="n"/>
       <c r="R15" s="23" t="n"/>
       <c r="S15" s="23" t="n"/>
       <c r="T15" s="23" t="n"/>
-      <c r="U15" s="23" t="n"/>
+      <c r="U15" s="23">
+        <f>IF(AND(O15&lt;&gt;"", OR(P15&lt;&gt;"", Q15&lt;&gt;""), OR(AND(R15&lt;&gt;"", S15&lt;&gt;""), AND(S15&lt;&gt;"", T15&lt;&gt;""), AND(R15&lt;&gt;"", T15&lt;&gt;""))), "Accredited", "In Progress")</f>
+        <v/>
+      </c>
       <c r="V15" s="23" t="n"/>
       <c r="W15" s="23" t="inlineStr">
         <is>
@@ -2309,37 +2316,39 @@
           <t>Bronze</t>
         </is>
       </c>
-      <c r="G16" s="23" t="inlineStr">
+      <c r="G16" s="23" t="n"/>
+      <c r="H16" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="H16" s="23" t="n"/>
       <c r="I16" s="23" t="n"/>
       <c r="J16" s="23" t="n"/>
-      <c r="K16" s="23" t="inlineStr">
+      <c r="K16" s="23" t="n"/>
+      <c r="L16" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="L16" s="23" t="inlineStr">
+      <c r="M16" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="M16" s="23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="N16" s="23" t="n"/>
+      <c r="N16" s="23">
+        <f>IF(AND(G16&lt;&gt;"", OR(H16&lt;&gt;"", I16&lt;&gt;""), J16&lt;&gt;"", K16&lt;&gt;"", L16&lt;&gt;"", M16&lt;&gt;""), "Accredited", "In Progress")</f>
+        <v/>
+      </c>
       <c r="O16" s="23" t="n"/>
       <c r="P16" s="23" t="n"/>
       <c r="Q16" s="23" t="n"/>
       <c r="R16" s="23" t="n"/>
       <c r="S16" s="23" t="n"/>
       <c r="T16" s="23" t="n"/>
-      <c r="U16" s="23" t="n"/>
+      <c r="U16" s="23">
+        <f>IF(AND(O16&lt;&gt;"", OR(P16&lt;&gt;"", Q16&lt;&gt;""), OR(AND(R16&lt;&gt;"", S16&lt;&gt;""), AND(S16&lt;&gt;"", T16&lt;&gt;""), AND(R16&lt;&gt;"", T16&lt;&gt;""))), "Accredited", "In Progress")</f>
+        <v/>
+      </c>
       <c r="V16" s="23" t="n"/>
       <c r="W16" s="23">
         <f>IF(AND(Q16&lt;&gt;"", OR(R16&lt;&gt;"", S16&lt;&gt;""), OR(AND(T16&lt;&gt;"", U16&lt;&gt;""), AND(U16&lt;&gt;"", V16&lt;&gt;""), AND(T16&lt;&gt;"", V16&lt;&gt;""))), "Accredited", "In Progress")</f>

--- a/data/partner/Focus Partner Tracking BR.xlsx
+++ b/data/partner/Focus Partner Tracking BR.xlsx
@@ -316,7 +316,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -400,6 +400,10 @@
     <xf numFmtId="0" fontId="4" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2443,40 +2447,89 @@
       <c r="AF17" s="23" t="n"/>
     </row>
     <row r="18" ht="12.75" customHeight="1">
+      <c r="A18" s="39" t="n">
+        <v>644733</v>
+      </c>
       <c r="B18" s="39" t="inlineStr">
         <is>
           <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
         </is>
       </c>
-      <c r="C18" s="40" t="inlineStr">
+      <c r="C18" s="39" t="inlineStr">
         <is>
           <t>IT Protect</t>
         </is>
       </c>
-      <c r="D18" s="27" t="n"/>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="D18" s="39" t="n"/>
+      <c r="E18" s="39" t="inlineStr">
         <is>
           <t>Bronze</t>
         </is>
       </c>
-      <c r="G18" s="23" t="n"/>
-      <c r="H18" s="23" t="n"/>
-      <c r="I18" s="23" t="n"/>
+      <c r="F18" s="41" t="n"/>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H18" s="23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I18" s="23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="J18" s="23" t="n"/>
-      <c r="K18" s="23" t="n"/>
-      <c r="L18" s="23" t="n"/>
-      <c r="M18" s="23" t="n"/>
-      <c r="N18" s="23" t="n"/>
+      <c r="K18" s="23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L18" s="23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M18" s="23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N18" s="23">
+        <f>IF(AND(G18&lt;&gt;"", OR(H18&lt;&gt;"", I18&lt;&gt;""), J18&lt;&gt;"", K18&lt;&gt;"", L18&lt;&gt;"", M18&lt;&gt;""), "Accredited", "In Progress")</f>
+        <v/>
+      </c>
       <c r="O18" s="23" t="n"/>
-      <c r="P18" s="23" t="n"/>
-      <c r="Q18" s="23" t="n"/>
+      <c r="P18" s="23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="Q18" s="23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="R18" s="23" t="n"/>
       <c r="S18" s="23" t="n"/>
-      <c r="T18" s="23" t="n"/>
-      <c r="U18" s="23" t="n"/>
+      <c r="T18" s="23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="U18" s="23">
+        <f>IF(AND(O18&lt;&gt;"", OR(P18&lt;&gt;"", Q18&lt;&gt;""), OR(AND(R18&lt;&gt;"", S18&lt;&gt;""), AND(S18&lt;&gt;"", T18&lt;&gt;""), AND(R18&lt;&gt;"", T18&lt;&gt;""))), "Accredited", "In Progress")</f>
+        <v/>
+      </c>
       <c r="V18" s="23" t="n"/>
-      <c r="W18" s="23" t="n"/>
-      <c r="X18" s="25" t="n"/>
+      <c r="W18" s="23">
+        <f>IF(AND(N18="Accredited", U18="Accredited",V18&lt;&gt;""), "Accredited", "In Progress")</f>
+        <v/>
+      </c>
+      <c r="X18" s="42" t="n"/>
       <c r="Y18" s="23" t="n"/>
       <c r="Z18" s="23" t="n"/>
       <c r="AA18" s="23" t="n"/>
@@ -6850,7 +6903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7463,6 +7516,88 @@
         <v>1</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>001f200001xtmLIAAY</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Servix Informática Ltda</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" t="n">
+        <v>5</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>4</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/partner/Focus Partner Tracking BR.xlsx
+++ b/data/partner/Focus Partner Tracking BR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16960" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BR" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guardian" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tech Certs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BR" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Guardian" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Tech Certs" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BR'!$A$3:$F$19</definedName>
@@ -5460,7 +5460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="8.6640625" customWidth="1" min="1" max="26"/>
@@ -5611,48 +5611,48 @@
       </c>
     </row>
     <row r="5" ht="13" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
-        <is>
-          <t>David Celestino</t>
-        </is>
-      </c>
-      <c r="B5" s="27" t="inlineStr">
-        <is>
-          <t>david.celestino@asper.tec.br</t>
-        </is>
-      </c>
-      <c r="C5" s="27" t="inlineStr">
-        <is>
-          <t>Asper</t>
-        </is>
-      </c>
-      <c r="D5" s="27" t="b">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Omar Fernandes</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ocavalcante@tdec.com.br</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TDEC</t>
+        </is>
+      </c>
+      <c r="D5" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="27" t="b">
+      <c r="E5" t="b">
         <v>1</v>
       </c>
-      <c r="F5" s="27" t="b">
+      <c r="F5" t="b">
         <v>1</v>
       </c>
-      <c r="G5" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" s="27" t="inlineStr">
-        <is>
-          <t>faltam provas</t>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Guardian concluído ✅</t>
         </is>
       </c>
     </row>
     <row r="6" ht="13" customHeight="1">
       <c r="A6" s="27" t="inlineStr">
         <is>
-          <t>Avner Nahum</t>
+          <t>David Celestino</t>
         </is>
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>avner.nahum@asper.tec.br</t>
+          <t>david.celestino@asper.tec.br</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
@@ -5681,51 +5681,51 @@
     <row r="7" ht="13" customHeight="1">
       <c r="A7" s="27" t="inlineStr">
         <is>
-          <t>Lucas Vasconcelos</t>
+          <t>Avner Nahum</t>
         </is>
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>lucas.silva@globalsectec.com.br</t>
+          <t>avner.nahum@asper.tec.br</t>
         </is>
       </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
-          <t>GlobalSec</t>
+          <t>Asper</t>
         </is>
       </c>
       <c r="D7" s="27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="27" t="b">
         <v>0</v>
       </c>
       <c r="H7" s="27" t="inlineStr">
         <is>
-          <t>realizando curso intro para liberar especialista</t>
+          <t>faltam provas</t>
         </is>
       </c>
     </row>
     <row r="8" ht="13" customHeight="1">
       <c r="A8" s="27" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Lucas Vasconcelos</t>
         </is>
       </c>
       <c r="B8" s="27" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>lucas.silva@globalsectec.com.br</t>
         </is>
       </c>
       <c r="C8" s="27" t="inlineStr">
         <is>
-          <t>ISH</t>
+          <t>GlobalSec</t>
         </is>
       </c>
       <c r="D8" s="27" t="b">
@@ -5742,28 +5742,24 @@
       </c>
       <c r="H8" s="27" t="inlineStr">
         <is>
-          <t>aguardando o nelson</t>
+          <t>realizando curso intro para liberar especialista</t>
         </is>
       </c>
     </row>
     <row r="9" ht="13" customHeight="1">
       <c r="A9" s="27" t="inlineStr">
         <is>
-          <t>Alessandro Vitalino</t>
-        </is>
-      </c>
-      <c r="B9" s="27" t="inlineStr">
-        <is>
-          <t>alessandro.vitalino@netsecurity.com.br</t>
-        </is>
-      </c>
+          <t>Thiago Gonçalves</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="inlineStr"/>
       <c r="C9" s="27" t="inlineStr">
         <is>
-          <t>Netsecurity</t>
+          <t>ISH</t>
         </is>
       </c>
       <c r="D9" s="27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="27" t="b">
         <v>1</v>
@@ -5772,23 +5768,23 @@
         <v>1</v>
       </c>
       <c r="G9" s="27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="27" t="inlineStr">
         <is>
-          <t>cursos liberados</t>
+          <t>Guardian concluído ✅</t>
         </is>
       </c>
     </row>
     <row r="10" ht="13" customHeight="1">
       <c r="A10" s="27" t="inlineStr">
         <is>
-          <t>Gutenberg Brito</t>
+          <t>Alessandro Vitalino</t>
         </is>
       </c>
       <c r="B10" s="27" t="inlineStr">
         <is>
-          <t>gutenberg.brito@netsecurity.com.br</t>
+          <t>alessandro.vitalino@netsecurity.com.br</t>
         </is>
       </c>
       <c r="C10" s="27" t="inlineStr">
@@ -5817,17 +5813,17 @@
     <row r="11" ht="13" customHeight="1">
       <c r="A11" s="27" t="inlineStr">
         <is>
-          <t>Marco Leissman</t>
+          <t>Gutenberg Brito</t>
         </is>
       </c>
       <c r="B11" s="27" t="inlineStr">
         <is>
-          <t>marco.leissmann@underprotection.com.br</t>
+          <t>gutenberg.brito@netsecurity.com.br</t>
         </is>
       </c>
       <c r="C11" s="27" t="inlineStr">
         <is>
-          <t>Underprotection</t>
+          <t>Netsecurity</t>
         </is>
       </c>
       <c r="D11" s="27" t="b">
@@ -5844,19 +5840,19 @@
       </c>
       <c r="H11" s="27" t="inlineStr">
         <is>
-          <t>liberar treinamentos. finalizando online</t>
+          <t>cursos liberados</t>
         </is>
       </c>
     </row>
     <row r="12" ht="13" customHeight="1">
       <c r="A12" s="27" t="inlineStr">
         <is>
-          <t>Ney Gelbcke Junior</t>
+          <t>Marco Leissman</t>
         </is>
       </c>
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>ney.gelbcke@underprotection.com.br</t>
+          <t>marco.leissmann@underprotection.com.br</t>
         </is>
       </c>
       <c r="C12" s="27" t="inlineStr">
@@ -5885,21 +5881,21 @@
     <row r="13" ht="13" customHeight="1">
       <c r="A13" s="27" t="inlineStr">
         <is>
-          <t>Yueslly Lisboa</t>
+          <t>Ney Gelbcke Junior</t>
         </is>
       </c>
       <c r="B13" s="27" t="inlineStr">
         <is>
-          <t>yueslly.lisboa@xsite.com.br</t>
+          <t>ney.gelbcke@underprotection.com.br</t>
         </is>
       </c>
       <c r="C13" s="27" t="inlineStr">
         <is>
-          <t>XSite</t>
+          <t>Underprotection</t>
         </is>
       </c>
       <c r="D13" s="27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="27" t="b">
         <v>1</v>
@@ -5908,6 +5904,40 @@
         <v>1</v>
       </c>
       <c r="G13" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" s="27" t="inlineStr">
+        <is>
+          <t>liberar treinamentos. finalizando online</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="27" t="inlineStr">
+        <is>
+          <t>Yueslly Lisboa</t>
+        </is>
+      </c>
+      <c r="B14" s="27" t="inlineStr">
+        <is>
+          <t>yueslly.lisboa@xsite.com.br</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>XSite</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="27" t="b">
         <v>1</v>
       </c>
     </row>

--- a/data/partner/Focus Partner Tracking BR.xlsx
+++ b/data/partner/Focus Partner Tracking BR.xlsx
@@ -5749,10 +5749,14 @@
     <row r="9" ht="13" customHeight="1">
       <c r="A9" s="27" t="inlineStr">
         <is>
-          <t>Thiago Gonçalves</t>
-        </is>
-      </c>
-      <c r="B9" s="27" t="inlineStr"/>
+          <t>Thiago Pereira Gonçalves</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>thiago.pereira@ish.com.br</t>
+        </is>
+      </c>
       <c r="C9" s="27" t="inlineStr">
         <is>
           <t>ISH</t>

--- a/data/partner/Focus Partner Tracking BR.xlsx
+++ b/data/partner/Focus Partner Tracking BR.xlsx
@@ -5943,6 +5943,11 @@
       </c>
       <c r="G14" s="27" t="b">
         <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Guardian concluído ✅</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>

--- a/data/partner/Focus Partner Tracking BR.xlsx
+++ b/data/partner/Focus Partner Tracking BR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16960" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="BR" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Guardian" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Tech Certs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BR" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guardian" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tech Certs" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BR'!$A$3:$F$19</definedName>
@@ -1318,19 +1318,11 @@
         <v/>
       </c>
       <c r="O6" s="23" t="n"/>
-      <c r="P6" s="23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="P6" s="23" t="n"/>
       <c r="Q6" s="23" t="n"/>
       <c r="R6" s="23" t="n"/>
       <c r="S6" s="23" t="n"/>
-      <c r="T6" s="23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="T6" s="23" t="n"/>
       <c r="U6" s="23">
         <f>IF(AND(O6&lt;&gt;"", OR(P6&lt;&gt;"", Q6&lt;&gt;""), OR(AND(R6&lt;&gt;"", S6&lt;&gt;""), AND(S6&lt;&gt;"", T6&lt;&gt;""), AND(R6&lt;&gt;"", T6&lt;&gt;""))), "Accredited", "In Progress")</f>
         <v/>
@@ -1438,11 +1430,7 @@
         <v/>
       </c>
       <c r="O7" s="23" t="n"/>
-      <c r="P7" s="23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="P7" s="23" t="n"/>
       <c r="Q7" s="23" t="n"/>
       <c r="R7" s="23" t="n"/>
       <c r="S7" s="23" t="n"/>
@@ -7037,19 +7025,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
         <v>21</v>
       </c>
       <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>19</v>
+      </c>
+      <c r="G2" t="n">
         <v>11</v>
-      </c>
-      <c r="F2" t="n">
-        <v>20</v>
-      </c>
-      <c r="G2" t="n">
-        <v>12</v>
       </c>
       <c r="H2" t="n">
         <v>35</v>
@@ -7058,13 +7046,13 @@
         <v>12</v>
       </c>
       <c r="J2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M2" t="n">
         <v>28</v>
@@ -7076,7 +7064,7 @@
         <v>49</v>
       </c>
       <c r="P2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -7159,7 +7147,7 @@
         <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
@@ -7171,7 +7159,7 @@
         <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O4" t="n">
         <v>7</v>
@@ -7242,13 +7230,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -7272,7 +7260,7 @@
         <v>5</v>
       </c>
       <c r="M6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N6" t="n">
         <v>5</v>
@@ -7293,17 +7281,23 @@
           <t>GLOBAL SEC. TECNOLOGIA &amp; INFORMACAO EIRELI</t>
         </is>
       </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
       <c r="H7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
       </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
       <c r="N7" t="n">
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -7365,10 +7359,10 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
         <v>3</v>
@@ -7377,7 +7371,7 @@
         <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
         <v>2</v>
@@ -7389,10 +7383,10 @@
         <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
         <v>4</v>
@@ -7401,7 +7395,7 @@
         <v>6</v>
       </c>
       <c r="P9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -7417,10 +7411,10 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
@@ -7445,46 +7439,46 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
         <v>5</v>
       </c>
       <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
         <v>2</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="n">
         <v>4</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" t="n">
         <v>4</v>
       </c>
-      <c r="J11" t="n">
+      <c r="N11" t="n">
         <v>5</v>
       </c>
-      <c r="K11" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>4</v>
-      </c>
-      <c r="M11" t="n">
-        <v>5</v>
-      </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>6</v>
       </c>
-      <c r="O11" t="n">
-        <v>8</v>
-      </c>
       <c r="P11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">

--- a/data/partner/Focus Partner Tracking BR.xlsx
+++ b/data/partner/Focus Partner Tracking BR.xlsx
@@ -1298,7 +1298,11 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="G6" s="23" t="n"/>
+      <c r="G6" s="23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H6" s="23" t="n"/>
       <c r="I6" s="23" t="inlineStr">
         <is>
@@ -1318,16 +1322,28 @@
         <v/>
       </c>
       <c r="O6" s="23" t="n"/>
-      <c r="P6" s="23" t="n"/>
+      <c r="P6" s="23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="Q6" s="23" t="n"/>
       <c r="R6" s="23" t="n"/>
       <c r="S6" s="23" t="n"/>
-      <c r="T6" s="23" t="n"/>
+      <c r="T6" s="23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="U6" s="23">
         <f>IF(AND(O6&lt;&gt;"", OR(P6&lt;&gt;"", Q6&lt;&gt;""), OR(AND(R6&lt;&gt;"", S6&lt;&gt;""), AND(S6&lt;&gt;"", T6&lt;&gt;""), AND(R6&lt;&gt;"", T6&lt;&gt;""))), "Accredited", "In Progress")</f>
         <v/>
       </c>
-      <c r="V6" s="26" t="n"/>
+      <c r="V6" s="26" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="W6" s="23">
         <f>IF(AND(N6="Accredited", U6="Accredited",V6&lt;&gt;""), "Accredited", "In Progress")</f>
         <v/>
@@ -5742,12 +5758,12 @@
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>thiago.pereira@ish.com.br</t>
+          <t>thiago.goncalves@asper.tec.br</t>
         </is>
       </c>
       <c r="C9" s="27" t="inlineStr">
         <is>
-          <t>ISH</t>
+          <t>Asper</t>
         </is>
       </c>
       <c r="D9" s="27" t="b">
@@ -7025,7 +7041,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
         <v>21</v>
@@ -7077,10 +7093,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -7356,7 +7372,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
         <v>4</v>

--- a/data/partner/Focus Partner Tracking BR.xlsx
+++ b/data/partner/Focus Partner Tracking BR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16960" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BR" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guardian" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tech Certs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BR" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Guardian" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Tech Certs" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BR'!$A$3:$F$19</definedName>
@@ -1209,11 +1209,7 @@
       </c>
       <c r="Q5" s="23" t="n"/>
       <c r="R5" s="23" t="n"/>
-      <c r="S5" s="23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="S5" s="23" t="n"/>
       <c r="T5" s="23" t="inlineStr">
         <is>
           <t>OK</t>

--- a/data/partner/Focus Partner Tracking BR.xlsx
+++ b/data/partner/Focus Partner Tracking BR.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16960" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="BR" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Guardian" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Tech Certs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BR" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guardian" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tech Certs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EM Certs Detail" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BR'!$A$3:$F$19</definedName>
@@ -7646,4 +7647,5914 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F210"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID Reseller</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Course</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Course Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Daniel Batista</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>daniel.batista@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>346</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Daniel Batista</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>daniel.batista@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>488</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Daniel Batista</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>daniel.batista@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>535</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Cloud Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Daniel Batista</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>daniel.batista@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>539</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Elnatã Diniz</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>elnata.diniz@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>375</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Elnatã Diniz</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>elnata.diniz@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>488</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Gabriel Andrade</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>gabriel.andrade@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>346</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Guilherme Silva</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>guilherme.silva@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>346</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Guilherme Silva</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>guilherme.silva@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>483</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tenable One Exposure Management Platform Introduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Guilherme Silva</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>guilherme.silva@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>535</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Cloud Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Lucas Albano</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>lucas.albano@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>346</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Lucas Albano</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>lucas.albano@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>552</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Exposure Management Business Theory</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Lucas Henrique</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>lucas.damasceno@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>303</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Lucas Henrique</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>lucas.damasceno@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>333</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Security Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Lucas Henrique</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>lucas.damasceno@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>346</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Lucas Henrique</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>lucas.damasceno@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>414</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Identity Exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Lucas Henrique</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>lucas.damasceno@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>488</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Lucas Henrique</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>lucas.damasceno@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>535</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Cloud Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Lucas Henrique</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>lucas.damasceno@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>539</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Lucas Henrique</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>lucas.damasceno@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>552</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Exposure Management Business Theory</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ronilson Machado</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ronilson.machado@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>303</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ronilson Machado</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ronilson.machado@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>346</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ronilson Machado</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ronilson.machado@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>535</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Cloud Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ronilson Machado</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ronilson.machado@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>552</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Exposure Management Business Theory</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Tamiris Silva</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>tamiris.silva@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>303</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Tamiris Silva</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>tamiris.silva@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>333</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Security Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Tamiris Silva</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>tamiris.silva@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>346</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Tamiris Silva</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>tamiris.silva@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>535</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Cloud Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Tamiris Silva</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>tamiris.silva@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>552</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Exposure Management Business Theory</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Thainá Goes</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>thaina.goes@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>552</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Exposure Management Business Theory</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Wander Marcio do Reis</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>wander.reis@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>303</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Wander Marcio do Reis</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>wander.reis@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>333</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Security Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Wander Marcio do Reis</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>wander.reis@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>346</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Wander Marcio do Reis</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>wander.reis@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>414</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Identity Exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Wander Marcio do Reis</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>wander.reis@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>488</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Wander Marcio do Reis</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>wander.reis@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>535</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Cloud Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>581437</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Wander Marcio do Reis</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>wander.reis@shieldsec.com.br</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>552</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Exposure Management Business Theory</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>390733</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>TDec Redes de Computadores Ltda</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Omar Fernandes</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ocavalcante@tdec.com.br</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>483</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tenable One Exposure Management Platform Introduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>390733</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>TDec Redes de Computadores Ltda</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Omar Fernandes</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ocavalcante@tdec.com.br</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>488</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>390733</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>TDec Redes de Computadores Ltda</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Omar Fernandes</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ocavalcante@tdec.com.br</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>539</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>390733</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>TDec Redes de Computadores Ltda</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Omar Fernandes</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ocavalcante@tdec.com.br</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>552</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Exposure Management Business Theory</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>390733</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>TDec Redes de Computadores Ltda</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Raúl Carbonari</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>rcarbonari@tdec.com.br</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>303</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>390733</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>TDec Redes de Computadores Ltda</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Raúl Carbonari</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>rcarbonari@tdec.com.br</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>333</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Security Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>739732</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ASPER TECNOLOGIA – RIO DE JANEIRO LTDA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Arlem Barros</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>arlem.barros@asper.tec.br</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>303</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>739732</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ASPER TECNOLOGIA – RIO DE JANEIRO LTDA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Caio Almeida</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>caio.almeida@asper.tec.br</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>346</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>739732</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ASPER TECNOLOGIA – RIO DE JANEIRO LTDA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Erico Albino</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>erico.albino@asper.tec.br</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>303</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>739732</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ASPER TECNOLOGIA – RIO DE JANEIRO LTDA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Erico Albino</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>erico.albino@asper.tec.br</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>483</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tenable One Exposure Management Platform Introduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>739732</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ASPER TECNOLOGIA – RIO DE JANEIRO LTDA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Nicole Grazielle Rodrigues dos Santos</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>nicole.santos@asper.tec.br</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>303</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>739732</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ASPER TECNOLOGIA – RIO DE JANEIRO LTDA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Nicole Grazielle Rodrigues dos Santos</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>nicole.santos@asper.tec.br</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>333</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Security Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>739732</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ASPER TECNOLOGIA – RIO DE JANEIRO LTDA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Nicole Grazielle Rodrigues dos Santos</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>nicole.santos@asper.tec.br</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>346</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>739732</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ASPER TECNOLOGIA – RIO DE JANEIRO LTDA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Nicole Grazielle Rodrigues dos Santos</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>nicole.santos@asper.tec.br</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>483</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tenable One Exposure Management Platform Introduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>579399</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>XSite</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Adriele De Jesus Primo</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>adriele.primo@xsite.com.br</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>346</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>579399</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>XSite</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Adriele De Jesus Primo</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>adriele.primo@xsite.com.br</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>414</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Identity Exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>579399</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>XSite</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Alexandre Gomes</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>alexandre.gomes@xsite.com.br</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>488</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>579399</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>XSite</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Breno Dos Santos Silva</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>breno.silva@xsite.com.br</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>346</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>579399</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>XSite</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>DANIEL DA CONCEIÇÃO</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>daniel.castro@xsite.com.br</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>346</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>579399</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>XSite</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>DANIEL DA CONCEIÇÃO</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>daniel.castro@xsite.com.br</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>552</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Exposure Management Business Theory</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>579399</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>XSite</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Diego Souza</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>diego.souza@xsite.com.br</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>346</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>579399</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>XSite</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Diego Souza</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>diego.souza@xsite.com.br</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>488</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>579399</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>XSite</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Emanuele Nobre</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>emanuele.nobre@xsite.com.br</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>488</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>579399</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>XSite</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Emanuele Nobre</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>emanuele.nobre@xsite.com.br</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>539</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>579399</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>XSite</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Jonatan Dos Santos Gomes</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>jonatan.gomes@xsite.com.br</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>346</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>579399</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>XSite</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Jonatan Dos Santos Gomes</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>jonatan.gomes@xsite.com.br</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>488</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>579399</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>XSite</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Jonatan Dos Santos Gomes</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>jonatan.gomes@xsite.com.br</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>535</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Cloud Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>579399</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>XSite</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Leandro Assmar</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>leandro.assmar@xsite.com.br</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>488</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>579399</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>XSite</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Leonardo Oliveira</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>leonardo.oliveira@xsite.com.br</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>539</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>579399</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>XSite</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Yueslly Lisboa</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>yueslly.lisboa@xsite.com.br</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>303</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>579399</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>XSite</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Yueslly Lisboa</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>yueslly.lisboa@xsite.com.br</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>333</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Security Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>579399</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>XSite</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Yueslly Lisboa</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>yueslly.lisboa@xsite.com.br</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>346</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>579399</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>XSite</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Yueslly Lisboa</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>yueslly.lisboa@xsite.com.br</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>488</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>579399</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>XSite</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Yuri Souza</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>yuri.souza@xsite.com.br</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>488</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Alexandre Pertel Gonçalves</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>alexandre.goncalves@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>346</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Anderson Lemos</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>anderson.lemos@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>303</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Anderson Lemos</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>anderson.lemos@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>333</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Security Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Anderson Lemos</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>anderson.lemos@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>539</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Anderson Neiva</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>anderson.neiva@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>303</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Claudio Neto</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>claudio.neto@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>535</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Cloud Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Claudio Neto</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>claudio.neto@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>539</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Danilo De Santana Dantas</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>danilo.dantas@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>535</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Cloud Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Diego Costa</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>diego.costa@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>346</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Edson Junior</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>edson.junior@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>539</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Edson Junior</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>edson.junior@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>552</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Exposure Management Business Theory</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Eliabe Bento</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>eliabe.bento@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>414</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Identity Exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Felipe Santos da Silva</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>felipe.ssilva@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>483</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Tenable One Exposure Management Platform Introduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Felipus Gomes</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>felipus.gomes@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>303</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Felipus Gomes</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>felipus.gomes@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>333</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Security Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Felipus Gomes</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>felipus.gomes@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>346</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Felipus Gomes</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>felipus.gomes@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>483</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Tenable One Exposure Management Platform Introduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Gabriel Gattini</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>gabriel.gattini@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>483</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Tenable One Exposure Management Platform Introduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Hecio Arruda</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>hecio.arruda@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>303</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Hecio Arruda</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>hecio.arruda@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>333</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Security Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Hecio Arruda</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>hecio.arruda@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>346</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Jacques Almeida</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>jacques.almeida@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>303</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Joelma Da Silva Batista</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>joelma.batista@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>333</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Security Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Joelma Da Silva Batista</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>joelma.batista@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>346</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Joelma Da Silva Batista</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>joelma.batista@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>488</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Jonas Nasser</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>jonas.nasser@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>346</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Kramer Saunders</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>kramer.saunders@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>346</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Lucas De Araujo Feitosa</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>lucas.feitosa@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>535</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Cloud Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Lucas De Araujo Feitosa</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>lucas.feitosa@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>539</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Marcelo Mantovani</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>marcelo.mantovani@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>346</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Marcelo Martins</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>marcelo.martins@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>333</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Security Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Marcelo Martins</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>marcelo.martins@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>539</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Marcio Mendes</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>marcio.mendes@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>539</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Mateus Mantovani</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>mateus.mantovani@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>333</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Security Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Matheus Manea</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>matheus.manea@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>346</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Raouf Ahmadian Yazdi</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>raouf.yazdi@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>333</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Security Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Reginaldo Santos</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>reginaldo.santos@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>303</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Reginaldo Santos</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>reginaldo.santos@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>483</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Tenable One Exposure Management Platform Introduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Roger Marques</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>roger.marques@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>483</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Tenable One Exposure Management Platform Introduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Sidnei Santana</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>sidnei.santana@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>346</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Sidnei Santana</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>sidnei.santana@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>488</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Tamiris Silva</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>tamiris.silva@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>303</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Tamiris Silva</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>tamiris.silva@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>333</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Security Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Tamiris Silva</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>tamiris.silva@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>346</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Tamiris Silva</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>tamiris.silva@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>488</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Thiago Gomes</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>thiago.gomes@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>346</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Valdir Neto</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>valdir.neto@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>539</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Valter Pereira da Costa Junior</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>valter.costa@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>303</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Valter Pereira da Costa Junior</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>valter.costa@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>346</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Victor Saldanha</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>victor.santos@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>303</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Victor Saldanha</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>victor.santos@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>333</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Security Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Victor Saldanha</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>victor.santos@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>346</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Victor Saldanha</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>victor.santos@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>414</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Identity Exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Victor Silva</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>victor.araujo@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>488</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Victor Silva</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>victor.araujo@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>539</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>397166</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>ISH Tecnologia SA</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Wagner De Jesus Belo Meireles</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>wagner.meireles@ish.com.br</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>346</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>993857</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>GLOBAL SEC. TECNOLOGIA &amp; INFORMACAO EIRELI</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Lucas Vasconcelos</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>lucas.vasconcelos@globalsectecnologia.com.br</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>303</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>510201</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Netsecurity Tecnologia LTDA</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>ALESSANDRO VIEIRA</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>alessandro.vitalino@netsecurity.com.br</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>303</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>510201</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Netsecurity Tecnologia LTDA</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>ALESSANDRO VIEIRA</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>alessandro.vitalino@netsecurity.com.br</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>333</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Security Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>510201</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Netsecurity Tecnologia LTDA</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>ALESSANDRO VIEIRA</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>alessandro.vitalino@netsecurity.com.br</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>346</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>510201</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Netsecurity Tecnologia LTDA</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>ALESSANDRO VIEIRA</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>alessandro.vitalino@netsecurity.com.br</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>414</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Identity Exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>510201</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Netsecurity Tecnologia LTDA</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>ALESSANDRO VIEIRA</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>alessandro.vitalino@netsecurity.com.br</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>535</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Cloud Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>510201</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Netsecurity Tecnologia LTDA</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>ALESSANDRO VIEIRA</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>alessandro.vitalino@netsecurity.com.br</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>552</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Exposure Management Business Theory</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>510201</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Netsecurity Tecnologia LTDA</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>André Feltrin</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>andre.feltrin@netsecurity.com.br</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>414</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Identity Exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>510201</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Netsecurity Tecnologia LTDA</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>André Feltrin</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>andre.feltrin@netsecurity.com.br</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>483</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Tenable One Exposure Management Platform Introduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>510201</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Netsecurity Tecnologia LTDA</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>André Feltrin</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>andre.feltrin@netsecurity.com.br</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>535</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Cloud Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>510201</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Netsecurity Tecnologia LTDA</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>André Feltrin</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>andre.feltrin@netsecurity.com.br</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>552</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Exposure Management Business Theory</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>510201</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Netsecurity Tecnologia LTDA</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Bruno Leite</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>bruno.leite@netsecurity.com.br</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>375</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>510201</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Netsecurity Tecnologia LTDA</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Bruno Leite</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>bruno.leite@netsecurity.com.br</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>488</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>510201</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Netsecurity Tecnologia LTDA</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Gutenberg Brito</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>gutenberg.brito@netsecurity.com.br</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>303</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>510201</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Netsecurity Tecnologia LTDA</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Gutenberg Brito</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>gutenberg.brito@netsecurity.com.br</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>333</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Security Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>510201</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Netsecurity Tecnologia LTDA</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Gutenberg Brito</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>gutenberg.brito@netsecurity.com.br</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>346</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>510201</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Netsecurity Tecnologia LTDA</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Gutenberg Brito</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>gutenberg.brito@netsecurity.com.br</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>535</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Cloud Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>510201</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Netsecurity Tecnologia LTDA</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Leonardo Silva</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>leonardo.silva@netsecurity.com.br</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>333</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Security Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>510201</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Netsecurity Tecnologia LTDA</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Leonardo Silva</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>leonardo.silva@netsecurity.com.br</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>346</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>510201</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Netsecurity Tecnologia LTDA</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Leonardo Silva</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>leonardo.silva@netsecurity.com.br</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>414</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Identity Exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>510201</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Netsecurity Tecnologia LTDA</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Leonardo Silva</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>leonardo.silva@netsecurity.com.br</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>535</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Cloud Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>510201</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Netsecurity Tecnologia LTDA</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Mar�lia Cardoso</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>marilia.cardoso@netsecurity.com.br</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>346</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>510201</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Netsecurity Tecnologia LTDA</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Thiago Ribeiro</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>thiago.ribeiro@netsecurity.com.br</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>375</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>510201</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Netsecurity Tecnologia LTDA</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Willian Santos Arruda</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>willian.arruda@netsecurity.com.br</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>535</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Cloud Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>458265</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Future Technologies Informatica Ltda</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Leonardo Figueira</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>leonardo.figueira@future.com.br</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>303</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>458265</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Future Technologies Informatica Ltda</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Leonardo Figueira</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>leonardo.figueira@future.com.br</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>333</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Security Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>458265</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Future Technologies Informatica Ltda</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Matheus Zaparolli</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>matheus.zaparolli@future.com.br</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>346</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>458265</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Future Technologies Informatica Ltda</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Odimar Junior</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>odimar.junior@future.com.br</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>333</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Security Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>458265</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Future Technologies Informatica Ltda</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Odimar Junior</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>odimar.junior@future.com.br</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>346</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>458265</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Future Technologies Informatica Ltda</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Pablo Silva</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>pablo.silva@future.com.br</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>488</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>458265</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Future Technologies Informatica Ltda</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Thaciany Silva</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>thaciany.silva@future.com.br</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>346</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>119472</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>ACCENTURE DO BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Carlos Araújo</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>carlos.h.araujo@accenture.com</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>552</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Exposure Management Business Theory</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>119472</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>ACCENTURE DO BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Felipe Guerreiro do Prado</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>f.guerreiro.do.prado@accenture.com</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>346</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>119472</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>ACCENTURE DO BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Herbert Barros</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>herbert.b.rocha@accenture.com</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>303</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>119472</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>ACCENTURE DO BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Herbert Barros</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>herbert.b.rocha@accenture.com</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>488</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>119472</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>ACCENTURE DO BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Moisés Dantas Felix</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>moises.d.felix@accenture.com</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>535</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Cloud Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>106294</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Under Protection Consultoria em Informatica LTDA</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Andrey Melo</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>andrey.melo@underprotection.com.br</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>333</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Security Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>106294</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Under Protection Consultoria em Informatica LTDA</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Andrey Melo</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>andrey.melo@underprotection.com.br</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>346</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>106294</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Under Protection Consultoria em Informatica LTDA</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Jefferson Abbin</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>jefferson.abbin@underprotection.com.br</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>535</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Cloud Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>106294</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Under Protection Consultoria em Informatica LTDA</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Jefferson Abbin</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>jefferson.abbin@underprotection.com.br</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>552</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Exposure Management Business Theory</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>106294</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Under Protection Consultoria em Informatica LTDA</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Julia Johnson</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>julia.melo@underprotection.com.br</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>414</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Identity Exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>106294</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Under Protection Consultoria em Informatica LTDA</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Marco Antonio Leissmann</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>marco.leissmann@underprotection.com.br</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>303</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>106294</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Under Protection Consultoria em Informatica LTDA</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Marco Antonio Leissmann</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>marco.leissmann@underprotection.com.br</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>333</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Security Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>106294</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Under Protection Consultoria em Informatica LTDA</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Marco Antonio Leissmann</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>marco.leissmann@underprotection.com.br</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>346</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>106294</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Under Protection Consultoria em Informatica LTDA</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Marco Antonio Leissmann</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>marco.leissmann@underprotection.com.br</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>414</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Identity Exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>106294</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Under Protection Consultoria em Informatica LTDA</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Marco Antonio Leissmann</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>marco.leissmann@underprotection.com.br</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>483</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Tenable One Exposure Management Platform Introduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>106294</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Under Protection Consultoria em Informatica LTDA</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Marco Antonio Leissmann</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>marco.leissmann@underprotection.com.br</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>535</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Cloud Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>106294</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Under Protection Consultoria em Informatica LTDA</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Marco Antonio Leissmann</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>marco.leissmann@underprotection.com.br</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>552</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Exposure Management Business Theory</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>106294</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Under Protection Consultoria em Informatica LTDA</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Ney Gelbcke Junior</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>ney.gelbcke@underprotection.com.br</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>346</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>106294</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Under Protection Consultoria em Informatica LTDA</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Ney Gelbcke Junior</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>ney.gelbcke@underprotection.com.br</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>552</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Exposure Management Business Theory</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>543439</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Kryptus Seguranca da Informacao SA</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Paulo Rigonato</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>paulo.monteiro@kryptus.com</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>346</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>543439</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Kryptus Seguranca da Informacao SA</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Paulo Rigonato</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>paulo.monteiro@kryptus.com</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>535</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Cloud Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>543439</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Kryptus Seguranca da Informacao SA</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Sabino Lima</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>sabino.lima@kryptus.com</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>346</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>543439</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Kryptus Seguranca da Informacao SA</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Sabino Lima</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>sabino.lima@kryptus.com</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>488</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>686107</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>e-Safer</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Adenilson Alves da Silva</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>asilva@e-safer.com.br</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>303</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>686107</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>e-Safer</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Ana Clara Ferreira</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>asantos@e-safer.com.br</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>346</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>686107</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>e-Safer</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Arlem Barros</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>abarros@e-safer.com.br</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>303</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>686107</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>e-Safer</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Bruno Magalhaes</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>bmagalhaes@e-safer.com.br</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>303</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>686107</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>e-Safer</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Bruno Magalhaes</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>bmagalhaes@e-safer.com.br</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>535</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Cloud Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>001f200001xtmLIAAY</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Servix Informática Ltda</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Evandro Lima</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>evandro.lima@servix.com</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>375</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>001f200001xtmLIAAY</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Servix Informática Ltda</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Evandro Lima</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>evandro.lima@servix.com</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>539</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>001f200001xtmLIAAY</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Servix Informática Ltda</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Filipe Augusto</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>filipe.silva@servix.com</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>346</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>001f200001xtmLIAAY</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Servix Informática Ltda</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>João Ferreira</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>joao.ferreira@servix.com</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>488</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>001f200001xtmLIAAY</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Servix Informática Ltda</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>João Ferreira</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>joao.ferreira@servix.com</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>539</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>001f200001xtmLIAAY</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Servix Informática Ltda</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Matheus Passos</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>matheus.passos@servix.com</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>333</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Security Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Ana Loucenco</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>ana.lourenco@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>333</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Security Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Ana Loucenco</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>ana.lourenco@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>346</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Ana Loucenco</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>ana.lourenco@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>483</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Tenable One Exposure Management Platform Introduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Ana Loucenco</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>ana.lourenco@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>535</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Cloud Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>FLAVIO BARBOSA</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>flavio.barbosa@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>346</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Paulo Medeiros</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>paulo.medeiros@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>375</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Paulo Medeiros</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>paulo.medeiros@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>539</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Pedro Comin</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>pedro.comin@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>303</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Pedro Comin</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>pedro.comin@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>346</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Pedro Comin</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>pedro.comin@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>488</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Ricardo Claus</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>ricardo.claus@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>346</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Ricardo Claus</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>ricardo.claus@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>414</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Identity Exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Ricardo Claus</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>ricardo.claus@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>483</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Tenable One Exposure Management Platform Introduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Ricardo Claus</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>ricardo.claus@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>535</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Cloud Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Sávio Alves</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>savio.alves@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>304</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Tenable Security Center Specialist</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Thiago Borges</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>thiago.borges@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>346</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Wilmar Navarro da Silva Neto</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>wilmar.neto@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>375</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/partner/Focus Partner Tracking BR.xlsx
+++ b/data/partner/Focus Partner Tracking BR.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16960" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BR" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guardian" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tech Certs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EM Certs Detail" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="BR" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Guardian" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Tech Certs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="EM Certs Detail" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BR'!$A$3:$F$19</definedName>
@@ -1995,11 +1995,7 @@
         <v/>
       </c>
       <c r="O12" s="23" t="n"/>
-      <c r="P12" s="23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="P12" s="23" t="n"/>
       <c r="Q12" s="23" t="n"/>
       <c r="R12" s="23" t="n"/>
       <c r="S12" s="23" t="n"/>
@@ -2056,11 +2052,7 @@
       <c r="I13" s="23" t="n"/>
       <c r="J13" s="23" t="n"/>
       <c r="K13" s="23" t="n"/>
-      <c r="L13" s="23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="L13" s="23" t="n"/>
       <c r="M13" s="23" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2071,11 +2063,7 @@
         <v/>
       </c>
       <c r="O13" s="23" t="n"/>
-      <c r="P13" s="23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="P13" s="23" t="n"/>
       <c r="Q13" s="23" t="n"/>
       <c r="R13" s="23" t="n"/>
       <c r="S13" s="23" t="n"/>
@@ -2248,13 +2236,21 @@
           <t>Bronze</t>
         </is>
       </c>
-      <c r="G15" s="23" t="n"/>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H15" s="23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="I15" s="23" t="n"/>
+      <c r="I15" s="23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="J15" s="23" t="n"/>
       <c r="K15" s="23" t="n"/>
       <c r="L15" s="23" t="n"/>
@@ -2281,7 +2277,11 @@
         <f>IF(AND(O15&lt;&gt;"", OR(P15&lt;&gt;"", Q15&lt;&gt;""), OR(AND(R15&lt;&gt;"", S15&lt;&gt;""), AND(S15&lt;&gt;"", T15&lt;&gt;""), AND(R15&lt;&gt;"", T15&lt;&gt;""))), "Accredited", "In Progress")</f>
         <v/>
       </c>
-      <c r="V15" s="23" t="n"/>
+      <c r="V15" s="23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="W15" s="23" t="inlineStr">
         <is>
           <t>In Progress</t>
@@ -2321,7 +2321,11 @@
           <t>Bronze</t>
         </is>
       </c>
-      <c r="G16" s="23" t="n"/>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H16" s="23" t="inlineStr">
         <is>
           <t>OK</t>
@@ -6943,7 +6947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7038,46 +7042,46 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H2" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="I2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J2" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N2" t="n">
+        <v>8</v>
+      </c>
+      <c r="O2" t="n">
         <v>9</v>
       </c>
-      <c r="L2" t="n">
-        <v>25</v>
-      </c>
-      <c r="M2" t="n">
-        <v>28</v>
-      </c>
-      <c r="N2" t="n">
-        <v>17</v>
-      </c>
-      <c r="O2" t="n">
-        <v>49</v>
-      </c>
       <c r="P2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -7090,10 +7094,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -7169,7 +7173,7 @@
         <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
         <v>7</v>
@@ -7212,7 +7216,7 @@
         <v>8</v>
       </c>
       <c r="J5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K5" t="n">
         <v>4</v>
@@ -7255,34 +7259,34 @@
         <v>3</v>
       </c>
       <c r="G6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H6" t="n">
         <v>9</v>
       </c>
-      <c r="H6" t="n">
-        <v>8</v>
-      </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K6" t="n">
         <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="P6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -7323,10 +7327,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -7340,17 +7344,14 @@
       <c r="J8" t="n">
         <v>2</v>
       </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
       <c r="L8" t="n">
         <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>7</v>
@@ -7402,13 +7403,13 @@
         <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
+        <v>5</v>
+      </c>
+      <c r="P9" t="n">
         <v>6</v>
-      </c>
-      <c r="P9" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -7420,26 +7421,11 @@
           <t>ACCENTURE DO BRASIL LTDA</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
       <c r="O10" t="n">
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -7510,7 +7496,7 @@
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -7642,6 +7628,55 @@
       </c>
       <c r="P15" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Demais Parceiros</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>50</v>
+      </c>
+      <c r="D16" t="n">
+        <v>144</v>
+      </c>
+      <c r="E16" t="n">
+        <v>31</v>
+      </c>
+      <c r="F16" t="n">
+        <v>31</v>
+      </c>
+      <c r="G16" t="n">
+        <v>20</v>
+      </c>
+      <c r="H16" t="n">
+        <v>44</v>
+      </c>
+      <c r="I16" t="n">
+        <v>25</v>
+      </c>
+      <c r="J16" t="n">
+        <v>73</v>
+      </c>
+      <c r="K16" t="n">
+        <v>23</v>
+      </c>
+      <c r="L16" t="n">
+        <v>40</v>
+      </c>
+      <c r="M16" t="n">
+        <v>52</v>
+      </c>
+      <c r="N16" t="n">
+        <v>65</v>
+      </c>
+      <c r="O16" t="n">
+        <v>158</v>
+      </c>
+      <c r="P16" t="n">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -7655,7 +7690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F210"/>
+  <dimension ref="A1:F235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7869,7 +7904,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Gabriel Andrade</t>
+          <t>Gabriel Lacerda</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -8261,7 +8296,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ronilson Machado</t>
+          <t>Ronilson Toledo Santos Machado</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -8289,7 +8324,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ronilson Machado</t>
+          <t>Ronilson Toledo Santos Machado</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -8317,7 +8352,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ronilson Machado</t>
+          <t>Ronilson Toledo Santos Machado</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -8345,7 +8380,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ronilson Machado</t>
+          <t>Ronilson Toledo Santos Machado</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -8728,29 +8763,29 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>390733</v>
+        <v>581437</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TDec Redes de Computadores Ltda</t>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Omar Fernandes</t>
+          <t>Wander Marcio do Reis</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ocavalcante@tdec.com.br</t>
+          <t>wander.reis@shieldsec.com.br</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>483</v>
+        <v>561</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tenable One Exposure Management Platform Introduction</t>
+          <t>Tenable One Exposure Management Platform Specialist On-Demand</t>
         </is>
       </c>
     </row>
@@ -8765,20 +8800,20 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Omar Fernandes</t>
+          <t>Raúl Carbonari</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ocavalcante@tdec.com.br</t>
+          <t>rcarbonari@tdec.com.br</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>488</v>
+        <v>303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
@@ -8793,104 +8828,104 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Omar Fernandes</t>
+          <t>Raúl Carbonari</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ocavalcante@tdec.com.br</t>
+          <t>rcarbonari@tdec.com.br</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>539</v>
+        <v>333</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tenable Cloud Security Specialist On-Demand</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>390733</v>
+        <v>739732</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TDec Redes de Computadores Ltda</t>
+          <t>ASPER TECNOLOGIA – RIO DE JANEIRO LTDA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Omar Fernandes</t>
+          <t>Arlem Barros</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ocavalcante@tdec.com.br</t>
+          <t>arlem.barros@asper.tec.br</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>552</v>
+        <v>303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Exposure Management Business Theory</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>390733</v>
+        <v>739732</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TDec Redes de Computadores Ltda</t>
+          <t>ASPER TECNOLOGIA – RIO DE JANEIRO LTDA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Raúl Carbonari</t>
+          <t>Caio Almeida</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>rcarbonari@tdec.com.br</t>
+          <t>caio.almeida@asper.tec.br</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>303</v>
+        <v>346</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>390733</v>
+        <v>739732</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TDec Redes de Computadores Ltda</t>
+          <t>ASPER TECNOLOGIA – RIO DE JANEIRO LTDA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Raúl Carbonari</t>
+          <t>Erico Albino</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>rcarbonari@tdec.com.br</t>
+          <t>erico.albino@asper.tec.br</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>333</v>
+        <v>303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
@@ -8905,12 +8940,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Arlem Barros</t>
+          <t>Nicole Grazielle Rodrigues dos Santos</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>arlem.barros@asper.tec.br</t>
+          <t>nicole.santos@asper.tec.br</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -8933,20 +8968,20 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Caio Almeida</t>
+          <t>Nicole Grazielle Rodrigues dos Santos</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>caio.almeida@asper.tec.br</t>
+          <t>nicole.santos@asper.tec.br</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
@@ -8961,20 +8996,20 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Erico Albino</t>
+          <t>Nicole Grazielle Rodrigues dos Santos</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>erico.albino@asper.tec.br</t>
+          <t>nicole.santos@asper.tec.br</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>303</v>
+        <v>346</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -8989,12 +9024,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Erico Albino</t>
+          <t>Nicole Grazielle Rodrigues dos Santos</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>erico.albino@asper.tec.br</t>
+          <t>nicole.santos@asper.tec.br</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -9008,113 +9043,113 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>739732</v>
+        <v>579399</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ASPER TECNOLOGIA – RIO DE JANEIRO LTDA</t>
+          <t>XSite</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nicole Grazielle Rodrigues dos Santos</t>
+          <t>Adriele De Jesus Primo</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>nicole.santos@asper.tec.br</t>
+          <t>adriele.primo@xsite.com.br</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>303</v>
+        <v>346</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>739732</v>
+        <v>579399</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ASPER TECNOLOGIA – RIO DE JANEIRO LTDA</t>
+          <t>XSite</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nicole Grazielle Rodrigues dos Santos</t>
+          <t>Adriele De Jesus Primo</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>nicole.santos@asper.tec.br</t>
+          <t>adriele.primo@xsite.com.br</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>333</v>
+        <v>414</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Introduction to Tenable Identity Exposure</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>739732</v>
+        <v>579399</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ASPER TECNOLOGIA – RIO DE JANEIRO LTDA</t>
+          <t>XSite</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Nicole Grazielle Rodrigues dos Santos</t>
+          <t>Alexandre Gomes</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>nicole.santos@asper.tec.br</t>
+          <t>alexandre.gomes@xsite.com.br</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>346</v>
+        <v>488</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>739732</v>
+        <v>579399</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ASPER TECNOLOGIA – RIO DE JANEIRO LTDA</t>
+          <t>XSite</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Nicole Grazielle Rodrigues dos Santos</t>
+          <t>Breno Dos Santos Silva</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>nicole.santos@asper.tec.br</t>
+          <t>breno.silva@xsite.com.br</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>483</v>
+        <v>346</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tenable One Exposure Management Platform Introduction</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -9129,20 +9164,20 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Adriele De Jesus Primo</t>
+          <t>DANIEL DA CONCEIÇÃO</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>adriele.primo@xsite.com.br</t>
+          <t>daniel.castro@xsite.com.br</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>346</v>
+        <v>552</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Exposure Management Business Theory</t>
         </is>
       </c>
     </row>
@@ -9157,20 +9192,20 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Adriele De Jesus Primo</t>
+          <t>Diego Souza</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>adriele.primo@xsite.com.br</t>
+          <t>diego.souza@xsite.com.br</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>414</v>
+        <v>346</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Identity Exposure</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -9185,12 +9220,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Alexandre Gomes</t>
+          <t>Diego Souza</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>alexandre.gomes@xsite.com.br</t>
+          <t>diego.souza@xsite.com.br</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -9213,20 +9248,20 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Breno Dos Santos Silva</t>
+          <t>Emanuele Nobre</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>breno.silva@xsite.com.br</t>
+          <t>emanuele.nobre@xsite.com.br</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>346</v>
+        <v>488</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
         </is>
       </c>
     </row>
@@ -9241,20 +9276,20 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DANIEL DA CONCEIÇÃO</t>
+          <t>Emanuele Nobre</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>daniel.castro@xsite.com.br</t>
+          <t>emanuele.nobre@xsite.com.br</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>346</v>
+        <v>539</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
         </is>
       </c>
     </row>
@@ -9269,20 +9304,20 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DANIEL DA CONCEIÇÃO</t>
+          <t>Jonatan Dos Santos Gomes</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>daniel.castro@xsite.com.br</t>
+          <t>jonatan.gomes@xsite.com.br</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>552</v>
+        <v>346</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Exposure Management Business Theory</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -9297,20 +9332,20 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Diego Souza</t>
+          <t>Jonatan Dos Santos Gomes</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>diego.souza@xsite.com.br</t>
+          <t>jonatan.gomes@xsite.com.br</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>346</v>
+        <v>488</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
         </is>
       </c>
     </row>
@@ -9325,20 +9360,20 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Diego Souza</t>
+          <t>Jonatan Dos Santos Gomes</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>diego.souza@xsite.com.br</t>
+          <t>jonatan.gomes@xsite.com.br</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>488</v>
+        <v>535</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
@@ -9353,12 +9388,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Emanuele Nobre</t>
+          <t>Leandro Assmar</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>emanuele.nobre@xsite.com.br</t>
+          <t>leandro.assmar@xsite.com.br</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -9381,12 +9416,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Emanuele Nobre</t>
+          <t>Leonardo Oliveira</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>emanuele.nobre@xsite.com.br</t>
+          <t>leonardo.oliveira@xsite.com.br</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -9409,20 +9444,20 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jonatan Dos Santos Gomes</t>
+          <t>Yueslly Lisboa</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>jonatan.gomes@xsite.com.br</t>
+          <t>yueslly.lisboa@xsite.com.br</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>346</v>
+        <v>303</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
@@ -9437,20 +9472,20 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Jonatan Dos Santos Gomes</t>
+          <t>Yueslly Lisboa</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>jonatan.gomes@xsite.com.br</t>
+          <t>yueslly.lisboa@xsite.com.br</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>488</v>
+        <v>333</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
@@ -9465,20 +9500,20 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Jonatan Dos Santos Gomes</t>
+          <t>Yueslly Lisboa</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>jonatan.gomes@xsite.com.br</t>
+          <t>yueslly.lisboa@xsite.com.br</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>535</v>
+        <v>346</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9528,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Leandro Assmar</t>
+          <t>Yueslly Lisboa</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>leandro.assmar@xsite.com.br</t>
+          <t>yueslly.lisboa@xsite.com.br</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -9521,160 +9556,160 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Leonardo Oliveira</t>
+          <t>Yuri Souza</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>leonardo.oliveira@xsite.com.br</t>
+          <t>yuri.souza@xsite.com.br</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>539</v>
+        <v>488</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tenable Cloud Security Specialist On-Demand</t>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>579399</v>
+        <v>397166</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>XSite</t>
+          <t>ISH Tecnologia SA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Yueslly Lisboa</t>
+          <t>Alexandre Pertel Gonçalves</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>yueslly.lisboa@xsite.com.br</t>
+          <t>alexandre.goncalves@ish.com.br</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>303</v>
+        <v>346</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>579399</v>
+        <v>397166</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>XSite</t>
+          <t>ISH Tecnologia SA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Yueslly Lisboa</t>
+          <t>Anderson Lemos</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>yueslly.lisboa@xsite.com.br</t>
+          <t>anderson.lemos@ish.com.br</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>333</v>
+        <v>303</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>579399</v>
+        <v>397166</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>XSite</t>
+          <t>ISH Tecnologia SA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Yueslly Lisboa</t>
+          <t>Anderson Lemos</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>yueslly.lisboa@xsite.com.br</t>
+          <t>anderson.lemos@ish.com.br</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>579399</v>
+        <v>397166</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>XSite</t>
+          <t>ISH Tecnologia SA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Yueslly Lisboa</t>
+          <t>Anderson Lemos</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>yueslly.lisboa@xsite.com.br</t>
+          <t>anderson.lemos@ish.com.br</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>488</v>
+        <v>539</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>579399</v>
+        <v>397166</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>XSite</t>
+          <t>ISH Tecnologia SA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Yuri Souza</t>
+          <t>Anderson Neiva</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>yuri.souza@xsite.com.br</t>
+          <t>anderson.neiva@ish.com.br</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>488</v>
+        <v>303</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
@@ -9689,20 +9724,20 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Alexandre Pertel Gonçalves</t>
+          <t>Claudio Neto</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>alexandre.goncalves@ish.com.br</t>
+          <t>claudio.neto@ish.com.br</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>346</v>
+        <v>535</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
@@ -9717,20 +9752,20 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Anderson Lemos</t>
+          <t>Claudio Neto</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>anderson.lemos@ish.com.br</t>
+          <t>claudio.neto@ish.com.br</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>303</v>
+        <v>539</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
         </is>
       </c>
     </row>
@@ -9745,20 +9780,20 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Anderson Lemos</t>
+          <t>Danilo De Santana Dantas</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>anderson.lemos@ish.com.br</t>
+          <t>danilo.dantas@ish.com.br</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>333</v>
+        <v>535</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
@@ -9773,20 +9808,20 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Anderson Lemos</t>
+          <t>Diego Costa</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>anderson.lemos@ish.com.br</t>
+          <t>diego.costa@ish.com.br</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>539</v>
+        <v>346</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tenable Cloud Security Specialist On-Demand</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -9801,20 +9836,20 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Anderson Neiva</t>
+          <t>Edson Júnior</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>anderson.neiva@ish.com.br</t>
+          <t>edson.junior@ish.com.br</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>303</v>
+        <v>539</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
         </is>
       </c>
     </row>
@@ -9829,20 +9864,20 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Claudio Neto</t>
+          <t>Edson Júnior</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>claudio.neto@ish.com.br</t>
+          <t>edson.junior@ish.com.br</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>535</v>
+        <v>552</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Exposure Management Business Theory</t>
         </is>
       </c>
     </row>
@@ -9857,20 +9892,20 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Claudio Neto</t>
+          <t>Eliabe Bento</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>claudio.neto@ish.com.br</t>
+          <t>eliabe.bento@ish.com.br</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>539</v>
+        <v>414</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tenable Cloud Security Specialist On-Demand</t>
+          <t>Introduction to Tenable Identity Exposure</t>
         </is>
       </c>
     </row>
@@ -9885,20 +9920,20 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Danilo De Santana Dantas</t>
+          <t>Felipe Santos da Silva</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>danilo.dantas@ish.com.br</t>
+          <t>felipe.ssilva@ish.com.br</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>535</v>
+        <v>483</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Tenable One Exposure Management Platform Introduction</t>
         </is>
       </c>
     </row>
@@ -9913,20 +9948,20 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Diego Costa</t>
+          <t>Felipus Gomes</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>diego.costa@ish.com.br</t>
+          <t>felipus.gomes@ish.com.br</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>346</v>
+        <v>303</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
@@ -9941,20 +9976,20 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Edson Junior</t>
+          <t>Felipus Gomes</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>edson.junior@ish.com.br</t>
+          <t>felipus.gomes@ish.com.br</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>539</v>
+        <v>333</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tenable Cloud Security Specialist On-Demand</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
@@ -9969,20 +10004,20 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Edson Junior</t>
+          <t>Felipus Gomes</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>edson.junior@ish.com.br</t>
+          <t>felipus.gomes@ish.com.br</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>552</v>
+        <v>346</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Exposure Management Business Theory</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -9997,20 +10032,20 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Eliabe Bento</t>
+          <t>Felipus Gomes</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>eliabe.bento@ish.com.br</t>
+          <t>felipus.gomes@ish.com.br</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>414</v>
+        <v>483</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Identity Exposure</t>
+          <t>Tenable One Exposure Management Platform Introduction</t>
         </is>
       </c>
     </row>
@@ -10025,12 +10060,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Felipe Santos da Silva</t>
+          <t>Gabriel Gattini</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>felipe.ssilva@ish.com.br</t>
+          <t>gabriel.gattini@ish.com.br</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -10053,12 +10088,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Felipus Gomes</t>
+          <t>Hecio Arruda</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>felipus.gomes@ish.com.br</t>
+          <t>hecio.arruda@ish.com.br</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -10081,12 +10116,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Felipus Gomes</t>
+          <t>Hecio Arruda</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>felipus.gomes@ish.com.br</t>
+          <t>hecio.arruda@ish.com.br</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -10109,12 +10144,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Felipus Gomes</t>
+          <t>Hecio Arruda</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>felipus.gomes@ish.com.br</t>
+          <t>hecio.arruda@ish.com.br</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -10137,20 +10172,20 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Felipus Gomes</t>
+          <t>Jacques Almeida</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>felipus.gomes@ish.com.br</t>
+          <t>jacques.almeida@ish.com.br</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>483</v>
+        <v>303</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tenable One Exposure Management Platform Introduction</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
@@ -10165,20 +10200,20 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Gabriel Gattini</t>
+          <t>Joelma Da Silva Batista</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>gabriel.gattini@ish.com.br</t>
+          <t>joelma.batista@ish.com.br</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>483</v>
+        <v>333</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tenable One Exposure Management Platform Introduction</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
@@ -10193,20 +10228,20 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hecio Arruda</t>
+          <t>Joelma Da Silva Batista</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>hecio.arruda@ish.com.br</t>
+          <t>joelma.batista@ish.com.br</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>303</v>
+        <v>346</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -10221,20 +10256,20 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hecio Arruda</t>
+          <t>Joelma Da Silva Batista</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>hecio.arruda@ish.com.br</t>
+          <t>joelma.batista@ish.com.br</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>333</v>
+        <v>488</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
         </is>
       </c>
     </row>
@@ -10249,12 +10284,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hecio Arruda</t>
+          <t>Jonas Nasser</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>hecio.arruda@ish.com.br</t>
+          <t>jonas.nasser@ish.com.br</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -10277,20 +10312,20 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Jacques Almeida</t>
+          <t>Kramer Saunders</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>jacques.almeida@ish.com.br</t>
+          <t>kramer.saunders@ish.com.br</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>303</v>
+        <v>346</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -10305,20 +10340,20 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Joelma Da Silva Batista</t>
+          <t>Lucas De Araujo Feitosa</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>joelma.batista@ish.com.br</t>
+          <t>lucas.feitosa@ish.com.br</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>333</v>
+        <v>535</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
@@ -10333,20 +10368,20 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Joelma Da Silva Batista</t>
+          <t>Lucas De Araujo Feitosa</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>joelma.batista@ish.com.br</t>
+          <t>lucas.feitosa@ish.com.br</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>346</v>
+        <v>539</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
         </is>
       </c>
     </row>
@@ -10361,20 +10396,20 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Joelma Da Silva Batista</t>
+          <t>Luiz Eduardo Eleuterio de Souza</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>joelma.batista@ish.com.br</t>
+          <t>luiz.eduardo@visioncybersecurity.com</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>488</v>
+        <v>303</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
@@ -10389,20 +10424,20 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Jonas Nasser</t>
+          <t>Luiz Eduardo Eleuterio de Souza</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>jonas.nasser@ish.com.br</t>
+          <t>luiz.eduardo@visioncybersecurity.com</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
@@ -10417,12 +10452,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Kramer Saunders</t>
+          <t>Luiz Eduardo Eleuterio de Souza</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>kramer.saunders@ish.com.br</t>
+          <t>luiz.eduardo@visioncybersecurity.com</t>
         </is>
       </c>
       <c r="E99" t="n">
@@ -10445,12 +10480,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Lucas De Araujo Feitosa</t>
+          <t>Luiz Eduardo Eleuterio de Souza</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>lucas.feitosa@ish.com.br</t>
+          <t>luiz.eduardo@visioncybersecurity.com</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -10473,20 +10508,20 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Lucas De Araujo Feitosa</t>
+          <t>Luiz Eduardo Eleuterio de Souza</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>lucas.feitosa@ish.com.br</t>
+          <t>luiz.eduardo@visioncybersecurity.com</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>539</v>
+        <v>552</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tenable Cloud Security Specialist On-Demand</t>
+          <t>Exposure Management Business Theory</t>
         </is>
       </c>
     </row>
@@ -10501,20 +10536,20 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Marcelo Mantovani</t>
+          <t>Luiz Gustavo Batista Bugiga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>marcelo.mantovani@ish.com.br</t>
+          <t>luiz.bugiga@visioncybersecurity.com</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>346</v>
+        <v>303</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
@@ -10529,20 +10564,20 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Marcelo Martins</t>
+          <t>Marcelo Mantovani</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>marcelo.martins@ish.com.br</t>
+          <t>marcelo.mantovani@ish.com.br</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -10566,11 +10601,11 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>539</v>
+        <v>333</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tenable Cloud Security Specialist On-Demand</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
@@ -10585,12 +10620,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Marcio Mendes</t>
+          <t>Marcelo Martins</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>marcio.mendes@ish.com.br</t>
+          <t>marcelo.martins@ish.com.br</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -10613,20 +10648,20 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Mateus Mantovani</t>
+          <t>Marcio Mendes</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>mateus.mantovani@ish.com.br</t>
+          <t>marcio.mendes@ish.com.br</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>333</v>
+        <v>539</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
         </is>
       </c>
     </row>
@@ -10641,20 +10676,20 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Matheus Manea</t>
+          <t>Mateus Mantovani</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>matheus.manea@ish.com.br</t>
+          <t>mateus.mantovani@ish.com.br</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
@@ -10669,20 +10704,20 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Raouf Ahmadian Yazdi</t>
+          <t>Matheus Manea</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>raouf.yazdi@ish.com.br</t>
+          <t>matheus.manea@ish.com.br</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -11182,11 +11217,11 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>488</v>
+        <v>539</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
         </is>
       </c>
     </row>
@@ -11201,68 +11236,68 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Victor Silva</t>
+          <t>Wagner De Jesus Belo Meireles</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>victor.araujo@ish.com.br</t>
+          <t>wagner.meireles@ish.com.br</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>539</v>
+        <v>346</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tenable Cloud Security Specialist On-Demand</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>397166</v>
+        <v>993857</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ISH Tecnologia SA</t>
+          <t>GLOBAL SEC. TECNOLOGIA &amp; INFORMACAO EIRELI</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Wagner De Jesus Belo Meireles</t>
+          <t>Lucas Vasconcelos</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>wagner.meireles@ish.com.br</t>
+          <t>lucas.vasconcelos@globalsectecnologia.com.br</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>346</v>
+        <v>303</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>993857</v>
+        <v>510201</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>GLOBAL SEC. TECNOLOGIA &amp; INFORMACAO EIRELI</t>
+          <t>Netsecurity Tecnologia LTDA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Lucas Vasconcelos</t>
+          <t>ALESSANDRO VIEIRA</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>lucas.vasconcelos@globalsectecnologia.com.br</t>
+          <t>alessandro.vitalino@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -11294,11 +11329,11 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>303</v>
+        <v>333</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
@@ -11322,11 +11357,11 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -11350,11 +11385,11 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>346</v>
+        <v>414</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable Identity Exposure</t>
         </is>
       </c>
     </row>
@@ -11378,11 +11413,11 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>414</v>
+        <v>535</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Identity Exposure</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
@@ -11406,11 +11441,11 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>535</v>
+        <v>552</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Exposure Management Business Theory</t>
         </is>
       </c>
     </row>
@@ -11425,20 +11460,20 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>ALESSANDRO VIEIRA</t>
+          <t>André Feltrin</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>alessandro.vitalino@netsecurity.com.br</t>
+          <t>andre.feltrin@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>552</v>
+        <v>414</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Exposure Management Business Theory</t>
+          <t>Introduction to Tenable Identity Exposure</t>
         </is>
       </c>
     </row>
@@ -11462,11 +11497,11 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>414</v>
+        <v>483</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Identity Exposure</t>
+          <t>Tenable One Exposure Management Platform Introduction</t>
         </is>
       </c>
     </row>
@@ -11490,11 +11525,11 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>483</v>
+        <v>535</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tenable One Exposure Management Platform Introduction</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
@@ -11518,11 +11553,11 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>535</v>
+        <v>552</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Exposure Management Business Theory</t>
         </is>
       </c>
     </row>
@@ -11537,20 +11572,20 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>André Feltrin</t>
+          <t>Bruno Leite</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>andre.feltrin@netsecurity.com.br</t>
+          <t>bruno.leite@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>552</v>
+        <v>375</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Exposure Management Business Theory</t>
+          <t>Tenable Vulnerability Management Specialist</t>
         </is>
       </c>
     </row>
@@ -11574,11 +11609,11 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>375</v>
+        <v>488</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tenable Vulnerability Management Specialist</t>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
         </is>
       </c>
     </row>
@@ -11593,20 +11628,20 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bruno Leite</t>
+          <t>Gutenberg Brito</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>bruno.leite@netsecurity.com.br</t>
+          <t>gutenberg.brito@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>488</v>
+        <v>303</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
@@ -11630,11 +11665,11 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>303</v>
+        <v>333</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
@@ -11658,11 +11693,11 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -11686,11 +11721,11 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>346</v>
+        <v>535</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
@@ -11714,11 +11749,11 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>535</v>
+        <v>552</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Exposure Management Business Theory</t>
         </is>
       </c>
     </row>
@@ -11733,20 +11768,20 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Leonardo Silva</t>
+          <t>Gutenberg Brito</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>leonardo.silva@netsecurity.com.br</t>
+          <t>gutenberg.brito@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>333</v>
+        <v>561</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Tenable One Exposure Management Platform Specialist On-Demand</t>
         </is>
       </c>
     </row>
@@ -11770,11 +11805,11 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
@@ -11798,11 +11833,11 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>414</v>
+        <v>346</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Identity Exposure</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -11826,11 +11861,11 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>535</v>
+        <v>414</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Introduction to Tenable Identity Exposure</t>
         </is>
       </c>
     </row>
@@ -11845,20 +11880,20 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Mar�lia Cardoso</t>
+          <t>Leonardo Silva</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>marilia.cardoso@netsecurity.com.br</t>
+          <t>leonardo.silva@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>346</v>
+        <v>535</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
@@ -11873,20 +11908,20 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Thiago Ribeiro</t>
+          <t>Mar�lia Cardoso</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>thiago.ribeiro@netsecurity.com.br</t>
+          <t>marilia.cardoso@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>375</v>
+        <v>346</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tenable Vulnerability Management Specialist</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -11901,40 +11936,40 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Willian Santos Arruda</t>
+          <t>Thiago Ribeiro</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>willian.arruda@netsecurity.com.br</t>
+          <t>thiago.ribeiro@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>535</v>
+        <v>375</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Tenable Vulnerability Management Specialist</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>458265</v>
+        <v>510201</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Future Technologies Informatica Ltda</t>
+          <t>Netsecurity Tecnologia LTDA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Leonardo Figueira</t>
+          <t>Willian Santos Arruda</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>leonardo.figueira@future.com.br</t>
+          <t>willian.arruda@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E153" t="n">
@@ -11948,21 +11983,21 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>458265</v>
+        <v>510201</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Future Technologies Informatica Ltda</t>
+          <t>Netsecurity Tecnologia LTDA</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Leonardo Figueira</t>
+          <t>Willian Santos Arruda</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>leonardo.figueira@future.com.br</t>
+          <t>willian.arruda@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E154" t="n">
@@ -11976,21 +12011,21 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>458265</v>
+        <v>510201</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Future Technologies Informatica Ltda</t>
+          <t>Netsecurity Tecnologia LTDA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Matheus Zaparolli</t>
+          <t>Willian Santos Arruda</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>matheus.zaparolli@future.com.br</t>
+          <t>willian.arruda@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E155" t="n">
@@ -12004,85 +12039,85 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>458265</v>
+        <v>510201</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Future Technologies Informatica Ltda</t>
+          <t>Netsecurity Tecnologia LTDA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Odimar Junior</t>
+          <t>Willian Santos Arruda</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>odimar.junior@future.com.br</t>
+          <t>willian.arruda@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>333</v>
+        <v>483</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Tenable One Exposure Management Platform Introduction</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>458265</v>
+        <v>510201</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Future Technologies Informatica Ltda</t>
+          <t>Netsecurity Tecnologia LTDA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Odimar Junior</t>
+          <t>Willian Santos Arruda</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>odimar.junior@future.com.br</t>
+          <t>willian.arruda@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>346</v>
+        <v>535</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>458265</v>
+        <v>510201</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Future Technologies Informatica Ltda</t>
+          <t>Netsecurity Tecnologia LTDA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Pablo Silva</t>
+          <t>Willian Santos Arruda</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>pablo.silva@future.com.br</t>
+          <t>willian.arruda@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>488</v>
+        <v>552</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+          <t>Exposure Management Business Theory</t>
         </is>
       </c>
     </row>
@@ -12097,68 +12132,68 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Thaciany Silva</t>
+          <t>Leonardo Figueira</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>thaciany.silva@future.com.br</t>
+          <t>leonardo.figueira@future.com.br</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>346</v>
+        <v>303</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>119472</v>
+        <v>458265</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ACCENTURE DO BRASIL LTDA</t>
+          <t>Future Technologies Informatica Ltda</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Carlos Araújo</t>
+          <t>Leonardo Figueira</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>carlos.h.araujo@accenture.com</t>
+          <t>leonardo.figueira@future.com.br</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>552</v>
+        <v>333</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Exposure Management Business Theory</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>119472</v>
+        <v>458265</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ACCENTURE DO BRASIL LTDA</t>
+          <t>Future Technologies Informatica Ltda</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Felipe Guerreiro do Prado</t>
+          <t>Matheus Zaparolli</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>f.guerreiro.do.prado@accenture.com</t>
+          <t>matheus.zaparolli@future.com.br</t>
         </is>
       </c>
       <c r="E161" t="n">
@@ -12172,133 +12207,133 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>119472</v>
+        <v>458265</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ACCENTURE DO BRASIL LTDA</t>
+          <t>Future Technologies Informatica Ltda</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Herbert Barros</t>
+          <t>Odimar Junior</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>herbert.b.rocha@accenture.com</t>
+          <t>odimar.junior@future.com.br</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>303</v>
+        <v>333</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>119472</v>
+        <v>458265</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ACCENTURE DO BRASIL LTDA</t>
+          <t>Future Technologies Informatica Ltda</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Herbert Barros</t>
+          <t>Odimar Junior</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>herbert.b.rocha@accenture.com</t>
+          <t>odimar.junior@future.com.br</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>488</v>
+        <v>346</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119472</v>
+        <v>458265</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ACCENTURE DO BRASIL LTDA</t>
+          <t>Future Technologies Informatica Ltda</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Moisés Dantas Felix</t>
+          <t>Thaciany Silva</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>moises.d.felix@accenture.com</t>
+          <t>thaciany.silva@future.com.br</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>535</v>
+        <v>346</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>106294</v>
+        <v>119472</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Under Protection Consultoria em Informatica LTDA</t>
+          <t>ACCENTURE DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Andrey Melo</t>
+          <t>Carlos Araújo</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>andrey.melo@underprotection.com.br</t>
+          <t>carlos.h.araujo@accenture.com</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>333</v>
+        <v>552</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Exposure Management Business Theory</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>106294</v>
+        <v>119472</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Under Protection Consultoria em Informatica LTDA</t>
+          <t>ACCENTURE DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Andrey Melo</t>
+          <t>Felipe Guerreiro do Prado</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>andrey.melo@underprotection.com.br</t>
+          <t>f.guerreiro.do.prado@accenture.com</t>
         </is>
       </c>
       <c r="E166" t="n">
@@ -12312,49 +12347,49 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>106294</v>
+        <v>119472</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Under Protection Consultoria em Informatica LTDA</t>
+          <t>ACCENTURE DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Jefferson Abbin</t>
+          <t>Luis Fernandes</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>jefferson.abbin@underprotection.com.br</t>
+          <t>luis.ant.fernandes@accenture.com</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>535</v>
+        <v>346</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>106294</v>
+        <v>119472</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Under Protection Consultoria em Informatica LTDA</t>
+          <t>ACCENTURE DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Jefferson Abbin</t>
+          <t>Luis Fernandes</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>jefferson.abbin@underprotection.com.br</t>
+          <t>luis.ant.fernandes@accenture.com</t>
         </is>
       </c>
       <c r="E168" t="n">
@@ -12368,29 +12403,29 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>106294</v>
+        <v>119472</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Under Protection Consultoria em Informatica LTDA</t>
+          <t>ACCENTURE DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Julia Johnson</t>
+          <t>Moisés Dantas Felix</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>julia.melo@underprotection.com.br</t>
+          <t>moises.d.felix@accenture.com</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>414</v>
+        <v>535</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Identity Exposure</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
@@ -12405,20 +12440,20 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Marco Antonio Leissmann</t>
+          <t>Andrey Melo</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>marco.leissmann@underprotection.com.br</t>
+          <t>andrey.melo@underprotection.com.br</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>303</v>
+        <v>333</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
@@ -12433,20 +12468,20 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Marco Antonio Leissmann</t>
+          <t>Andrey Melo</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>marco.leissmann@underprotection.com.br</t>
+          <t>andrey.melo@underprotection.com.br</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -12461,20 +12496,20 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Marco Antonio Leissmann</t>
+          <t>Jefferson Abbin</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>marco.leissmann@underprotection.com.br</t>
+          <t>jefferson.abbin@underprotection.com.br</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>346</v>
+        <v>303</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
@@ -12489,20 +12524,20 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Marco Antonio Leissmann</t>
+          <t>Jefferson Abbin</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>marco.leissmann@underprotection.com.br</t>
+          <t>jefferson.abbin@underprotection.com.br</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>414</v>
+        <v>333</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Identity Exposure</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
@@ -12517,20 +12552,20 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Marco Antonio Leissmann</t>
+          <t>Jefferson Abbin</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>marco.leissmann@underprotection.com.br</t>
+          <t>jefferson.abbin@underprotection.com.br</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>483</v>
+        <v>346</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tenable One Exposure Management Platform Introduction</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -12545,20 +12580,20 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Marco Antonio Leissmann</t>
+          <t>Jefferson Abbin</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>marco.leissmann@underprotection.com.br</t>
+          <t>jefferson.abbin@underprotection.com.br</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>535</v>
+        <v>483</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Tenable One Exposure Management Platform Introduction</t>
         </is>
       </c>
     </row>
@@ -12573,20 +12608,20 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Marco Antonio Leissmann</t>
+          <t>Jefferson Abbin</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>marco.leissmann@underprotection.com.br</t>
+          <t>jefferson.abbin@underprotection.com.br</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>552</v>
+        <v>535</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Exposure Management Business Theory</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
@@ -12601,20 +12636,20 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Ney Gelbcke Junior</t>
+          <t>Jefferson Abbin</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>ney.gelbcke@underprotection.com.br</t>
+          <t>jefferson.abbin@underprotection.com.br</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>346</v>
+        <v>552</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Exposure Management Business Theory</t>
         </is>
       </c>
     </row>
@@ -12629,96 +12664,96 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Ney Gelbcke Junior</t>
+          <t>Julia Johnson</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>ney.gelbcke@underprotection.com.br</t>
+          <t>julia.melo@underprotection.com.br</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>552</v>
+        <v>414</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Exposure Management Business Theory</t>
+          <t>Introduction to Tenable Identity Exposure</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>543439</v>
+        <v>106294</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Kryptus Seguranca da Informacao SA</t>
+          <t>Under Protection Consultoria em Informatica LTDA</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Paulo Rigonato</t>
+          <t>Marco Antonio Leissmann</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>paulo.monteiro@kryptus.com</t>
+          <t>marco.leissmann@underprotection.com.br</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>346</v>
+        <v>303</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>543439</v>
+        <v>106294</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Kryptus Seguranca da Informacao SA</t>
+          <t>Under Protection Consultoria em Informatica LTDA</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Paulo Rigonato</t>
+          <t>Marco Antonio Leissmann</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>paulo.monteiro@kryptus.com</t>
+          <t>marco.leissmann@underprotection.com.br</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>535</v>
+        <v>333</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>543439</v>
+        <v>106294</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Kryptus Seguranca da Informacao SA</t>
+          <t>Under Protection Consultoria em Informatica LTDA</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Sabino Lima</t>
+          <t>Marco Antonio Leissmann</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>sabino.lima@kryptus.com</t>
+          <t>marco.leissmann@underprotection.com.br</t>
         </is>
       </c>
       <c r="E181" t="n">
@@ -12732,453 +12767,441 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>543439</v>
+        <v>106294</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Kryptus Seguranca da Informacao SA</t>
+          <t>Under Protection Consultoria em Informatica LTDA</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Sabino Lima</t>
+          <t>Marco Antonio Leissmann</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>sabino.lima@kryptus.com</t>
+          <t>marco.leissmann@underprotection.com.br</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>488</v>
+        <v>414</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+          <t>Introduction to Tenable Identity Exposure</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>686107</v>
+        <v>106294</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>e-Safer</t>
+          <t>Under Protection Consultoria em Informatica LTDA</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Adenilson Alves da Silva</t>
+          <t>Marco Antonio Leissmann</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>asilva@e-safer.com.br</t>
+          <t>marco.leissmann@underprotection.com.br</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>303</v>
+        <v>483</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Tenable One Exposure Management Platform Introduction</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>686107</v>
+        <v>106294</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>e-Safer</t>
+          <t>Under Protection Consultoria em Informatica LTDA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Ana Clara Ferreira</t>
+          <t>Marco Antonio Leissmann</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>asantos@e-safer.com.br</t>
+          <t>marco.leissmann@underprotection.com.br</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>346</v>
+        <v>535</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>686107</v>
+        <v>106294</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>e-Safer</t>
+          <t>Under Protection Consultoria em Informatica LTDA</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Arlem Barros</t>
+          <t>Marco Antonio Leissmann</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>abarros@e-safer.com.br</t>
+          <t>marco.leissmann@underprotection.com.br</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>303</v>
+        <v>552</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Exposure Management Business Theory</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>686107</v>
+        <v>106294</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>e-Safer</t>
+          <t>Under Protection Consultoria em Informatica LTDA</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Bruno Magalhaes</t>
+          <t>Ney Gelbcke Junior</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>bmagalhaes@e-safer.com.br</t>
+          <t>ney.gelbcke@underprotection.com.br</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>303</v>
+        <v>552</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Exposure Management Business Theory</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>686107</v>
+        <v>543439</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>e-Safer</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Bruno Magalhaes</t>
+          <t>João Bessa</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>bmagalhaes@e-safer.com.br</t>
+          <t>joao.bessa@kryptus.com</t>
         </is>
       </c>
       <c r="E187" t="n">
+        <v>333</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Security Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>543439</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Kryptus Seguranca da Informacao SA</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>João Bessa</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>joao.bessa@kryptus.com</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>346</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>543439</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Kryptus Seguranca da Informacao SA</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>João Bessa</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>joao.bessa@kryptus.com</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
         <v>535</v>
       </c>
-      <c r="F187" t="inlineStr">
+      <c r="F189" t="inlineStr">
         <is>
           <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>001f200001xtmLIAAY</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Servix Informática Ltda</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Evandro Lima</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>evandro.lima@servix.com</t>
-        </is>
-      </c>
-      <c r="E188" t="n">
-        <v>375</v>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>Tenable Vulnerability Management Specialist</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>001f200001xtmLIAAY</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Servix Informática Ltda</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Evandro Lima</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>evandro.lima@servix.com</t>
-        </is>
-      </c>
-      <c r="E189" t="n">
-        <v>539</v>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>Tenable Cloud Security Specialist On-Demand</t>
-        </is>
-      </c>
-    </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>001f200001xtmLIAAY</t>
-        </is>
+      <c r="A190" t="n">
+        <v>543439</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Servix Informática Ltda</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Filipe Augusto</t>
+          <t>João Bessa</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>filipe.silva@servix.com</t>
+          <t>joao.bessa@kryptus.com</t>
         </is>
       </c>
       <c r="E190" t="n">
+        <v>552</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Exposure Management Business Theory</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>543439</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Kryptus Seguranca da Informacao SA</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Leonardo Alarcon</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>leonardo.alarcon@kryptus.com</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>483</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Tenable One Exposure Management Platform Introduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>543439</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Kryptus Seguranca da Informacao SA</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Lucas Carvalho</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>lucas.carvalho@kryptus.com</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
         <v>346</v>
       </c>
-      <c r="F190" t="inlineStr">
+      <c r="F192" t="inlineStr">
         <is>
           <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>001f200001xtmLIAAY</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Servix Informática Ltda</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>João Ferreira</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>joao.ferreira@servix.com</t>
-        </is>
-      </c>
-      <c r="E191" t="n">
-        <v>488</v>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>Tenable Vulnerability Management Specialist On-Demand</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>001f200001xtmLIAAY</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Servix Informática Ltda</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>João Ferreira</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>joao.ferreira@servix.com</t>
-        </is>
-      </c>
-      <c r="E192" t="n">
-        <v>539</v>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>Tenable Cloud Security Specialist On-Demand</t>
-        </is>
-      </c>
-    </row>
     <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>001f200001xtmLIAAY</t>
-        </is>
+      <c r="A193" t="n">
+        <v>543439</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Servix Informática Ltda</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Matheus Passos</t>
+          <t>Paulo Rigonato</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>matheus.passos@servix.com</t>
+          <t>paulo.monteiro@kryptus.com</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>644733</v>
+        <v>543439</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Ana Loucenco</t>
+          <t>Paulo Rigonato</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>ana.lourenco@itprotect.com.br</t>
+          <t>paulo.monteiro@kryptus.com</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>333</v>
+        <v>535</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>644733</v>
+        <v>543439</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Ana Loucenco</t>
+          <t>Rogerio Araujo</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>ana.lourenco@itprotect.com.br</t>
+          <t>rogerio.araujo@kryptus.com</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>644733</v>
+        <v>543439</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Ana Loucenco</t>
+          <t>Rogerio Araujo</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>ana.lourenco@itprotect.com.br</t>
+          <t>rogerio.araujo@kryptus.com</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>483</v>
+        <v>346</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Tenable One Exposure Management Platform Introduction</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>644733</v>
+        <v>543439</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Ana Loucenco</t>
+          <t>Rogerio Araujo</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>ana.lourenco@itprotect.com.br</t>
+          <t>rogerio.araujo@kryptus.com</t>
         </is>
       </c>
       <c r="E197" t="n">
@@ -13192,161 +13215,161 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>644733</v>
+        <v>543439</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>FLAVIO BARBOSA</t>
+          <t>Rogerio Araujo</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>flavio.barbosa@itprotect.com.br</t>
+          <t>rogerio.araujo@kryptus.com</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>346</v>
+        <v>552</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Exposure Management Business Theory</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>644733</v>
+        <v>543439</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Paulo Medeiros</t>
+          <t>Rogerio Araujo</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>paulo.medeiros@itprotect.com.br</t>
+          <t>rogerio.araujo@kryptus.com</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>375</v>
+        <v>561</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Tenable Vulnerability Management Specialist</t>
+          <t>Tenable One Exposure Management Platform Specialist On-Demand</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>644733</v>
+        <v>543439</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Paulo Medeiros</t>
+          <t>Sabino Lima</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>paulo.medeiros@itprotect.com.br</t>
+          <t>sabino.lima@kryptus.com</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>539</v>
+        <v>333</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Tenable Cloud Security Specialist On-Demand</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>644733</v>
+        <v>543439</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Pedro Comin</t>
+          <t>Sabino Lima</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>pedro.comin@itprotect.com.br</t>
+          <t>sabino.lima@kryptus.com</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>303</v>
+        <v>346</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>644733</v>
+        <v>543439</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Pedro Comin</t>
+          <t>Sabino Lima</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>pedro.comin@itprotect.com.br</t>
+          <t>sabino.lima@kryptus.com</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>346</v>
+        <v>483</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Tenable One Exposure Management Platform Introduction</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>644733</v>
+        <v>543439</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Pedro Comin</t>
+          <t>Sabino Lima</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>pedro.comin@itprotect.com.br</t>
+          <t>sabino.lima@kryptus.com</t>
         </is>
       </c>
       <c r="E203" t="n">
@@ -13360,195 +13383,907 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>644733</v>
+        <v>543439</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Ricardo Claus</t>
+          <t>Sabino Lima</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>ricardo.claus@itprotect.com.br</t>
+          <t>sabino.lima@kryptus.com</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>346</v>
+        <v>535</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>644733</v>
+        <v>543439</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Ricardo Claus</t>
+          <t>Sabino Lima</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>ricardo.claus@itprotect.com.br</t>
+          <t>sabino.lima@kryptus.com</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>414</v>
+        <v>552</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Identity Exposure</t>
+          <t>Exposure Management Business Theory</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>644733</v>
+        <v>543439</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Ricardo Claus</t>
+          <t>Sabino Lima</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>ricardo.claus@itprotect.com.br</t>
+          <t>sabino.lima@kryptus.com</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>483</v>
+        <v>561</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Tenable One Exposure Management Platform Introduction</t>
+          <t>Tenable One Exposure Management Platform Specialist On-Demand</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>644733</v>
+        <v>686107</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>e-Safer</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Ricardo Claus</t>
+          <t>Adenilson Alves da Silva</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>ricardo.claus@itprotect.com.br</t>
+          <t>asilva@e-safer.com.br</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>535</v>
+        <v>303</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>644733</v>
+        <v>686107</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>e-Safer</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Sávio Alves</t>
+          <t>Ana Clara Ferreira</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>savio.alves@itprotect.com.br</t>
+          <t>asantos@e-safer.com.br</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>304</v>
+        <v>346</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Tenable Security Center Specialist</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>644733</v>
+        <v>686107</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>e-Safer</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Thiago Borges</t>
+          <t>Ana Clara Ferreira</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>thiago.borges@itprotect.com.br</t>
+          <t>asantos@e-safer.com.br</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>346</v>
+        <v>483</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Tenable One Exposure Management Platform Introduction</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
+        <v>686107</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>e-Safer</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Arlem Barros</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>abarros@e-safer.com.br</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>303</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>686107</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>e-Safer</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Bruno Magalhaes</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>bmagalhaes@e-safer.com.br</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>303</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>686107</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>e-Safer</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Bruno Magalhaes</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>bmagalhaes@e-safer.com.br</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>535</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Cloud Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>001f200001xtmLIAAY</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Servix Informática Ltda</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Evandro Lima</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>evandro.lima@servix.com</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>375</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>001f200001xtmLIAAY</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Servix Informática Ltda</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Evandro Lima</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>evandro.lima@servix.com</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>539</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>001f200001xtmLIAAY</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Servix Informática Ltda</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Filipe Augusto</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>filipe.silva@servix.com</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>346</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>001f200001xtmLIAAY</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Servix Informática Ltda</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>João Ferreira</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>joao.ferreira@servix.com</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>488</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>001f200001xtmLIAAY</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Servix Informática Ltda</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>João Ferreira</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>joao.ferreira@servix.com</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>539</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>001f200001xtmLIAAY</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Servix Informática Ltda</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Matheus Passos</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>matheus.passos@servix.com</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>333</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Security Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
         <v>644733</v>
       </c>
-      <c r="B210" t="inlineStr">
+      <c r="B219" t="inlineStr">
         <is>
           <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Wilmar Navarro da Silva Neto</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Ana Loucenco</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>ana.lourenco@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>333</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Security Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Ana Loucenco</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>ana.lourenco@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>346</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Ana Loucenco</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>ana.lourenco@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>483</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Tenable One Exposure Management Platform Introduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Ana Loucenco</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>ana.lourenco@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>535</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Cloud Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>FLAVIO BARBOSA</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>flavio.barbosa@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>346</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Paul M</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>paulo.medeiros@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>375</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Paul M</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>paulo.medeiros@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>539</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Pedro Comin</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>pedro.comin@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>303</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Pedro Comin</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>pedro.comin@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>346</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Pedro Comin</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>pedro.comin@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>488</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Ricardo Claus</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>ricardo.claus@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>346</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Ricardo Claus</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>ricardo.claus@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>414</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Identity Exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Ricardo Claus</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>ricardo.claus@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>483</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Tenable One Exposure Management Platform Introduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Ricardo Claus</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>ricardo.claus@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>535</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Cloud Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Sávio Alves</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>savio.alves@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>304</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Tenable Security Center Specialist</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Thiago Borges</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>thiago.borges@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>346</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Wilmar Neto</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
         <is>
           <t>wilmar.neto@itprotect.com.br</t>
         </is>
       </c>
-      <c r="E210" t="n">
+      <c r="E235" t="n">
         <v>375</v>
       </c>
-      <c r="F210" t="inlineStr">
+      <c r="F235" t="inlineStr">
         <is>
           <t>Tenable Vulnerability Management Specialist</t>
         </is>

--- a/data/partner/Focus Partner Tracking BR.xlsx
+++ b/data/partner/Focus Partner Tracking BR.xlsx
@@ -7143,46 +7143,40 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E4" t="n">
-        <v>6</v>
-      </c>
-      <c r="F4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>3</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
         <v>5</v>
       </c>
-      <c r="I4" t="n">
+      <c r="O4" t="n">
         <v>5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>10</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" t="n">
-        <v>3</v>
-      </c>
-      <c r="N4" t="n">
-        <v>7</v>
-      </c>
-      <c r="O4" t="n">
-        <v>7</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -7637,46 +7631,46 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E16" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F16" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G16" t="n">
+        <v>21</v>
+      </c>
+      <c r="H16" t="n">
+        <v>45</v>
+      </c>
+      <c r="I16" t="n">
+        <v>26</v>
+      </c>
+      <c r="J16" t="n">
+        <v>74</v>
+      </c>
+      <c r="K16" t="n">
+        <v>24</v>
+      </c>
+      <c r="L16" t="n">
+        <v>41</v>
+      </c>
+      <c r="M16" t="n">
+        <v>53</v>
+      </c>
+      <c r="N16" t="n">
+        <v>66</v>
+      </c>
+      <c r="O16" t="n">
+        <v>159</v>
+      </c>
+      <c r="P16" t="n">
         <v>20</v>
-      </c>
-      <c r="H16" t="n">
-        <v>44</v>
-      </c>
-      <c r="I16" t="n">
-        <v>25</v>
-      </c>
-      <c r="J16" t="n">
-        <v>73</v>
-      </c>
-      <c r="K16" t="n">
-        <v>23</v>
-      </c>
-      <c r="L16" t="n">
-        <v>40</v>
-      </c>
-      <c r="M16" t="n">
-        <v>52</v>
-      </c>
-      <c r="N16" t="n">
-        <v>65</v>
-      </c>
-      <c r="O16" t="n">
-        <v>158</v>
-      </c>
-      <c r="P16" t="n">
-        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/data/partner/Focus Partner Tracking BR.xlsx
+++ b/data/partner/Focus Partner Tracking BR.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16960" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="BR" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Guardian" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Tech Certs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="EM Certs Detail" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BR" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guardian" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tech Certs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EM Certs Detail" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BR'!$A$3:$F$19</definedName>
@@ -1561,7 +1561,11 @@
         </is>
       </c>
       <c r="Q8" s="23" t="n"/>
-      <c r="R8" s="23" t="n"/>
+      <c r="R8" s="23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="S8" s="23" t="n"/>
       <c r="T8" s="23" t="inlineStr">
         <is>
@@ -7042,46 +7046,46 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
         <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
         <v>7</v>
       </c>
       <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="n">
         <v>7</v>
       </c>
-      <c r="J2" t="n">
-        <v>8</v>
-      </c>
       <c r="K2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M2" t="n">
         <v>7</v>
       </c>
-      <c r="L2" t="n">
-        <v>6</v>
-      </c>
-      <c r="M2" t="n">
-        <v>10</v>
-      </c>
       <c r="N2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O2" t="n">
         <v>9</v>
       </c>
       <c r="P2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -7094,10 +7098,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -7143,40 +7147,46 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
         <v>4</v>
       </c>
       <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
         <v>4</v>
       </c>
-      <c r="F4" t="n">
+      <c r="I4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
         <v>2</v>
       </c>
-      <c r="G4" t="n">
+      <c r="M4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" t="n">
         <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O4" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -7244,7 +7254,7 @@
         <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
         <v>4</v>
@@ -7253,10 +7263,10 @@
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
         <v>4</v>
@@ -7416,7 +7426,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
         <v>5</v>
@@ -7490,10 +7500,10 @@
         <v>1</v>
       </c>
       <c r="O12" t="n">
+        <v>5</v>
+      </c>
+      <c r="P12" t="n">
         <v>4</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -7631,46 +7641,46 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E16" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F16" t="n">
         <v>32</v>
       </c>
       <c r="G16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H16" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I16" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J16" t="n">
         <v>74</v>
       </c>
       <c r="K16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M16" t="n">
         <v>53</v>
       </c>
       <c r="N16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O16" t="n">
         <v>159</v>
       </c>
       <c r="P16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -7684,7 +7694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F235"/>
+  <dimension ref="A1:F254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8290,20 +8300,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ronilson Toledo Santos Machado</t>
+          <t>Lucas Henrique</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ronilson.machado@shieldsec.com.br</t>
+          <t>lucas.damasceno@shieldsec.com.br</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>303</v>
+        <v>561</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Tenable One Exposure Management Platform Specialist On-Demand</t>
         </is>
       </c>
     </row>
@@ -8327,11 +8337,11 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>346</v>
+        <v>303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
@@ -8355,11 +8365,11 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>535</v>
+        <v>346</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -8383,11 +8393,11 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>552</v>
+        <v>535</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Exposure Management Business Theory</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
@@ -8402,20 +8412,20 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tamiris Silva</t>
+          <t>Ronilson Toledo Santos Machado</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>tamiris.silva@shieldsec.com.br</t>
+          <t>ronilson.machado@shieldsec.com.br</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>303</v>
+        <v>552</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Exposure Management Business Theory</t>
         </is>
       </c>
     </row>
@@ -8439,11 +8449,11 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>333</v>
+        <v>303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
@@ -8467,11 +8477,11 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
@@ -8495,11 +8505,11 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>535</v>
+        <v>346</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -8523,11 +8533,11 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>552</v>
+        <v>535</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Exposure Management Business Theory</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
@@ -8542,12 +8552,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Thainá Goes</t>
+          <t>Tamiris Silva</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>thaina.goes@shieldsec.com.br</t>
+          <t>tamiris.silva@shieldsec.com.br</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -8570,20 +8580,20 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Wander Marcio do Reis</t>
+          <t>Thainá Goes</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>wander.reis@shieldsec.com.br</t>
+          <t>thaina.goes@shieldsec.com.br</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>303</v>
+        <v>552</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Exposure Management Business Theory</t>
         </is>
       </c>
     </row>
@@ -8607,11 +8617,11 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>333</v>
+        <v>303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
@@ -8635,11 +8645,11 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
@@ -8663,11 +8673,11 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>414</v>
+        <v>346</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Identity Exposure</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -8691,11 +8701,11 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>488</v>
+        <v>414</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+          <t>Introduction to Tenable Identity Exposure</t>
         </is>
       </c>
     </row>
@@ -8719,11 +8729,11 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>535</v>
+        <v>488</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
         </is>
       </c>
     </row>
@@ -8747,11 +8757,11 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>552</v>
+        <v>535</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Exposure Management Business Theory</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
@@ -8775,39 +8785,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tenable One Exposure Management Platform Specialist On-Demand</t>
+          <t>Exposure Management Business Theory</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>390733</v>
+        <v>581437</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TDec Redes de Computadores Ltda</t>
+          <t>SHIELD SECURITY TECNOLOGIA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Raúl Carbonari</t>
+          <t>Wander Marcio do Reis</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>rcarbonari@tdec.com.br</t>
+          <t>wander.reis@shieldsec.com.br</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>303</v>
+        <v>561</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Tenable One Exposure Management Platform Specialist On-Demand</t>
         </is>
       </c>
     </row>
@@ -8822,124 +8832,124 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Raúl Carbonari</t>
+          <t>OMAR CAVALCANTE</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>rcarbonari@tdec.com.br</t>
+          <t>ocavalcante@tdec.com.br</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>333</v>
+        <v>483</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Tenable One Exposure Management Platform Introduction</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>739732</v>
+        <v>390733</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ASPER TECNOLOGIA – RIO DE JANEIRO LTDA</t>
+          <t>TDec Redes de Computadores Ltda</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Arlem Barros</t>
+          <t>OMAR CAVALCANTE</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>arlem.barros@asper.tec.br</t>
+          <t>ocavalcante@tdec.com.br</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>303</v>
+        <v>488</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>739732</v>
+        <v>390733</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ASPER TECNOLOGIA – RIO DE JANEIRO LTDA</t>
+          <t>TDec Redes de Computadores Ltda</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Caio Almeida</t>
+          <t>OMAR CAVALCANTE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>caio.almeida@asper.tec.br</t>
+          <t>ocavalcante@tdec.com.br</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>346</v>
+        <v>539</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>739732</v>
+        <v>390733</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ASPER TECNOLOGIA – RIO DE JANEIRO LTDA</t>
+          <t>TDec Redes de Computadores Ltda</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Erico Albino</t>
+          <t>OMAR CAVALCANTE</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>erico.albino@asper.tec.br</t>
+          <t>ocavalcante@tdec.com.br</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>303</v>
+        <v>552</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Exposure Management Business Theory</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>739732</v>
+        <v>390733</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ASPER TECNOLOGIA – RIO DE JANEIRO LTDA</t>
+          <t>TDec Redes de Computadores Ltda</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nicole Grazielle Rodrigues dos Santos</t>
+          <t>Raúl Carbonari</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>nicole.santos@asper.tec.br</t>
+          <t>rcarbonari@tdec.com.br</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -8953,21 +8963,21 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>739732</v>
+        <v>390733</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ASPER TECNOLOGIA – RIO DE JANEIRO LTDA</t>
+          <t>TDec Redes de Computadores Ltda</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Nicole Grazielle Rodrigues dos Santos</t>
+          <t>Raúl Carbonari</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>nicole.santos@asper.tec.br</t>
+          <t>rcarbonari@tdec.com.br</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -8990,20 +9000,20 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nicole Grazielle Rodrigues dos Santos</t>
+          <t>Arlem Barros</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>nicole.santos@asper.tec.br</t>
+          <t>arlem.barros@asper.tec.br</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>346</v>
+        <v>303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
@@ -9018,188 +9028,188 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nicole Grazielle Rodrigues dos Santos</t>
+          <t>Caio Almeida</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>nicole.santos@asper.tec.br</t>
+          <t>caio.almeida@asper.tec.br</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>483</v>
+        <v>346</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tenable One Exposure Management Platform Introduction</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>579399</v>
+        <v>739732</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>XSite</t>
+          <t>ASPER TECNOLOGIA – RIO DE JANEIRO LTDA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Adriele De Jesus Primo</t>
+          <t>Erico Albino</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>adriele.primo@xsite.com.br</t>
+          <t>erico.albino@asper.tec.br</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>346</v>
+        <v>303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>579399</v>
+        <v>739732</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>XSite</t>
+          <t>ASPER TECNOLOGIA – RIO DE JANEIRO LTDA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Adriele De Jesus Primo</t>
+          <t>Luygui Pereira</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>adriele.primo@xsite.com.br</t>
+          <t>luygui.pereira@asper.tec.br</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>414</v>
+        <v>346</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Identity Exposure</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>579399</v>
+        <v>739732</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>XSite</t>
+          <t>ASPER TECNOLOGIA – RIO DE JANEIRO LTDA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Alexandre Gomes</t>
+          <t>Nicole Grazielle Rodrigues dos Santos</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>alexandre.gomes@xsite.com.br</t>
+          <t>nicole.santos@asper.tec.br</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>488</v>
+        <v>303</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>579399</v>
+        <v>739732</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>XSite</t>
+          <t>ASPER TECNOLOGIA – RIO DE JANEIRO LTDA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Breno Dos Santos Silva</t>
+          <t>Nicole Grazielle Rodrigues dos Santos</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>breno.silva@xsite.com.br</t>
+          <t>nicole.santos@asper.tec.br</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>579399</v>
+        <v>739732</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>XSite</t>
+          <t>ASPER TECNOLOGIA – RIO DE JANEIRO LTDA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DANIEL DA CONCEIÇÃO</t>
+          <t>Nicole Grazielle Rodrigues dos Santos</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>daniel.castro@xsite.com.br</t>
+          <t>nicole.santos@asper.tec.br</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>552</v>
+        <v>346</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Exposure Management Business Theory</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>579399</v>
+        <v>739732</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>XSite</t>
+          <t>ASPER TECNOLOGIA – RIO DE JANEIRO LTDA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Diego Souza</t>
+          <t>Nicole Grazielle Rodrigues dos Santos</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>diego.souza@xsite.com.br</t>
+          <t>nicole.santos@asper.tec.br</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>346</v>
+        <v>483</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Tenable One Exposure Management Platform Introduction</t>
         </is>
       </c>
     </row>
@@ -9214,20 +9224,20 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Diego Souza</t>
+          <t>Adriele De Jesus Primo</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>diego.souza@xsite.com.br</t>
+          <t>adriele.primo@xsite.com.br</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>488</v>
+        <v>346</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -9242,20 +9252,20 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Emanuele Nobre</t>
+          <t>Adriele De Jesus Primo</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>emanuele.nobre@xsite.com.br</t>
+          <t>adriele.primo@xsite.com.br</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>488</v>
+        <v>414</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+          <t>Introduction to Tenable Identity Exposure</t>
         </is>
       </c>
     </row>
@@ -9270,20 +9280,20 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Emanuele Nobre</t>
+          <t>Adriele De Jesus Primo</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>emanuele.nobre@xsite.com.br</t>
+          <t>adriele.primo@xsite.com.br</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>539</v>
+        <v>420</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tenable Cloud Security Specialist On-Demand</t>
+          <t>Tenable Identity Exposure Specialist</t>
         </is>
       </c>
     </row>
@@ -9298,20 +9308,20 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jonatan Dos Santos Gomes</t>
+          <t>Alexandre Gomes</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>jonatan.gomes@xsite.com.br</t>
+          <t>alexandre.gomes@xsite.com.br</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>346</v>
+        <v>488</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
         </is>
       </c>
     </row>
@@ -9326,20 +9336,20 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jonatan Dos Santos Gomes</t>
+          <t>Breno Dos Santos Silva</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>jonatan.gomes@xsite.com.br</t>
+          <t>breno.silva@xsite.com.br</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>488</v>
+        <v>346</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -9354,20 +9364,20 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jonatan Dos Santos Gomes</t>
+          <t>DANIEL DA CONCEIÇÃO</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>jonatan.gomes@xsite.com.br</t>
+          <t>daniel.castro@xsite.com.br</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>535</v>
+        <v>552</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Exposure Management Business Theory</t>
         </is>
       </c>
     </row>
@@ -9382,20 +9392,20 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Leandro Assmar</t>
+          <t>Diego Souza</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>leandro.assmar@xsite.com.br</t>
+          <t>diego.souza@xsite.com.br</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>488</v>
+        <v>346</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -9410,20 +9420,20 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Leonardo Oliveira</t>
+          <t>Diego Souza</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>leonardo.oliveira@xsite.com.br</t>
+          <t>diego.souza@xsite.com.br</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>539</v>
+        <v>488</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tenable Cloud Security Specialist On-Demand</t>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
         </is>
       </c>
     </row>
@@ -9438,20 +9448,20 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Yueslly Lisboa</t>
+          <t>Emanuele Nobre</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>yueslly.lisboa@xsite.com.br</t>
+          <t>emanuele.nobre@xsite.com.br</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>303</v>
+        <v>488</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
         </is>
       </c>
     </row>
@@ -9466,20 +9476,20 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Yueslly Lisboa</t>
+          <t>Emanuele Nobre</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>yueslly.lisboa@xsite.com.br</t>
+          <t>emanuele.nobre@xsite.com.br</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>333</v>
+        <v>539</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9504,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Yueslly Lisboa</t>
+          <t>Jonatan Dos Santos Gomes</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>yueslly.lisboa@xsite.com.br</t>
+          <t>jonatan.gomes@xsite.com.br</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -9522,12 +9532,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Yueslly Lisboa</t>
+          <t>Jonatan Dos Santos Gomes</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>yueslly.lisboa@xsite.com.br</t>
+          <t>jonatan.gomes@xsite.com.br</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -9550,216 +9560,216 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Yuri Souza</t>
+          <t>Jonatan Dos Santos Gomes</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>yuri.souza@xsite.com.br</t>
+          <t>jonatan.gomes@xsite.com.br</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>488</v>
+        <v>535</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>397166</v>
+        <v>579399</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ISH Tecnologia SA</t>
+          <t>XSite</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Alexandre Pertel Gonçalves</t>
+          <t>Leandro Assmar</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>alexandre.goncalves@ish.com.br</t>
+          <t>leandro.assmar@xsite.com.br</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>346</v>
+        <v>488</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>397166</v>
+        <v>579399</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ISH Tecnologia SA</t>
+          <t>XSite</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Anderson Lemos</t>
+          <t>Leonardo Oliveira</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>anderson.lemos@ish.com.br</t>
+          <t>leonardo.oliveira@xsite.com.br</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>303</v>
+        <v>539</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>397166</v>
+        <v>579399</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ISH Tecnologia SA</t>
+          <t>XSite</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Anderson Lemos</t>
+          <t>Yueslly Lisboa</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>anderson.lemos@ish.com.br</t>
+          <t>yueslly.lisboa@xsite.com.br</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>333</v>
+        <v>303</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>397166</v>
+        <v>579399</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ISH Tecnologia SA</t>
+          <t>XSite</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Anderson Lemos</t>
+          <t>Yueslly Lisboa</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>anderson.lemos@ish.com.br</t>
+          <t>yueslly.lisboa@xsite.com.br</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>539</v>
+        <v>333</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tenable Cloud Security Specialist On-Demand</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>397166</v>
+        <v>579399</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ISH Tecnologia SA</t>
+          <t>XSite</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Anderson Neiva</t>
+          <t>Yueslly Lisboa</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>anderson.neiva@ish.com.br</t>
+          <t>yueslly.lisboa@xsite.com.br</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>303</v>
+        <v>346</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>397166</v>
+        <v>579399</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ISH Tecnologia SA</t>
+          <t>XSite</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Claudio Neto</t>
+          <t>Yueslly Lisboa</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>claudio.neto@ish.com.br</t>
+          <t>yueslly.lisboa@xsite.com.br</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>535</v>
+        <v>488</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>397166</v>
+        <v>579399</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ISH Tecnologia SA</t>
+          <t>XSite</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Claudio Neto</t>
+          <t>Yuri Souza</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>claudio.neto@ish.com.br</t>
+          <t>yuri.souza@xsite.com.br</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>539</v>
+        <v>488</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tenable Cloud Security Specialist On-Demand</t>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
         </is>
       </c>
     </row>
@@ -9774,20 +9784,20 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Danilo De Santana Dantas</t>
+          <t>Alexandre Pertel Gonçalves</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>danilo.dantas@ish.com.br</t>
+          <t>alexandre.goncalves@ish.com.br</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>535</v>
+        <v>346</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -9802,20 +9812,20 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Diego Costa</t>
+          <t>Anderson Lemos</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>diego.costa@ish.com.br</t>
+          <t>anderson.lemos@ish.com.br</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>346</v>
+        <v>303</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
@@ -9830,20 +9840,20 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Edson Júnior</t>
+          <t>Anderson Lemos</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>edson.junior@ish.com.br</t>
+          <t>anderson.lemos@ish.com.br</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>539</v>
+        <v>333</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tenable Cloud Security Specialist On-Demand</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
@@ -9858,20 +9868,20 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Edson Júnior</t>
+          <t>Anderson Lemos</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>edson.junior@ish.com.br</t>
+          <t>anderson.lemos@ish.com.br</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>552</v>
+        <v>539</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Exposure Management Business Theory</t>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
         </is>
       </c>
     </row>
@@ -9886,20 +9896,20 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Eliabe Bento</t>
+          <t>Anderson Neiva</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>eliabe.bento@ish.com.br</t>
+          <t>anderson.neiva@ish.com.br</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>414</v>
+        <v>303</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Identity Exposure</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
@@ -9914,20 +9924,20 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Felipe Santos da Silva</t>
+          <t>Claudio Neto</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>felipe.ssilva@ish.com.br</t>
+          <t>claudio.neto@ish.com.br</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>483</v>
+        <v>535</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tenable One Exposure Management Platform Introduction</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
@@ -9942,20 +9952,20 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Felipus Gomes</t>
+          <t>Claudio Neto</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>felipus.gomes@ish.com.br</t>
+          <t>claudio.neto@ish.com.br</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>303</v>
+        <v>539</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
         </is>
       </c>
     </row>
@@ -9970,20 +9980,20 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Felipus Gomes</t>
+          <t>Danilo De Santana Dantas</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>felipus.gomes@ish.com.br</t>
+          <t>danilo.dantas@ish.com.br</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>333</v>
+        <v>535</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
@@ -9998,12 +10008,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Felipus Gomes</t>
+          <t>Diego Do Rosário Costa</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>felipus.gomes@ish.com.br</t>
+          <t>diego.costa@ish.com.br</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -10026,20 +10036,20 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Felipus Gomes</t>
+          <t>Edson Júnior</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>felipus.gomes@ish.com.br</t>
+          <t>edson.junior@ish.com.br</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>483</v>
+        <v>539</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tenable One Exposure Management Platform Introduction</t>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
         </is>
       </c>
     </row>
@@ -10054,20 +10064,20 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Gabriel Gattini</t>
+          <t>Edson Júnior</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>gabriel.gattini@ish.com.br</t>
+          <t>edson.junior@ish.com.br</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>483</v>
+        <v>552</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tenable One Exposure Management Platform Introduction</t>
+          <t>Exposure Management Business Theory</t>
         </is>
       </c>
     </row>
@@ -10082,20 +10092,20 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hecio Arruda</t>
+          <t>Eliabe Bento</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>hecio.arruda@ish.com.br</t>
+          <t>eliabe.bento@ish.com.br</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>303</v>
+        <v>414</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Introduction to Tenable Identity Exposure</t>
         </is>
       </c>
     </row>
@@ -10110,20 +10120,20 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Hecio Arruda</t>
+          <t>Felipe Santos da Silva</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>hecio.arruda@ish.com.br</t>
+          <t>felipe.ssilva@ish.com.br</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>333</v>
+        <v>483</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Tenable One Exposure Management Platform Introduction</t>
         </is>
       </c>
     </row>
@@ -10138,20 +10148,20 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Hecio Arruda</t>
+          <t>Felipus Gomes</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>hecio.arruda@ish.com.br</t>
+          <t>felipus.gomes@ish.com.br</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>346</v>
+        <v>303</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
@@ -10166,20 +10176,20 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Jacques Almeida</t>
+          <t>Felipus Gomes</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>jacques.almeida@ish.com.br</t>
+          <t>felipus.gomes@ish.com.br</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>303</v>
+        <v>333</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
@@ -10194,20 +10204,20 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Joelma Da Silva Batista</t>
+          <t>Felipus Gomes</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>joelma.batista@ish.com.br</t>
+          <t>felipus.gomes@ish.com.br</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -10222,20 +10232,20 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Joelma Da Silva Batista</t>
+          <t>Felipus Gomes</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>joelma.batista@ish.com.br</t>
+          <t>felipus.gomes@ish.com.br</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>346</v>
+        <v>483</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Tenable One Exposure Management Platform Introduction</t>
         </is>
       </c>
     </row>
@@ -10250,20 +10260,20 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Joelma Da Silva Batista</t>
+          <t>Gabriel Gattini</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>joelma.batista@ish.com.br</t>
+          <t>gabriel.gattini@ish.com.br</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+          <t>Tenable One Exposure Management Platform Introduction</t>
         </is>
       </c>
     </row>
@@ -10278,20 +10288,20 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Jonas Nasser</t>
+          <t>Hecio Arruda</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>jonas.nasser@ish.com.br</t>
+          <t>hecio.arruda@ish.com.br</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>346</v>
+        <v>303</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
@@ -10306,20 +10316,20 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Kramer Saunders</t>
+          <t>Hecio Arruda</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>kramer.saunders@ish.com.br</t>
+          <t>hecio.arruda@ish.com.br</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
@@ -10334,20 +10344,20 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Lucas De Araujo Feitosa</t>
+          <t>Hecio Arruda</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>lucas.feitosa@ish.com.br</t>
+          <t>hecio.arruda@ish.com.br</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>535</v>
+        <v>346</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -10362,20 +10372,20 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Lucas De Araujo Feitosa</t>
+          <t>Jacques Almeida</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>lucas.feitosa@ish.com.br</t>
+          <t>jacques.almeida@ish.com.br</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>539</v>
+        <v>303</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tenable Cloud Security Specialist On-Demand</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
@@ -10390,20 +10400,20 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Luiz Eduardo Eleuterio de Souza</t>
+          <t>Joelma Da Silva Batista</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>luiz.eduardo@visioncybersecurity.com</t>
+          <t>joelma.batista@ish.com.br</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>303</v>
+        <v>333</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
@@ -10418,20 +10428,20 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Luiz Eduardo Eleuterio de Souza</t>
+          <t>Joelma Da Silva Batista</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>luiz.eduardo@visioncybersecurity.com</t>
+          <t>joelma.batista@ish.com.br</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -10446,20 +10456,20 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Luiz Eduardo Eleuterio de Souza</t>
+          <t>Joelma Da Silva Batista</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>luiz.eduardo@visioncybersecurity.com</t>
+          <t>joelma.batista@ish.com.br</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>346</v>
+        <v>488</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
         </is>
       </c>
     </row>
@@ -10474,20 +10484,20 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Luiz Eduardo Eleuterio de Souza</t>
+          <t>Jonas Nasser</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>luiz.eduardo@visioncybersecurity.com</t>
+          <t>jonas.nasser@ish.com.br</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>535</v>
+        <v>346</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -10502,20 +10512,20 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Luiz Eduardo Eleuterio de Souza</t>
+          <t>Kramer Saunders</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>luiz.eduardo@visioncybersecurity.com</t>
+          <t>kramer.saunders@ish.com.br</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>552</v>
+        <v>346</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Exposure Management Business Theory</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -10530,20 +10540,20 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Luiz Gustavo Batista Bugiga</t>
+          <t>Lucas De Araujo Feitosa</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>luiz.bugiga@visioncybersecurity.com</t>
+          <t>lucas.feitosa@ish.com.br</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>303</v>
+        <v>535</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
@@ -10558,20 +10568,20 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Marcelo Mantovani</t>
+          <t>Lucas De Araujo Feitosa</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>marcelo.mantovani@ish.com.br</t>
+          <t>lucas.feitosa@ish.com.br</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>346</v>
+        <v>539</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
         </is>
       </c>
     </row>
@@ -10586,20 +10596,20 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Marcelo Martins</t>
+          <t>Luiz Eduardo Eleuterio de Souza</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>marcelo.martins@ish.com.br</t>
+          <t>luiz.eduardo@visioncybersecurity.com</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>333</v>
+        <v>303</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
@@ -10614,20 +10624,20 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Marcelo Martins</t>
+          <t>Luiz Eduardo Eleuterio de Souza</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>marcelo.martins@ish.com.br</t>
+          <t>luiz.eduardo@visioncybersecurity.com</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>539</v>
+        <v>333</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tenable Cloud Security Specialist On-Demand</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
@@ -10642,20 +10652,20 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Marcio Mendes</t>
+          <t>Luiz Eduardo Eleuterio de Souza</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>marcio.mendes@ish.com.br</t>
+          <t>luiz.eduardo@visioncybersecurity.com</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>539</v>
+        <v>346</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tenable Cloud Security Specialist On-Demand</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -10670,20 +10680,20 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Mateus Mantovani</t>
+          <t>Luiz Eduardo Eleuterio de Souza</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>mateus.mantovani@ish.com.br</t>
+          <t>luiz.eduardo@visioncybersecurity.com</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>333</v>
+        <v>535</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
@@ -10698,20 +10708,20 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Matheus Manea</t>
+          <t>Luiz Eduardo Eleuterio de Souza</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>matheus.manea@ish.com.br</t>
+          <t>luiz.eduardo@visioncybersecurity.com</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>346</v>
+        <v>552</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Exposure Management Business Theory</t>
         </is>
       </c>
     </row>
@@ -10726,12 +10736,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Reginaldo Santos</t>
+          <t>Luiz Gustavo Batista Bugiga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>reginaldo.santos@ish.com.br</t>
+          <t>luiz.bugiga@visioncybersecurity.com</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -10754,20 +10764,20 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Reginaldo Santos</t>
+          <t>Marcelo Mantovani</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>reginaldo.santos@ish.com.br</t>
+          <t>marcelo.mantovani@ish.com.br</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>483</v>
+        <v>346</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tenable One Exposure Management Platform Introduction</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -10782,20 +10792,20 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Roger Marques</t>
+          <t>Marcelo Martins</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>roger.marques@ish.com.br</t>
+          <t>marcelo.martins@ish.com.br</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>483</v>
+        <v>333</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tenable One Exposure Management Platform Introduction</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
@@ -10810,20 +10820,20 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Sidnei Santana</t>
+          <t>Marcelo Martins</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>sidnei.santana@ish.com.br</t>
+          <t>marcelo.martins@ish.com.br</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>346</v>
+        <v>539</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
         </is>
       </c>
     </row>
@@ -10838,20 +10848,20 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Sidnei Santana</t>
+          <t>Marcio Mendes</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>sidnei.santana@ish.com.br</t>
+          <t>marcio.mendes@ish.com.br</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>488</v>
+        <v>539</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
         </is>
       </c>
     </row>
@@ -10866,20 +10876,20 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Tamiris Silva</t>
+          <t>Mateus Mantovani</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>tamiris.silva@ish.com.br</t>
+          <t>mateus.mantovani@ish.com.br</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>303</v>
+        <v>333</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
@@ -10894,20 +10904,20 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tamiris Silva</t>
+          <t>Matheus Manea</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>tamiris.silva@ish.com.br</t>
+          <t>matheus.manea@ish.com.br</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -10922,20 +10932,20 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tamiris Silva</t>
+          <t>Reginaldo Santos</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>tamiris.silva@ish.com.br</t>
+          <t>reginaldo.santos@ish.com.br</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>346</v>
+        <v>303</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
@@ -10950,20 +10960,20 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Tamiris Silva</t>
+          <t>Reginaldo Santos</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>tamiris.silva@ish.com.br</t>
+          <t>reginaldo.santos@ish.com.br</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+          <t>Tenable One Exposure Management Platform Introduction</t>
         </is>
       </c>
     </row>
@@ -10978,20 +10988,20 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Thiago Gomes</t>
+          <t>Roger Marques</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>thiago.gomes@ish.com.br</t>
+          <t>roger.marques@ish.com.br</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>346</v>
+        <v>483</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Tenable One Exposure Management Platform Introduction</t>
         </is>
       </c>
     </row>
@@ -11006,20 +11016,20 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Valdir Neto</t>
+          <t>Sidnei Santana</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>valdir.neto@ish.com.br</t>
+          <t>sidnei.santana@ish.com.br</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>539</v>
+        <v>346</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tenable Cloud Security Specialist On-Demand</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -11034,20 +11044,20 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Valter Pereira da Costa Junior</t>
+          <t>Sidnei Santana</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>valter.costa@ish.com.br</t>
+          <t>sidnei.santana@ish.com.br</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>303</v>
+        <v>488</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
         </is>
       </c>
     </row>
@@ -11062,20 +11072,20 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Valter Pereira da Costa Junior</t>
+          <t>Tamiris Silva</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>valter.costa@ish.com.br</t>
+          <t>tamiris.silva@ish.com.br</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>346</v>
+        <v>303</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
@@ -11090,20 +11100,20 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Victor Saldanha</t>
+          <t>Tamiris Silva</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>victor.santos@ish.com.br</t>
+          <t>tamiris.silva@ish.com.br</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>303</v>
+        <v>333</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
@@ -11118,20 +11128,20 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Victor Saldanha</t>
+          <t>Tamiris Silva</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>victor.santos@ish.com.br</t>
+          <t>tamiris.silva@ish.com.br</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -11146,20 +11156,20 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Victor Saldanha</t>
+          <t>Tamiris Silva</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>victor.santos@ish.com.br</t>
+          <t>tamiris.silva@ish.com.br</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>346</v>
+        <v>488</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
         </is>
       </c>
     </row>
@@ -11174,20 +11184,20 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Victor Saldanha</t>
+          <t>Thiago Gomes</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>victor.santos@ish.com.br</t>
+          <t>thiago.gomes@ish.com.br</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>414</v>
+        <v>346</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Identity Exposure</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -11202,12 +11212,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Victor Silva</t>
+          <t>Valdir Neto</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>victor.araujo@ish.com.br</t>
+          <t>valdir.neto@ish.com.br</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -11230,68 +11240,68 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Wagner De Jesus Belo Meireles</t>
+          <t>Valter Pereira da Costa Junior</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>wagner.meireles@ish.com.br</t>
+          <t>valter.costa@ish.com.br</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>346</v>
+        <v>303</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>993857</v>
+        <v>397166</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>GLOBAL SEC. TECNOLOGIA &amp; INFORMACAO EIRELI</t>
+          <t>ISH Tecnologia SA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Lucas Vasconcelos</t>
+          <t>Valter Pereira da Costa Junior</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>lucas.vasconcelos@globalsectecnologia.com.br</t>
+          <t>valter.costa@ish.com.br</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>303</v>
+        <v>346</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>510201</v>
+        <v>397166</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Netsecurity Tecnologia LTDA</t>
+          <t>ISH Tecnologia SA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ALESSANDRO VIEIRA</t>
+          <t>Victor Saldanha</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>alessandro.vitalino@netsecurity.com.br</t>
+          <t>victor.santos@ish.com.br</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -11305,21 +11315,21 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>510201</v>
+        <v>397166</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Netsecurity Tecnologia LTDA</t>
+          <t>ISH Tecnologia SA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ALESSANDRO VIEIRA</t>
+          <t>Victor Saldanha</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>alessandro.vitalino@netsecurity.com.br</t>
+          <t>victor.santos@ish.com.br</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -11333,21 +11343,21 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>510201</v>
+        <v>397166</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Netsecurity Tecnologia LTDA</t>
+          <t>ISH Tecnologia SA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ALESSANDRO VIEIRA</t>
+          <t>Victor Saldanha</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>alessandro.vitalino@netsecurity.com.br</t>
+          <t>victor.santos@ish.com.br</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -11361,21 +11371,21 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>510201</v>
+        <v>397166</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Netsecurity Tecnologia LTDA</t>
+          <t>ISH Tecnologia SA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>ALESSANDRO VIEIRA</t>
+          <t>Victor Saldanha</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>alessandro.vitalino@netsecurity.com.br</t>
+          <t>victor.santos@ish.com.br</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -11389,85 +11399,85 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>510201</v>
+        <v>397166</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Netsecurity Tecnologia LTDA</t>
+          <t>ISH Tecnologia SA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ALESSANDRO VIEIRA</t>
+          <t>Victor Silva</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>alessandro.vitalino@netsecurity.com.br</t>
+          <t>victor.araujo@ish.com.br</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>510201</v>
+        <v>397166</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Netsecurity Tecnologia LTDA</t>
+          <t>ISH Tecnologia SA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ALESSANDRO VIEIRA</t>
+          <t>Wagner De Jesus Belo Meireles</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>alessandro.vitalino@netsecurity.com.br</t>
+          <t>wagner.meireles@ish.com.br</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>552</v>
+        <v>346</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Exposure Management Business Theory</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>510201</v>
+        <v>993857</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Netsecurity Tecnologia LTDA</t>
+          <t>GLOBAL SEC. TECNOLOGIA &amp; INFORMACAO EIRELI</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>André Feltrin</t>
+          <t>Lucas Vasconcelos</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>andre.feltrin@netsecurity.com.br</t>
+          <t>lucas.vasconcelos@globalsectecnologia.com.br</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>414</v>
+        <v>303</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Identity Exposure</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
@@ -11482,20 +11492,20 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>André Feltrin</t>
+          <t>ALESSANDRO VIEIRA</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>andre.feltrin@netsecurity.com.br</t>
+          <t>alessandro.vitalino@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>483</v>
+        <v>303</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tenable One Exposure Management Platform Introduction</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
@@ -11510,20 +11520,20 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>André Feltrin</t>
+          <t>ALESSANDRO VIEIRA</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>andre.feltrin@netsecurity.com.br</t>
+          <t>alessandro.vitalino@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>535</v>
+        <v>333</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
@@ -11538,20 +11548,20 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>André Feltrin</t>
+          <t>ALESSANDRO VIEIRA</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>andre.feltrin@netsecurity.com.br</t>
+          <t>alessandro.vitalino@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>552</v>
+        <v>346</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Exposure Management Business Theory</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -11566,20 +11576,20 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bruno Leite</t>
+          <t>ALESSANDRO VIEIRA</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>bruno.leite@netsecurity.com.br</t>
+          <t>alessandro.vitalino@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>375</v>
+        <v>414</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tenable Vulnerability Management Specialist</t>
+          <t>Introduction to Tenable Identity Exposure</t>
         </is>
       </c>
     </row>
@@ -11594,20 +11604,20 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bruno Leite</t>
+          <t>ALESSANDRO VIEIRA</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>bruno.leite@netsecurity.com.br</t>
+          <t>alessandro.vitalino@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>488</v>
+        <v>535</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
@@ -11622,20 +11632,20 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Gutenberg Brito</t>
+          <t>ALESSANDRO VIEIRA</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>gutenberg.brito@netsecurity.com.br</t>
+          <t>alessandro.vitalino@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>303</v>
+        <v>552</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Exposure Management Business Theory</t>
         </is>
       </c>
     </row>
@@ -11650,20 +11660,20 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Gutenberg Brito</t>
+          <t>André Feltrin</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>gutenberg.brito@netsecurity.com.br</t>
+          <t>andre.feltrin@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>333</v>
+        <v>414</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Introduction to Tenable Identity Exposure</t>
         </is>
       </c>
     </row>
@@ -11678,20 +11688,20 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Gutenberg Brito</t>
+          <t>André Feltrin</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>gutenberg.brito@netsecurity.com.br</t>
+          <t>andre.feltrin@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>346</v>
+        <v>483</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Tenable One Exposure Management Platform Introduction</t>
         </is>
       </c>
     </row>
@@ -11706,12 +11716,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Gutenberg Brito</t>
+          <t>André Feltrin</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>gutenberg.brito@netsecurity.com.br</t>
+          <t>andre.feltrin@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E144" t="n">
@@ -11734,12 +11744,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Gutenberg Brito</t>
+          <t>André Feltrin</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>gutenberg.brito@netsecurity.com.br</t>
+          <t>andre.feltrin@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E145" t="n">
@@ -11762,20 +11772,20 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Gutenberg Brito</t>
+          <t>Bruno Leite</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>gutenberg.brito@netsecurity.com.br</t>
+          <t>bruno.leite@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>561</v>
+        <v>375</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tenable One Exposure Management Platform Specialist On-Demand</t>
+          <t>Tenable Vulnerability Management Specialist</t>
         </is>
       </c>
     </row>
@@ -11790,20 +11800,20 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Leonardo Silva</t>
+          <t>Bruno Leite</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>leonardo.silva@netsecurity.com.br</t>
+          <t>bruno.leite@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>333</v>
+        <v>488</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
         </is>
       </c>
     </row>
@@ -11818,20 +11828,20 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Leonardo Silva</t>
+          <t>Gutenberg Brito</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>leonardo.silva@netsecurity.com.br</t>
+          <t>gutenberg.brito@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>346</v>
+        <v>303</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
@@ -11846,20 +11856,20 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Leonardo Silva</t>
+          <t>Gutenberg Brito</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>leonardo.silva@netsecurity.com.br</t>
+          <t>gutenberg.brito@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>414</v>
+        <v>333</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Identity Exposure</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
@@ -11874,20 +11884,20 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Leonardo Silva</t>
+          <t>Gutenberg Brito</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>leonardo.silva@netsecurity.com.br</t>
+          <t>gutenberg.brito@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>535</v>
+        <v>346</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -11902,20 +11912,20 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Mar�lia Cardoso</t>
+          <t>Gutenberg Brito</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>marilia.cardoso@netsecurity.com.br</t>
+          <t>gutenberg.brito@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>346</v>
+        <v>535</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
@@ -11930,20 +11940,20 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Thiago Ribeiro</t>
+          <t>Gutenberg Brito</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>thiago.ribeiro@netsecurity.com.br</t>
+          <t>gutenberg.brito@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>375</v>
+        <v>552</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tenable Vulnerability Management Specialist</t>
+          <t>Exposure Management Business Theory</t>
         </is>
       </c>
     </row>
@@ -11958,20 +11968,20 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Willian Santos Arruda</t>
+          <t>Gutenberg Brito</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>willian.arruda@netsecurity.com.br</t>
+          <t>gutenberg.brito@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>303</v>
+        <v>561</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Tenable One Exposure Management Platform Specialist On-Demand</t>
         </is>
       </c>
     </row>
@@ -11986,12 +11996,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Willian Santos Arruda</t>
+          <t>Leonardo Silva</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>willian.arruda@netsecurity.com.br</t>
+          <t>leonardo.silva@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E154" t="n">
@@ -12014,12 +12024,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Willian Santos Arruda</t>
+          <t>Leonardo Silva</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>willian.arruda@netsecurity.com.br</t>
+          <t>leonardo.silva@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E155" t="n">
@@ -12042,20 +12052,20 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Willian Santos Arruda</t>
+          <t>Leonardo Silva</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>willian.arruda@netsecurity.com.br</t>
+          <t>leonardo.silva@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>483</v>
+        <v>414</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tenable One Exposure Management Platform Introduction</t>
+          <t>Introduction to Tenable Identity Exposure</t>
         </is>
       </c>
     </row>
@@ -12070,12 +12080,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Willian Santos Arruda</t>
+          <t>Leonardo Silva</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>willian.arruda@netsecurity.com.br</t>
+          <t>leonardo.silva@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E157" t="n">
@@ -12098,180 +12108,180 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Willian Santos Arruda</t>
+          <t>Mar�lia Cardoso</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>willian.arruda@netsecurity.com.br</t>
+          <t>marilia.cardoso@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>552</v>
+        <v>346</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Exposure Management Business Theory</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>458265</v>
+        <v>510201</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Future Technologies Informatica Ltda</t>
+          <t>Netsecurity Tecnologia LTDA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Leonardo Figueira</t>
+          <t>Rafael Shimkawa</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>leonardo.figueira@future.com.br</t>
+          <t>rafael.shimokawa@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>303</v>
+        <v>346</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>458265</v>
+        <v>510201</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Future Technologies Informatica Ltda</t>
+          <t>Netsecurity Tecnologia LTDA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Leonardo Figueira</t>
+          <t>Rafael Shimkawa</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>leonardo.figueira@future.com.br</t>
+          <t>rafael.shimokawa@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>333</v>
+        <v>483</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Tenable One Exposure Management Platform Introduction</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>458265</v>
+        <v>510201</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Future Technologies Informatica Ltda</t>
+          <t>Netsecurity Tecnologia LTDA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Matheus Zaparolli</t>
+          <t>Thiago Ribeiro</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>matheus.zaparolli@future.com.br</t>
+          <t>thiago.ribeiro@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>346</v>
+        <v>375</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Tenable Vulnerability Management Specialist</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>458265</v>
+        <v>510201</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Future Technologies Informatica Ltda</t>
+          <t>Netsecurity Tecnologia LTDA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Odimar Junior</t>
+          <t>Willian Santos Arruda</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>odimar.junior@future.com.br</t>
+          <t>willian.arruda@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>333</v>
+        <v>303</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>458265</v>
+        <v>510201</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Future Technologies Informatica Ltda</t>
+          <t>Netsecurity Tecnologia LTDA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Odimar Junior</t>
+          <t>Willian Santos Arruda</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>odimar.junior@future.com.br</t>
+          <t>willian.arruda@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>458265</v>
+        <v>510201</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Future Technologies Informatica Ltda</t>
+          <t>Netsecurity Tecnologia LTDA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Thaciany Silva</t>
+          <t>Willian Santos Arruda</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>thaciany.silva@future.com.br</t>
+          <t>willian.arruda@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E164" t="n">
@@ -12285,357 +12295,357 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119472</v>
+        <v>510201</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>ACCENTURE DO BRASIL LTDA</t>
+          <t>Netsecurity Tecnologia LTDA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Carlos Araújo</t>
+          <t>Willian Santos Arruda</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>carlos.h.araujo@accenture.com</t>
+          <t>willian.arruda@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>552</v>
+        <v>483</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Exposure Management Business Theory</t>
+          <t>Tenable One Exposure Management Platform Introduction</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119472</v>
+        <v>510201</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ACCENTURE DO BRASIL LTDA</t>
+          <t>Netsecurity Tecnologia LTDA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Felipe Guerreiro do Prado</t>
+          <t>Willian Santos Arruda</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>f.guerreiro.do.prado@accenture.com</t>
+          <t>willian.arruda@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>346</v>
+        <v>535</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119472</v>
+        <v>510201</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ACCENTURE DO BRASIL LTDA</t>
+          <t>Netsecurity Tecnologia LTDA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Luis Fernandes</t>
+          <t>Willian Santos Arruda</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>luis.ant.fernandes@accenture.com</t>
+          <t>willian.arruda@netsecurity.com.br</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>346</v>
+        <v>552</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Exposure Management Business Theory</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119472</v>
+        <v>458265</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ACCENTURE DO BRASIL LTDA</t>
+          <t>Future Technologies Informatica Ltda</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Luis Fernandes</t>
+          <t>Leonardo Figueira</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>luis.ant.fernandes@accenture.com</t>
+          <t>leonardo.figueira@future.com.br</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>552</v>
+        <v>303</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Exposure Management Business Theory</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119472</v>
+        <v>458265</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ACCENTURE DO BRASIL LTDA</t>
+          <t>Future Technologies Informatica Ltda</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Moisés Dantas Felix</t>
+          <t>Leonardo Figueira</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>moises.d.felix@accenture.com</t>
+          <t>leonardo.figueira@future.com.br</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>535</v>
+        <v>333</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>106294</v>
+        <v>458265</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Under Protection Consultoria em Informatica LTDA</t>
+          <t>Future Technologies Informatica Ltda</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Andrey Melo</t>
+          <t>Matheus Zaparolli</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>andrey.melo@underprotection.com.br</t>
+          <t>matheus.zaparolli@future.com.br</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>106294</v>
+        <v>458265</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Under Protection Consultoria em Informatica LTDA</t>
+          <t>Future Technologies Informatica Ltda</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Andrey Melo</t>
+          <t>Odimar Junior</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>andrey.melo@underprotection.com.br</t>
+          <t>odimar.junior@future.com.br</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>106294</v>
+        <v>458265</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Under Protection Consultoria em Informatica LTDA</t>
+          <t>Future Technologies Informatica Ltda</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Jefferson Abbin</t>
+          <t>Odimar Junior</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>jefferson.abbin@underprotection.com.br</t>
+          <t>odimar.junior@future.com.br</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>303</v>
+        <v>346</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>106294</v>
+        <v>458265</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Under Protection Consultoria em Informatica LTDA</t>
+          <t>Future Technologies Informatica Ltda</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Jefferson Abbin</t>
+          <t>Thaciany Silva</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>jefferson.abbin@underprotection.com.br</t>
+          <t>thaciany.silva@future.com.br</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>106294</v>
+        <v>119472</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Under Protection Consultoria em Informatica LTDA</t>
+          <t>ACCENTURE DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Jefferson Abbin</t>
+          <t>Carlos Araújo</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>jefferson.abbin@underprotection.com.br</t>
+          <t>carlos.h.araujo@accenture.com</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>346</v>
+        <v>552</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Exposure Management Business Theory</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>106294</v>
+        <v>119472</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Under Protection Consultoria em Informatica LTDA</t>
+          <t>ACCENTURE DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Jefferson Abbin</t>
+          <t>Felipe Guerreiro do Prado</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>jefferson.abbin@underprotection.com.br</t>
+          <t>f.guerreiro.do.prado@accenture.com</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>483</v>
+        <v>346</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tenable One Exposure Management Platform Introduction</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>106294</v>
+        <v>119472</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Under Protection Consultoria em Informatica LTDA</t>
+          <t>ACCENTURE DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Jefferson Abbin</t>
+          <t>Luis Fernandes</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>jefferson.abbin@underprotection.com.br</t>
+          <t>luis.ant.fernandes@accenture.com</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>535</v>
+        <v>346</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>106294</v>
+        <v>119472</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Under Protection Consultoria em Informatica LTDA</t>
+          <t>ACCENTURE DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Jefferson Abbin</t>
+          <t>Luis Fernandes</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>jefferson.abbin@underprotection.com.br</t>
+          <t>luis.ant.fernandes@accenture.com</t>
         </is>
       </c>
       <c r="E177" t="n">
@@ -12649,29 +12659,29 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>106294</v>
+        <v>119472</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Under Protection Consultoria em Informatica LTDA</t>
+          <t>ACCENTURE DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Julia Johnson</t>
+          <t>Moisés Dantas Felix</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>julia.melo@underprotection.com.br</t>
+          <t>moises.d.felix@accenture.com</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>414</v>
+        <v>535</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Identity Exposure</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
@@ -12686,20 +12696,20 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Marco Antonio Leissmann</t>
+          <t>Andrey Melo</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>marco.leissmann@underprotection.com.br</t>
+          <t>andrey.melo@underprotection.com.br</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>303</v>
+        <v>333</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
@@ -12714,20 +12724,20 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Marco Antonio Leissmann</t>
+          <t>Andrey Melo</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>marco.leissmann@underprotection.com.br</t>
+          <t>andrey.melo@underprotection.com.br</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -12742,20 +12752,20 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Marco Antonio Leissmann</t>
+          <t>Jefferson Abbin</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>marco.leissmann@underprotection.com.br</t>
+          <t>jefferson.abbin@underprotection.com.br</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>346</v>
+        <v>303</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
@@ -12770,20 +12780,20 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Marco Antonio Leissmann</t>
+          <t>Jefferson Abbin</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>marco.leissmann@underprotection.com.br</t>
+          <t>jefferson.abbin@underprotection.com.br</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>414</v>
+        <v>333</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Identity Exposure</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
@@ -12798,20 +12808,20 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Marco Antonio Leissmann</t>
+          <t>Jefferson Abbin</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>marco.leissmann@underprotection.com.br</t>
+          <t>jefferson.abbin@underprotection.com.br</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>483</v>
+        <v>346</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Tenable One Exposure Management Platform Introduction</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -12826,20 +12836,20 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Marco Antonio Leissmann</t>
+          <t>Jefferson Abbin</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>marco.leissmann@underprotection.com.br</t>
+          <t>jefferson.abbin@underprotection.com.br</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>535</v>
+        <v>483</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Tenable One Exposure Management Platform Introduction</t>
         </is>
       </c>
     </row>
@@ -12854,20 +12864,20 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Marco Antonio Leissmann</t>
+          <t>Jefferson Abbin</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>marco.leissmann@underprotection.com.br</t>
+          <t>jefferson.abbin@underprotection.com.br</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>552</v>
+        <v>535</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Exposure Management Business Theory</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
@@ -12882,12 +12892,12 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Ney Gelbcke Junior</t>
+          <t>Jefferson Abbin</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>ney.gelbcke@underprotection.com.br</t>
+          <t>jefferson.abbin@underprotection.com.br</t>
         </is>
       </c>
       <c r="E186" t="n">
@@ -12901,253 +12911,253 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>543439</v>
+        <v>106294</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Kryptus Seguranca da Informacao SA</t>
+          <t>Under Protection Consultoria em Informatica LTDA</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>João Bessa</t>
+          <t>Julia Johnson</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>joao.bessa@kryptus.com</t>
+          <t>julia.melo@underprotection.com.br</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>333</v>
+        <v>414</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Introduction to Tenable Identity Exposure</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>543439</v>
+        <v>106294</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Kryptus Seguranca da Informacao SA</t>
+          <t>Under Protection Consultoria em Informatica LTDA</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>João Bessa</t>
+          <t>Marco Antonio Leissmann</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>joao.bessa@kryptus.com</t>
+          <t>marco.leissmann@underprotection.com.br</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>346</v>
+        <v>303</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>543439</v>
+        <v>106294</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Kryptus Seguranca da Informacao SA</t>
+          <t>Under Protection Consultoria em Informatica LTDA</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>João Bessa</t>
+          <t>Marco Antonio Leissmann</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>joao.bessa@kryptus.com</t>
+          <t>marco.leissmann@underprotection.com.br</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>535</v>
+        <v>333</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>543439</v>
+        <v>106294</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Kryptus Seguranca da Informacao SA</t>
+          <t>Under Protection Consultoria em Informatica LTDA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>João Bessa</t>
+          <t>Marco Antonio Leissmann</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>joao.bessa@kryptus.com</t>
+          <t>marco.leissmann@underprotection.com.br</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>552</v>
+        <v>346</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Exposure Management Business Theory</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>543439</v>
+        <v>106294</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Kryptus Seguranca da Informacao SA</t>
+          <t>Under Protection Consultoria em Informatica LTDA</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Leonardo Alarcon</t>
+          <t>Marco Antonio Leissmann</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>leonardo.alarcon@kryptus.com</t>
+          <t>marco.leissmann@underprotection.com.br</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>483</v>
+        <v>414</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tenable One Exposure Management Platform Introduction</t>
+          <t>Introduction to Tenable Identity Exposure</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>543439</v>
+        <v>106294</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Kryptus Seguranca da Informacao SA</t>
+          <t>Under Protection Consultoria em Informatica LTDA</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Lucas Carvalho</t>
+          <t>Marco Antonio Leissmann</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>lucas.carvalho@kryptus.com</t>
+          <t>marco.leissmann@underprotection.com.br</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>346</v>
+        <v>483</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Tenable One Exposure Management Platform Introduction</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>543439</v>
+        <v>106294</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Kryptus Seguranca da Informacao SA</t>
+          <t>Under Protection Consultoria em Informatica LTDA</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Paulo Rigonato</t>
+          <t>Marco Antonio Leissmann</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>paulo.monteiro@kryptus.com</t>
+          <t>marco.leissmann@underprotection.com.br</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>346</v>
+        <v>535</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>543439</v>
+        <v>106294</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Kryptus Seguranca da Informacao SA</t>
+          <t>Under Protection Consultoria em Informatica LTDA</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Paulo Rigonato</t>
+          <t>Marco Antonio Leissmann</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>paulo.monteiro@kryptus.com</t>
+          <t>marco.leissmann@underprotection.com.br</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>535</v>
+        <v>552</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Exposure Management Business Theory</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>543439</v>
+        <v>106294</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Kryptus Seguranca da Informacao SA</t>
+          <t>Under Protection Consultoria em Informatica LTDA</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Rogerio Araujo</t>
+          <t>Ney Gelbcke Junior</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>rogerio.araujo@kryptus.com</t>
+          <t>ney.gelbcke@underprotection.com.br</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>333</v>
+        <v>552</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Exposure Management Business Theory</t>
         </is>
       </c>
     </row>
@@ -13162,20 +13172,20 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Rogerio Araujo</t>
+          <t>Atos Ramos</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>rogerio.araujo@kryptus.com</t>
+          <t>atos.ramos@kryptus.com</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>346</v>
+        <v>535</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
@@ -13190,20 +13200,20 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Rogerio Araujo</t>
+          <t>João Bessa</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>rogerio.araujo@kryptus.com</t>
+          <t>joao.bessa@kryptus.com</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>535</v>
+        <v>333</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
@@ -13218,20 +13228,20 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Rogerio Araujo</t>
+          <t>João Bessa</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>rogerio.araujo@kryptus.com</t>
+          <t>joao.bessa@kryptus.com</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>552</v>
+        <v>346</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Exposure Management Business Theory</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -13246,20 +13256,20 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Rogerio Araujo</t>
+          <t>João Bessa</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>rogerio.araujo@kryptus.com</t>
+          <t>joao.bessa@kryptus.com</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>561</v>
+        <v>535</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Tenable One Exposure Management Platform Specialist On-Demand</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
@@ -13274,20 +13284,20 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Sabino Lima</t>
+          <t>João Bessa</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>sabino.lima@kryptus.com</t>
+          <t>joao.bessa@kryptus.com</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>333</v>
+        <v>552</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Exposure Management Business Theory</t>
         </is>
       </c>
     </row>
@@ -13302,20 +13312,20 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Sabino Lima</t>
+          <t>Kauan Querino</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>sabino.lima@kryptus.com</t>
+          <t>kauan.oliveira@kryptus.com</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
@@ -13330,20 +13340,20 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Sabino Lima</t>
+          <t>Kauan Querino</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>sabino.lima@kryptus.com</t>
+          <t>kauan.oliveira@kryptus.com</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>483</v>
+        <v>346</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Tenable One Exposure Management Platform Introduction</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -13358,20 +13368,20 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Sabino Lima</t>
+          <t>Kauan Querino</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>sabino.lima@kryptus.com</t>
+          <t>kauan.oliveira@kryptus.com</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>488</v>
+        <v>535</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
@@ -13386,20 +13396,20 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Sabino Lima</t>
+          <t>Leonardo Alarcon</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>sabino.lima@kryptus.com</t>
+          <t>leonardo.alarcon@kryptus.com</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>535</v>
+        <v>483</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Tenable One Exposure Management Platform Introduction</t>
         </is>
       </c>
     </row>
@@ -13414,20 +13424,20 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Sabino Lima</t>
+          <t>Lucas Carvalho</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>sabino.lima@kryptus.com</t>
+          <t>lucas.carvalho@kryptus.com</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>552</v>
+        <v>346</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Exposure Management Business Theory</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
@@ -13442,388 +13452,376 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Sabino Lima</t>
+          <t>Paulo Rigonato</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>sabino.lima@kryptus.com</t>
+          <t>paulo.monteiro@kryptus.com</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>561</v>
+        <v>346</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Tenable One Exposure Management Platform Specialist On-Demand</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>686107</v>
+        <v>543439</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>e-Safer</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Adenilson Alves da Silva</t>
+          <t>Paulo Rigonato</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>asilva@e-safer.com.br</t>
+          <t>paulo.monteiro@kryptus.com</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>303</v>
+        <v>535</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>686107</v>
+        <v>543439</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>e-Safer</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Ana Clara Ferreira</t>
+          <t>Pedro Nickolas Araujo</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>asantos@e-safer.com.br</t>
+          <t>pedro.araujo@kryptus.com</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable Security Center</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>686107</v>
+        <v>543439</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>e-Safer</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Ana Clara Ferreira</t>
+          <t>Pedro Nickolas Araujo</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>asantos@e-safer.com.br</t>
+          <t>pedro.araujo@kryptus.com</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>483</v>
+        <v>346</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Tenable One Exposure Management Platform Introduction</t>
+          <t>Introduction to Tenable Vulnerability Management</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>686107</v>
+        <v>543439</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>e-Safer</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Arlem Barros</t>
+          <t>Pedro Nickolas Araujo</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>abarros@e-safer.com.br</t>
+          <t>pedro.araujo@kryptus.com</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>303</v>
+        <v>535</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>686107</v>
+        <v>543439</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>e-Safer</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Bruno Magalhaes</t>
+          <t>Pedro Nickolas Araujo</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>bmagalhaes@e-safer.com.br</t>
+          <t>pedro.araujo@kryptus.com</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>303</v>
+        <v>552</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Introduction to Tenable OT Security</t>
+          <t>Exposure Management Business Theory</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>686107</v>
+        <v>543439</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>e-Safer</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Bruno Magalhaes</t>
+          <t>Rogerio Araujo</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>bmagalhaes@e-safer.com.br</t>
+          <t>rogerio.araujo@kryptus.com</t>
         </is>
       </c>
       <c r="E212" t="n">
+        <v>333</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Security Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>543439</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Kryptus Seguranca da Informacao SA</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Rogerio Araujo</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>rogerio.araujo@kryptus.com</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>346</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>543439</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Kryptus Seguranca da Informacao SA</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Rogerio Araujo</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>rogerio.araujo@kryptus.com</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>483</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Tenable One Exposure Management Platform Introduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>543439</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Kryptus Seguranca da Informacao SA</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Rogerio Araujo</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>rogerio.araujo@kryptus.com</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
         <v>535</v>
       </c>
-      <c r="F212" t="inlineStr">
+      <c r="F215" t="inlineStr">
         <is>
           <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>001f200001xtmLIAAY</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Servix Informática Ltda</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Evandro Lima</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>evandro.lima@servix.com</t>
-        </is>
-      </c>
-      <c r="E213" t="n">
-        <v>375</v>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>Tenable Vulnerability Management Specialist</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>001f200001xtmLIAAY</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Servix Informática Ltda</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Evandro Lima</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>evandro.lima@servix.com</t>
-        </is>
-      </c>
-      <c r="E214" t="n">
-        <v>539</v>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>Tenable Cloud Security Specialist On-Demand</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>001f200001xtmLIAAY</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Servix Informática Ltda</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Filipe Augusto</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>filipe.silva@servix.com</t>
-        </is>
-      </c>
-      <c r="E215" t="n">
-        <v>346</v>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
-        </is>
-      </c>
-    </row>
     <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>001f200001xtmLIAAY</t>
-        </is>
+      <c r="A216" t="n">
+        <v>543439</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Servix Informática Ltda</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>João Ferreira</t>
+          <t>Rogerio Araujo</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>joao.ferreira@servix.com</t>
+          <t>rogerio.araujo@kryptus.com</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>488</v>
+        <v>552</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+          <t>Exposure Management Business Theory</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>001f200001xtmLIAAY</t>
-        </is>
+      <c r="A217" t="n">
+        <v>543439</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Servix Informática Ltda</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>João Ferreira</t>
+          <t>Rogerio Araujo</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>joao.ferreira@servix.com</t>
+          <t>rogerio.araujo@kryptus.com</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>539</v>
+        <v>561</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Tenable Cloud Security Specialist On-Demand</t>
+          <t>Tenable One Exposure Management Platform Specialist On-Demand</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>001f200001xtmLIAAY</t>
-        </is>
+      <c r="A218" t="n">
+        <v>543439</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Servix Informática Ltda</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Matheus Passos</t>
+          <t>Ronielly Nascimento</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>matheus.passos@servix.com</t>
+          <t>ronielly.nascimento@kryptus.com</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>333</v>
+        <v>535</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Security Center</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>644733</v>
+        <v>543439</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Ana Loucenco</t>
+          <t>Sabino Lima</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>ana.lourenco@itprotect.com.br</t>
+          <t>sabino.lima@kryptus.com</t>
         </is>
       </c>
       <c r="E219" t="n">
@@ -13837,21 +13835,21 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>644733</v>
+        <v>543439</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Ana Loucenco</t>
+          <t>Sabino Lima</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>ana.lourenco@itprotect.com.br</t>
+          <t>sabino.lima@kryptus.com</t>
         </is>
       </c>
       <c r="E220" t="n">
@@ -13865,21 +13863,21 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>644733</v>
+        <v>543439</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Ana Loucenco</t>
+          <t>Sabino Lima</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>ana.lourenco@itprotect.com.br</t>
+          <t>sabino.lima@kryptus.com</t>
         </is>
       </c>
       <c r="E221" t="n">
@@ -13893,133 +13891,133 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>644733</v>
+        <v>543439</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Ana Loucenco</t>
+          <t>Sabino Lima</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>ana.lourenco@itprotect.com.br</t>
+          <t>sabino.lima@kryptus.com</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>535</v>
+        <v>488</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>644733</v>
+        <v>543439</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>FLAVIO BARBOSA</t>
+          <t>Sabino Lima</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>flavio.barbosa@itprotect.com.br</t>
+          <t>sabino.lima@kryptus.com</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>346</v>
+        <v>535</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>644733</v>
+        <v>543439</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Paul M</t>
+          <t>Sabino Lima</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>paulo.medeiros@itprotect.com.br</t>
+          <t>sabino.lima@kryptus.com</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>375</v>
+        <v>552</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Tenable Vulnerability Management Specialist</t>
+          <t>Exposure Management Business Theory</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>644733</v>
+        <v>543439</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>Kryptus Seguranca da Informacao SA</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Paul M</t>
+          <t>Sabino Lima</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>paulo.medeiros@itprotect.com.br</t>
+          <t>sabino.lima@kryptus.com</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>539</v>
+        <v>561</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Tenable Cloud Security Specialist On-Demand</t>
+          <t>Tenable One Exposure Management Platform Specialist On-Demand</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>644733</v>
+        <v>686107</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>e-Safer</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Pedro Comin</t>
+          <t>Adenilson Alves da Silva</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>pedro.comin@itprotect.com.br</t>
+          <t>asilva@e-safer.com.br</t>
         </is>
       </c>
       <c r="E226" t="n">
@@ -14033,21 +14031,21 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>644733</v>
+        <v>686107</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>e-Safer</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Pedro Comin</t>
+          <t>Ana Clara Ferreira</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>pedro.comin@itprotect.com.br</t>
+          <t>asantos@e-safer.com.br</t>
         </is>
       </c>
       <c r="E227" t="n">
@@ -14061,189 +14059,195 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>644733</v>
+        <v>686107</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>e-Safer</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Pedro Comin</t>
+          <t>Ana Clara Ferreira</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>pedro.comin@itprotect.com.br</t>
+          <t>asantos@e-safer.com.br</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+          <t>Tenable One Exposure Management Platform Introduction</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>644733</v>
+        <v>686107</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>e-Safer</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Ricardo Claus</t>
+          <t>Arlem Barros</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>ricardo.claus@itprotect.com.br</t>
+          <t>abarros@e-safer.com.br</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>346</v>
+        <v>303</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Vulnerability Management</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>644733</v>
+        <v>686107</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>e-Safer</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Ricardo Claus</t>
+          <t>Bruno Magalhaes</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>ricardo.claus@itprotect.com.br</t>
+          <t>bmagalhaes@e-safer.com.br</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>414</v>
+        <v>303</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Identity Exposure</t>
+          <t>Introduction to Tenable OT Security</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>644733</v>
+        <v>686107</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>e-Safer</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Ricardo Claus</t>
+          <t>Bruno Magalhaes</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>ricardo.claus@itprotect.com.br</t>
+          <t>bmagalhaes@e-safer.com.br</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>483</v>
+        <v>535</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Tenable One Exposure Management Platform Introduction</t>
+          <t>Introduction to Tenable Cloud Security</t>
         </is>
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="n">
-        <v>644733</v>
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>001f200001xtmLIAAY</t>
+        </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>Servix Informática Ltda</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Ricardo Claus</t>
+          <t>Evandro Lima</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>ricardo.claus@itprotect.com.br</t>
+          <t>evandro.lima@servix.com</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>535</v>
+        <v>375</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Introduction to Tenable Cloud Security</t>
+          <t>Tenable Vulnerability Management Specialist</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="n">
-        <v>644733</v>
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>001f200001xtmLIAAY</t>
+        </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>Servix Informática Ltda</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Sávio Alves</t>
+          <t>Evandro Lima</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>savio.alves@itprotect.com.br</t>
+          <t>evandro.lima@servix.com</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>304</v>
+        <v>539</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Tenable Security Center Specialist</t>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
         </is>
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="n">
-        <v>644733</v>
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>001f200001xtmLIAAY</t>
+        </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+          <t>Servix Informática Ltda</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Thiago Borges</t>
+          <t>Filipe Augusto</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>thiago.borges@itprotect.com.br</t>
+          <t>filipe.silva@servix.com</t>
         </is>
       </c>
       <c r="E234" t="n">
@@ -14256,28 +14260,566 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="n">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>001f200001xtmLIAAY</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Servix Informática Ltda</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>João Ferreira</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>joao.ferreira@servix.com</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>488</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>001f200001xtmLIAAY</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Servix Informática Ltda</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>João Ferreira</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>joao.ferreira@servix.com</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>539</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>001f200001xtmLIAAY</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Servix Informática Ltda</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Matheus Passos</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>matheus.passos@servix.com</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>333</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Security Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
         <v>644733</v>
       </c>
-      <c r="B235" t="inlineStr">
+      <c r="B238" t="inlineStr">
         <is>
           <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr">
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Ana Loucenco</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>ana.lourenco@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>333</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Security Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Ana Loucenco</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>ana.lourenco@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>346</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Ana Loucenco</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>ana.lourenco@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>483</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Tenable One Exposure Management Platform Introduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Ana Loucenco</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>ana.lourenco@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>535</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Cloud Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>FLAVIO BARBOSA</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>flavio.barbosa@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>346</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Paul M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>paulo.medeiros@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>375</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Paul M</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>paulo.medeiros@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>539</v>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Tenable Cloud Security Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Pedro Comin</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>pedro.comin@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>303</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable OT Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Pedro Comin</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>pedro.comin@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>346</v>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Pedro Comin</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>pedro.comin@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>488</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Tenable Vulnerability Management Specialist On-Demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Ricardo Claus</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>ricardo.claus@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>346</v>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Ricardo Claus</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>ricardo.claus@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>414</v>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Identity Exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Ricardo Claus</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>ricardo.claus@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>483</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Tenable One Exposure Management Platform Introduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Ricardo Claus</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>ricardo.claus@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>535</v>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Cloud Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Sávio Alves</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>savio.alves@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>304</v>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Tenable Security Center Specialist</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Thiago Borges</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>thiago.borges@itprotect.com.br</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>346</v>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Introduction to Tenable Vulnerability Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>644733</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>IT PROTECT SERVICOS DE CONSULTORIA EM INFORMATICA EIRELI</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
         <is>
           <t>Wilmar Neto</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr">
+      <c r="D254" t="inlineStr">
         <is>
           <t>wilmar.neto@itprotect.com.br</t>
         </is>
       </c>
-      <c r="E235" t="n">
+      <c r="E254" t="n">
         <v>375</v>
       </c>
-      <c r="F235" t="inlineStr">
+      <c r="F254" t="inlineStr">
         <is>
           <t>Tenable Vulnerability Management Specialist</t>
         </is>
